--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Холод-Климат Сма</t>
   </si>
   <si>
-    <t xml:space="preserve">Uriarte taldea</t>
+    <t xml:space="preserve">Uriarte</t>
   </si>
   <si>
     <t xml:space="preserve">Favale</t>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">Torrington</t>
   </si>
   <si>
-    <t xml:space="preserve">Fluorgas Necton</t>
+    <t xml:space="preserve">Fluorgaz</t>
   </si>
   <si>
     <t xml:space="preserve">Климат</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">https://www.fijamom.com.ar/</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribuidora Belgrano</t>
+    <t xml:space="preserve">Belgrano</t>
   </si>
   <si>
     <t xml:space="preserve">https://catalogo.duxsoftware.com.ar/3820</t>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
   <si>
     <t xml:space="preserve">Рубрика</t>
   </si>
@@ -73,7 +73,13 @@
     <t xml:space="preserve">Uriarte</t>
   </si>
   <si>
+    <t xml:space="preserve">https://uriarte.com.ar/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Favale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.repuestosfavale.com/</t>
   </si>
   <si>
     <t xml:space="preserve">Фреон</t>
@@ -82,7 +88,13 @@
     <t xml:space="preserve">Torrington</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.torrington.com.ar/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fluorgaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://listado.mercadolibre.com.ar/fluor-gas-refrigerantes</t>
   </si>
   <si>
     <t xml:space="preserve">Климат</t>
@@ -115,13 +127,22 @@
     <t xml:space="preserve">Electrofrig</t>
   </si>
   <si>
+    <t xml:space="preserve">http://www.electrofrig.com.ar/es/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Electrocity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://electrocity.com.ar</t>
   </si>
   <si>
     <t xml:space="preserve">Масла</t>
   </si>
   <si>
     <t xml:space="preserve">Refrioil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://refrioil.com/</t>
   </si>
   <si>
     <t xml:space="preserve">Тэн холодильника</t>
@@ -136,6 +157,9 @@
     <t xml:space="preserve">IMI</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.instagram.com/imi.metalurgica.integral/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Сма</t>
   </si>
   <si>
@@ -145,7 +169,13 @@
     <t xml:space="preserve">Roma Repuestos insumos</t>
   </si>
   <si>
+    <t xml:space="preserve">https://tienda.romarep.com.ar/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oeste service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://oesteservice.com.ar/</t>
   </si>
   <si>
     <t xml:space="preserve">Distribuidora JC</t>
@@ -166,7 +196,13 @@
     <t xml:space="preserve">Dpmg Anton</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.dpmg.com.ar/brand/anton/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tidar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tidar.com.ar/</t>
   </si>
   <si>
     <t xml:space="preserve">Casa Jarse</t>
@@ -178,10 +214,19 @@
     <t xml:space="preserve">Lujumar srl</t>
   </si>
   <si>
+    <t xml:space="preserve">https://lujumar.com.ar/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Norfrig</t>
   </si>
   <si>
+    <t xml:space="preserve">https://norfrig.com.ar/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pilisar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pilisardistribuidor.com.ar/</t>
   </si>
   <si>
     <t xml:space="preserve">Подшипники</t>
@@ -193,10 +238,16 @@
     <t xml:space="preserve">Industrias MCT</t>
   </si>
   <si>
+    <t xml:space="preserve">https://industriasmct.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">СВЧ</t>
   </si>
   <si>
     <t xml:space="preserve">Guillermo pini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pini.com.ar/</t>
   </si>
   <si>
     <t xml:space="preserve">СВЧ и котлы</t>
@@ -205,10 +256,16 @@
     <t xml:space="preserve">Damfer</t>
   </si>
   <si>
+    <t xml:space="preserve">https://damfer.com/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Конденсаторы</t>
   </si>
   <si>
     <t xml:space="preserve">Persano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.persano.com.ar/index.php</t>
   </si>
   <si>
     <t xml:space="preserve">Итог по холоду и климату</t>
@@ -675,7 +732,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="6" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="8" style="1" width="8.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="10.16"/>
   </cols>
   <sheetData>
@@ -854,7 +914,9 @@
       <c r="D6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -878,13 +940,15 @@
         <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -905,16 +969,18 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -935,16 +1001,18 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -965,10 +1033,10 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>9</v>
@@ -977,7 +1045,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1002,7 +1070,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>9</v>
@@ -1011,7 +1079,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1033,10 +1101,10 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>9</v>
@@ -1045,7 +1113,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -1067,16 +1135,18 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -1098,11 +1168,13 @@
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -1123,16 +1195,18 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1153,10 +1227,10 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="7" t="s">
@@ -1183,16 +1257,18 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -1213,10 +1289,10 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="7" t="s">
@@ -1243,10 +1319,10 @@
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>9</v>
@@ -1254,7 +1330,9 @@
       <c r="D19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -1275,16 +1353,18 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -1305,10 +1385,10 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>9</v>
@@ -1317,7 +1397,7 @@
         <v>9</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1339,10 +1419,10 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>9</v>
@@ -1351,7 +1431,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1373,16 +1453,18 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -1404,11 +1486,13 @@
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="12" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -1430,12 +1514,12 @@
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="7"/>
       <c r="E25" s="11" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1457,14 +1541,16 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="7"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -1485,14 +1571,16 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -1513,14 +1601,16 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="2"/>
+      <c r="E28" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -1541,10 +1631,10 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1570,11 +1660,13 @@
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -1595,14 +1687,16 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -1623,16 +1717,18 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -1653,14 +1749,16 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -1681,7 +1779,7 @@
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="13" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
@@ -24620,11 +24718,30 @@
     <hyperlink ref="E3" r:id="rId1" display="https://www.ansal.com.ar/"/>
     <hyperlink ref="E4" r:id="rId2" display="https://www.reld.com.ar/"/>
     <hyperlink ref="E5" r:id="rId3" display="www.bellinihnos.com.ar/"/>
-    <hyperlink ref="E10" r:id="rId4" display="https://www.fijamom.com.ar/"/>
-    <hyperlink ref="E11" r:id="rId5" display="https://catalogo.duxsoftware.com.ar/3820"/>
-    <hyperlink ref="E12" r:id="rId6" display="https://www.agrupacionduna.com/"/>
-    <hyperlink ref="E21" r:id="rId7" display="https://distribuidorajc.com/"/>
-    <hyperlink ref="E25" r:id="rId8" display="https://casajarse.com/"/>
+    <hyperlink ref="E6" r:id="rId4" display="https://uriarte.com.ar/"/>
+    <hyperlink ref="E7" r:id="rId5" display="https://www.repuestosfavale.com/"/>
+    <hyperlink ref="E8" r:id="rId6" display="https://www.torrington.com.ar/"/>
+    <hyperlink ref="E9" r:id="rId7" display="https://listado.mercadolibre.com.ar/fluor-gas-refrigerantes"/>
+    <hyperlink ref="E10" r:id="rId8" display="https://www.fijamom.com.ar/"/>
+    <hyperlink ref="E11" r:id="rId9" display="https://catalogo.duxsoftware.com.ar/3820"/>
+    <hyperlink ref="E12" r:id="rId10" display="https://www.agrupacionduna.com/"/>
+    <hyperlink ref="E13" r:id="rId11" display="http://www.electrofrig.com.ar/es/"/>
+    <hyperlink ref="E14" r:id="rId12" display="https://electrocity.com.ar"/>
+    <hyperlink ref="E15" r:id="rId13" display="https://refrioil.com/"/>
+    <hyperlink ref="E17" r:id="rId14" display="https://www.instagram.com/imi.metalurgica.integral/"/>
+    <hyperlink ref="E19" r:id="rId15" display="https://tienda.romarep.com.ar/"/>
+    <hyperlink ref="E20" r:id="rId16" display="https://oesteservice.com.ar/"/>
+    <hyperlink ref="E21" r:id="rId17" display="https://distribuidorajc.com/"/>
+    <hyperlink ref="E23" r:id="rId18" display="https://www.dpmg.com.ar/brand/anton/"/>
+    <hyperlink ref="E24" r:id="rId19" display="https://tidar.com.ar/"/>
+    <hyperlink ref="E25" r:id="rId20" display="https://casajarse.com/"/>
+    <hyperlink ref="E26" r:id="rId21" display="https://lujumar.com.ar/"/>
+    <hyperlink ref="E27" r:id="rId22" display="https://norfrig.com.ar/"/>
+    <hyperlink ref="E28" r:id="rId23" display="https://pilisardistribuidor.com.ar/"/>
+    <hyperlink ref="E30" r:id="rId24" display="https://industriasmct.com"/>
+    <hyperlink ref="E31" r:id="rId25" display="https://pini.com.ar/"/>
+    <hyperlink ref="E32" r:id="rId26" display="https://damfer.com/"/>
+    <hyperlink ref="E33" r:id="rId27" display="https://www.persano.com.ar/index.php"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t xml:space="preserve">Рубрика</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t xml:space="preserve">Пароль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Скидка %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVA</t>
   </si>
   <si>
     <t xml:space="preserve">Холод-Климат</t>
@@ -275,8 +281,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -415,7 +422,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -449,6 +456,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -732,10 +743,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.43"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="8" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="9" style="1" width="8.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="10.16"/>
   </cols>
   <sheetData>
@@ -785,8 +797,12 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -803,24 +819,28 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="H3" s="9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -837,19 +857,19 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -871,19 +891,19 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -905,17 +925,17 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
-      <c r="C6" s="9"/>
+      <c r="C6" s="10"/>
       <c r="D6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -937,17 +957,17 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
-      <c r="C7" s="9"/>
+      <c r="C7" s="10"/>
       <c r="D7" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -969,17 +989,17 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1001,17 +1021,17 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1033,19 +1053,19 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>27</v>
+      <c r="E10" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1067,19 +1087,19 @@
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>29</v>
+      <c r="E11" s="12" t="s">
+        <v>31</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1101,19 +1121,19 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
@@ -1135,17 +1155,17 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -1168,12 +1188,12 @@
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="7"/>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -1195,17 +1215,17 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1227,14 +1247,14 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
@@ -1257,17 +1277,17 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1289,14 +1309,14 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
@@ -1319,19 +1339,19 @@
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -1353,17 +1373,17 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1385,19 +1405,19 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>53</v>
+      <c r="E21" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1419,19 +1439,19 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1453,17 +1473,17 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="10"/>
       <c r="D23" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1485,13 +1505,13 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="12" t="s">
-        <v>59</v>
+      <c r="B24" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="7"/>
       <c r="E24" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1514,12 +1534,12 @@
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="11" t="s">
-        <v>62</v>
+      <c r="E25" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1541,15 +1561,15 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="7"/>
       <c r="E26" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1571,15 +1591,15 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
@@ -1601,15 +1621,15 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="7"/>
       <c r="E28" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1631,10 +1651,10 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1660,12 +1680,12 @@
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1687,15 +1707,15 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -1717,17 +1737,17 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1749,15 +1769,15 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1778,12 +1798,12 @@
       <c r="V33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="13" t="s">
-        <v>82</v>
+      <c r="A34" s="14" t="s">
+        <v>84</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="88">
   <si>
     <t xml:space="preserve">Рубрика</t>
   </si>
@@ -43,6 +43,9 @@
     <t xml:space="preserve">Пароль</t>
   </si>
   <si>
+    <t xml:space="preserve">Валюта</t>
+  </si>
+  <si>
     <t xml:space="preserve">Скидка %</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.ansal.com.ar/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARS</t>
   </si>
   <si>
     <t xml:space="preserve">Reld</t>
@@ -80,6 +86,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://uriarte.com.ar/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USD</t>
   </si>
   <si>
     <t xml:space="preserve">Favale</t>
@@ -285,7 +294,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +339,12 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
     <font>
       <u val="single"/>
@@ -422,7 +437,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -467,7 +482,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -475,7 +490,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -736,8 +755,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V1048576"/>
-  <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:W1048576"/>
+  <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="17.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.43"/>
@@ -746,9 +765,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="9" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="16.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="10" style="1" width="8.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16380" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -774,6 +793,7 @@
       <c r="T1" s="3"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -803,7 +823,9 @@
       <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -816,32 +838,35 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="9" t="n">
         <v>0.21</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
@@ -854,26 +879,29 @@
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
       <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -888,26 +916,29 @@
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
       <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -922,24 +953,27 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
       <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -954,24 +988,27 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
       <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -986,24 +1023,27 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="H8" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1018,24 +1058,27 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
       <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="H9" s="11" t="s">
+        <v>22</v>
+      </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1050,26 +1093,29 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>29</v>
+      <c r="E10" s="12" t="s">
+        <v>32</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1084,26 +1130,29 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>31</v>
+      <c r="E11" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1118,26 +1167,29 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
       <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -1152,24 +1204,27 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
       <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1184,20 +1239,23 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
       <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="7"/>
       <c r="E14" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="H14" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1212,24 +1270,27 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1244,22 +1305,25 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1274,24 +1338,27 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
       <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1306,22 +1373,25 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1336,26 +1406,29 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
       <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="H19" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1370,24 +1443,27 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
       <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1402,26 +1478,29 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
       <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>55</v>
+      <c r="E21" s="12" t="s">
+        <v>58</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1436,26 +1515,29 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
       <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1470,24 +1552,27 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
       <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -1502,20 +1587,23 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
       <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="13" t="s">
-        <v>61</v>
+      <c r="B24" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="7"/>
       <c r="E24" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
+      <c r="H24" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1530,20 +1618,23 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
       <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="12" t="s">
-        <v>64</v>
+      <c r="E25" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1558,22 +1649,25 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
       <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="7"/>
       <c r="E26" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="H26" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1588,22 +1682,25 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
       <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="H27" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1618,22 +1715,25 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
       <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="7"/>
       <c r="E28" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="H28" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1648,20 +1748,23 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
       <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -1676,20 +1779,23 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
       <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+      <c r="H30" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -1704,22 +1810,25 @@
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
       <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
+      <c r="H31" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1734,24 +1843,27 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
       <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
+      <c r="H32" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -1766,22 +1878,25 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
       <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
+      <c r="H33" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -1796,14 +1911,15 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
       <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
-        <v>84</v>
+      <c r="A34" s="15" t="s">
+        <v>87</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="16"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -1822,6 +1938,7 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
       <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2"/>
@@ -1846,6 +1963,7 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1883,6 +2001,7 @@
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
+      <c r="W49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
@@ -1907,6 +2026,7 @@
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
@@ -1931,6 +2051,7 @@
       <c r="T51" s="3"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
@@ -1955,6 +2076,7 @@
       <c r="T52" s="3"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
@@ -1979,6 +2101,7 @@
       <c r="T53" s="3"/>
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
+      <c r="W53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
@@ -2003,6 +2126,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="2"/>
@@ -2027,6 +2151,7 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2"/>
@@ -2051,6 +2176,7 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2"/>
@@ -2075,6 +2201,7 @@
       <c r="T57" s="3"/>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2"/>
@@ -2099,6 +2226,7 @@
       <c r="T58" s="3"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
@@ -2123,6 +2251,7 @@
       <c r="T59" s="3"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
+      <c r="W59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
@@ -2147,6 +2276,7 @@
       <c r="T60" s="3"/>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="2"/>
@@ -2171,6 +2301,7 @@
       <c r="T61" s="3"/>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
@@ -2195,6 +2326,7 @@
       <c r="T62" s="3"/>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="2"/>
@@ -2219,6 +2351,7 @@
       <c r="T63" s="3"/>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
+      <c r="W63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="2"/>
@@ -2243,6 +2376,7 @@
       <c r="T64" s="3"/>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
@@ -2267,6 +2401,7 @@
       <c r="T65" s="3"/>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
+      <c r="W65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
@@ -2291,6 +2426,7 @@
       <c r="T66" s="3"/>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="2"/>
@@ -2315,6 +2451,7 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
@@ -2339,6 +2476,7 @@
       <c r="T68" s="3"/>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="2"/>
@@ -2363,6 +2501,7 @@
       <c r="T69" s="3"/>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
+      <c r="W69" s="3"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
@@ -2387,6 +2526,7 @@
       <c r="T70" s="3"/>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="2"/>
@@ -2411,6 +2551,7 @@
       <c r="T71" s="3"/>
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
+      <c r="W71" s="3"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="2"/>
@@ -2435,6 +2576,7 @@
       <c r="T72" s="3"/>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="2"/>
@@ -2459,6 +2601,7 @@
       <c r="T73" s="3"/>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
+      <c r="W73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="2"/>
@@ -2483,6 +2626,7 @@
       <c r="T74" s="3"/>
       <c r="U74" s="3"/>
       <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="2"/>
@@ -2507,6 +2651,7 @@
       <c r="T75" s="3"/>
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
+      <c r="W75" s="3"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
@@ -2531,6 +2676,7 @@
       <c r="T76" s="3"/>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="2"/>
@@ -2555,6 +2701,7 @@
       <c r="T77" s="3"/>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
+      <c r="W77" s="3"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="2"/>
@@ -2579,6 +2726,7 @@
       <c r="T78" s="3"/>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="2"/>
@@ -2603,6 +2751,7 @@
       <c r="T79" s="3"/>
       <c r="U79" s="3"/>
       <c r="V79" s="3"/>
+      <c r="W79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="2"/>
@@ -2627,6 +2776,7 @@
       <c r="T80" s="3"/>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="2"/>
@@ -2651,6 +2801,7 @@
       <c r="T81" s="3"/>
       <c r="U81" s="3"/>
       <c r="V81" s="3"/>
+      <c r="W81" s="3"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="2"/>
@@ -2675,6 +2826,7 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="2"/>
@@ -2699,6 +2851,7 @@
       <c r="T83" s="3"/>
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
+      <c r="W83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
@@ -2723,6 +2876,7 @@
       <c r="T84" s="3"/>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
@@ -2747,6 +2901,7 @@
       <c r="T85" s="3"/>
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
+      <c r="W85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="2"/>
@@ -2771,6 +2926,7 @@
       <c r="T86" s="3"/>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="2"/>
@@ -2795,6 +2951,7 @@
       <c r="T87" s="3"/>
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="2"/>
@@ -2819,6 +2976,7 @@
       <c r="T88" s="3"/>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="2"/>
@@ -2843,6 +3001,7 @@
       <c r="T89" s="3"/>
       <c r="U89" s="3"/>
       <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
@@ -2867,6 +3026,7 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
@@ -2891,6 +3051,7 @@
       <c r="T91" s="3"/>
       <c r="U91" s="3"/>
       <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
@@ -2915,6 +3076,7 @@
       <c r="T92" s="3"/>
       <c r="U92" s="3"/>
       <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
@@ -2939,6 +3101,7 @@
       <c r="T93" s="3"/>
       <c r="U93" s="3"/>
       <c r="V93" s="3"/>
+      <c r="W93" s="3"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
@@ -2963,6 +3126,7 @@
       <c r="T94" s="3"/>
       <c r="U94" s="3"/>
       <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="2"/>
@@ -2987,6 +3151,7 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="2"/>
@@ -3011,6 +3176,7 @@
       <c r="T96" s="3"/>
       <c r="U96" s="3"/>
       <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
@@ -3035,6 +3201,7 @@
       <c r="T97" s="3"/>
       <c r="U97" s="3"/>
       <c r="V97" s="3"/>
+      <c r="W97" s="3"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="2"/>
@@ -3059,6 +3226,7 @@
       <c r="T98" s="3"/>
       <c r="U98" s="3"/>
       <c r="V98" s="3"/>
+      <c r="W98" s="3"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="2"/>
@@ -3083,6 +3251,7 @@
       <c r="T99" s="3"/>
       <c r="U99" s="3"/>
       <c r="V99" s="3"/>
+      <c r="W99" s="3"/>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="2"/>
@@ -3107,6 +3276,7 @@
       <c r="T100" s="3"/>
       <c r="U100" s="3"/>
       <c r="V100" s="3"/>
+      <c r="W100" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
@@ -3131,6 +3301,7 @@
       <c r="T101" s="3"/>
       <c r="U101" s="3"/>
       <c r="V101" s="3"/>
+      <c r="W101" s="3"/>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="2"/>
@@ -3155,6 +3326,7 @@
       <c r="T102" s="3"/>
       <c r="U102" s="3"/>
       <c r="V102" s="3"/>
+      <c r="W102" s="3"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
@@ -3179,6 +3351,7 @@
       <c r="T103" s="3"/>
       <c r="U103" s="3"/>
       <c r="V103" s="3"/>
+      <c r="W103" s="3"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
@@ -3203,6 +3376,7 @@
       <c r="T104" s="3"/>
       <c r="U104" s="3"/>
       <c r="V104" s="3"/>
+      <c r="W104" s="3"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
@@ -3227,6 +3401,7 @@
       <c r="T105" s="3"/>
       <c r="U105" s="3"/>
       <c r="V105" s="3"/>
+      <c r="W105" s="3"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
@@ -3251,6 +3426,7 @@
       <c r="T106" s="3"/>
       <c r="U106" s="3"/>
       <c r="V106" s="3"/>
+      <c r="W106" s="3"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="2"/>
@@ -3275,6 +3451,7 @@
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="3"/>
+      <c r="W107" s="3"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="2"/>
@@ -3299,6 +3476,7 @@
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="3"/>
+      <c r="W108" s="3"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
@@ -3323,6 +3501,7 @@
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
       <c r="V109" s="3"/>
+      <c r="W109" s="3"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="2"/>
@@ -3347,6 +3526,7 @@
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="3"/>
+      <c r="W110" s="3"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="2"/>
@@ -3371,6 +3551,7 @@
       <c r="T111" s="3"/>
       <c r="U111" s="3"/>
       <c r="V111" s="3"/>
+      <c r="W111" s="3"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="2"/>
@@ -3395,6 +3576,7 @@
       <c r="T112" s="3"/>
       <c r="U112" s="3"/>
       <c r="V112" s="3"/>
+      <c r="W112" s="3"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="2"/>
@@ -3419,6 +3601,7 @@
       <c r="T113" s="3"/>
       <c r="U113" s="3"/>
       <c r="V113" s="3"/>
+      <c r="W113" s="3"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="2"/>
@@ -3443,6 +3626,7 @@
       <c r="T114" s="3"/>
       <c r="U114" s="3"/>
       <c r="V114" s="3"/>
+      <c r="W114" s="3"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="2"/>
@@ -3467,6 +3651,7 @@
       <c r="T115" s="3"/>
       <c r="U115" s="3"/>
       <c r="V115" s="3"/>
+      <c r="W115" s="3"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="2"/>
@@ -3491,6 +3676,7 @@
       <c r="T116" s="3"/>
       <c r="U116" s="3"/>
       <c r="V116" s="3"/>
+      <c r="W116" s="3"/>
     </row>
     <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="2"/>
@@ -3515,6 +3701,7 @@
       <c r="T117" s="3"/>
       <c r="U117" s="3"/>
       <c r="V117" s="3"/>
+      <c r="W117" s="3"/>
     </row>
     <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="2"/>
@@ -3539,6 +3726,7 @@
       <c r="T118" s="3"/>
       <c r="U118" s="3"/>
       <c r="V118" s="3"/>
+      <c r="W118" s="3"/>
     </row>
     <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="2"/>
@@ -3563,6 +3751,7 @@
       <c r="T119" s="3"/>
       <c r="U119" s="3"/>
       <c r="V119" s="3"/>
+      <c r="W119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="2"/>
@@ -3587,6 +3776,7 @@
       <c r="T120" s="3"/>
       <c r="U120" s="3"/>
       <c r="V120" s="3"/>
+      <c r="W120" s="3"/>
     </row>
     <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="2"/>
@@ -3611,6 +3801,7 @@
       <c r="T121" s="3"/>
       <c r="U121" s="3"/>
       <c r="V121" s="3"/>
+      <c r="W121" s="3"/>
     </row>
     <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="2"/>
@@ -3635,6 +3826,7 @@
       <c r="T122" s="3"/>
       <c r="U122" s="3"/>
       <c r="V122" s="3"/>
+      <c r="W122" s="3"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="2"/>
@@ -3659,6 +3851,7 @@
       <c r="T123" s="3"/>
       <c r="U123" s="3"/>
       <c r="V123" s="3"/>
+      <c r="W123" s="3"/>
     </row>
     <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="2"/>
@@ -3683,6 +3876,7 @@
       <c r="T124" s="3"/>
       <c r="U124" s="3"/>
       <c r="V124" s="3"/>
+      <c r="W124" s="3"/>
     </row>
     <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
@@ -3707,6 +3901,7 @@
       <c r="T125" s="3"/>
       <c r="U125" s="3"/>
       <c r="V125" s="3"/>
+      <c r="W125" s="3"/>
     </row>
     <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
@@ -3731,6 +3926,7 @@
       <c r="T126" s="3"/>
       <c r="U126" s="3"/>
       <c r="V126" s="3"/>
+      <c r="W126" s="3"/>
     </row>
     <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
@@ -3755,6 +3951,7 @@
       <c r="T127" s="3"/>
       <c r="U127" s="3"/>
       <c r="V127" s="3"/>
+      <c r="W127" s="3"/>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="2"/>
@@ -3779,6 +3976,7 @@
       <c r="T128" s="3"/>
       <c r="U128" s="3"/>
       <c r="V128" s="3"/>
+      <c r="W128" s="3"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="2"/>
@@ -3803,6 +4001,7 @@
       <c r="T129" s="3"/>
       <c r="U129" s="3"/>
       <c r="V129" s="3"/>
+      <c r="W129" s="3"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="2"/>
@@ -3827,6 +4026,7 @@
       <c r="T130" s="3"/>
       <c r="U130" s="3"/>
       <c r="V130" s="3"/>
+      <c r="W130" s="3"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
@@ -3851,6 +4051,7 @@
       <c r="T131" s="3"/>
       <c r="U131" s="3"/>
       <c r="V131" s="3"/>
+      <c r="W131" s="3"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
@@ -3875,6 +4076,7 @@
       <c r="T132" s="3"/>
       <c r="U132" s="3"/>
       <c r="V132" s="3"/>
+      <c r="W132" s="3"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="2"/>
@@ -3899,6 +4101,7 @@
       <c r="T133" s="3"/>
       <c r="U133" s="3"/>
       <c r="V133" s="3"/>
+      <c r="W133" s="3"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
@@ -3923,6 +4126,7 @@
       <c r="T134" s="3"/>
       <c r="U134" s="3"/>
       <c r="V134" s="3"/>
+      <c r="W134" s="3"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
@@ -3947,6 +4151,7 @@
       <c r="T135" s="3"/>
       <c r="U135" s="3"/>
       <c r="V135" s="3"/>
+      <c r="W135" s="3"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="2"/>
@@ -3971,6 +4176,7 @@
       <c r="T136" s="3"/>
       <c r="U136" s="3"/>
       <c r="V136" s="3"/>
+      <c r="W136" s="3"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="2"/>
@@ -3995,6 +4201,7 @@
       <c r="T137" s="3"/>
       <c r="U137" s="3"/>
       <c r="V137" s="3"/>
+      <c r="W137" s="3"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="2"/>
@@ -4019,6 +4226,7 @@
       <c r="T138" s="3"/>
       <c r="U138" s="3"/>
       <c r="V138" s="3"/>
+      <c r="W138" s="3"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="2"/>
@@ -4043,6 +4251,7 @@
       <c r="T139" s="3"/>
       <c r="U139" s="3"/>
       <c r="V139" s="3"/>
+      <c r="W139" s="3"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
@@ -4067,6 +4276,7 @@
       <c r="T140" s="3"/>
       <c r="U140" s="3"/>
       <c r="V140" s="3"/>
+      <c r="W140" s="3"/>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="2"/>
@@ -4091,6 +4301,7 @@
       <c r="T141" s="3"/>
       <c r="U141" s="3"/>
       <c r="V141" s="3"/>
+      <c r="W141" s="3"/>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="2"/>
@@ -4115,6 +4326,7 @@
       <c r="T142" s="3"/>
       <c r="U142" s="3"/>
       <c r="V142" s="3"/>
+      <c r="W142" s="3"/>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="2"/>
@@ -4139,6 +4351,7 @@
       <c r="T143" s="3"/>
       <c r="U143" s="3"/>
       <c r="V143" s="3"/>
+      <c r="W143" s="3"/>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
@@ -4163,6 +4376,7 @@
       <c r="T144" s="3"/>
       <c r="U144" s="3"/>
       <c r="V144" s="3"/>
+      <c r="W144" s="3"/>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="2"/>
@@ -4187,6 +4401,7 @@
       <c r="T145" s="3"/>
       <c r="U145" s="3"/>
       <c r="V145" s="3"/>
+      <c r="W145" s="3"/>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
@@ -4211,6 +4426,7 @@
       <c r="T146" s="3"/>
       <c r="U146" s="3"/>
       <c r="V146" s="3"/>
+      <c r="W146" s="3"/>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
@@ -4235,6 +4451,7 @@
       <c r="T147" s="3"/>
       <c r="U147" s="3"/>
       <c r="V147" s="3"/>
+      <c r="W147" s="3"/>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="2"/>
@@ -4259,6 +4476,7 @@
       <c r="T148" s="3"/>
       <c r="U148" s="3"/>
       <c r="V148" s="3"/>
+      <c r="W148" s="3"/>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="2"/>
@@ -4283,6 +4501,7 @@
       <c r="T149" s="3"/>
       <c r="U149" s="3"/>
       <c r="V149" s="3"/>
+      <c r="W149" s="3"/>
     </row>
     <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="2"/>
@@ -4307,6 +4526,7 @@
       <c r="T150" s="3"/>
       <c r="U150" s="3"/>
       <c r="V150" s="3"/>
+      <c r="W150" s="3"/>
     </row>
     <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="2"/>
@@ -4331,6 +4551,7 @@
       <c r="T151" s="3"/>
       <c r="U151" s="3"/>
       <c r="V151" s="3"/>
+      <c r="W151" s="3"/>
     </row>
     <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="2"/>
@@ -4355,6 +4576,7 @@
       <c r="T152" s="3"/>
       <c r="U152" s="3"/>
       <c r="V152" s="3"/>
+      <c r="W152" s="3"/>
     </row>
     <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
@@ -4379,6 +4601,7 @@
       <c r="T153" s="3"/>
       <c r="U153" s="3"/>
       <c r="V153" s="3"/>
+      <c r="W153" s="3"/>
     </row>
     <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="2"/>
@@ -4403,6 +4626,7 @@
       <c r="T154" s="3"/>
       <c r="U154" s="3"/>
       <c r="V154" s="3"/>
+      <c r="W154" s="3"/>
     </row>
     <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="2"/>
@@ -4427,6 +4651,7 @@
       <c r="T155" s="3"/>
       <c r="U155" s="3"/>
       <c r="V155" s="3"/>
+      <c r="W155" s="3"/>
     </row>
     <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
@@ -4451,6 +4676,7 @@
       <c r="T156" s="3"/>
       <c r="U156" s="3"/>
       <c r="V156" s="3"/>
+      <c r="W156" s="3"/>
     </row>
     <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="2"/>
@@ -4475,6 +4701,7 @@
       <c r="T157" s="3"/>
       <c r="U157" s="3"/>
       <c r="V157" s="3"/>
+      <c r="W157" s="3"/>
     </row>
     <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="2"/>
@@ -4499,6 +4726,7 @@
       <c r="T158" s="3"/>
       <c r="U158" s="3"/>
       <c r="V158" s="3"/>
+      <c r="W158" s="3"/>
     </row>
     <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="2"/>
@@ -4523,6 +4751,7 @@
       <c r="T159" s="3"/>
       <c r="U159" s="3"/>
       <c r="V159" s="3"/>
+      <c r="W159" s="3"/>
     </row>
     <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="2"/>
@@ -4547,6 +4776,7 @@
       <c r="T160" s="3"/>
       <c r="U160" s="3"/>
       <c r="V160" s="3"/>
+      <c r="W160" s="3"/>
     </row>
     <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="2"/>
@@ -4571,6 +4801,7 @@
       <c r="T161" s="3"/>
       <c r="U161" s="3"/>
       <c r="V161" s="3"/>
+      <c r="W161" s="3"/>
     </row>
     <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="2"/>
@@ -4595,6 +4826,7 @@
       <c r="T162" s="3"/>
       <c r="U162" s="3"/>
       <c r="V162" s="3"/>
+      <c r="W162" s="3"/>
     </row>
     <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="2"/>
@@ -4619,6 +4851,7 @@
       <c r="T163" s="3"/>
       <c r="U163" s="3"/>
       <c r="V163" s="3"/>
+      <c r="W163" s="3"/>
     </row>
     <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="2"/>
@@ -4643,6 +4876,7 @@
       <c r="T164" s="3"/>
       <c r="U164" s="3"/>
       <c r="V164" s="3"/>
+      <c r="W164" s="3"/>
     </row>
     <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="2"/>
@@ -4667,6 +4901,7 @@
       <c r="T165" s="3"/>
       <c r="U165" s="3"/>
       <c r="V165" s="3"/>
+      <c r="W165" s="3"/>
     </row>
     <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="2"/>
@@ -4691,6 +4926,7 @@
       <c r="T166" s="3"/>
       <c r="U166" s="3"/>
       <c r="V166" s="3"/>
+      <c r="W166" s="3"/>
     </row>
     <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="2"/>
@@ -4715,6 +4951,7 @@
       <c r="T167" s="3"/>
       <c r="U167" s="3"/>
       <c r="V167" s="3"/>
+      <c r="W167" s="3"/>
     </row>
     <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="2"/>
@@ -4739,6 +4976,7 @@
       <c r="T168" s="3"/>
       <c r="U168" s="3"/>
       <c r="V168" s="3"/>
+      <c r="W168" s="3"/>
     </row>
     <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="2"/>
@@ -4763,6 +5001,7 @@
       <c r="T169" s="3"/>
       <c r="U169" s="3"/>
       <c r="V169" s="3"/>
+      <c r="W169" s="3"/>
     </row>
     <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="2"/>
@@ -4787,6 +5026,7 @@
       <c r="T170" s="3"/>
       <c r="U170" s="3"/>
       <c r="V170" s="3"/>
+      <c r="W170" s="3"/>
     </row>
     <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="2"/>
@@ -4811,6 +5051,7 @@
       <c r="T171" s="3"/>
       <c r="U171" s="3"/>
       <c r="V171" s="3"/>
+      <c r="W171" s="3"/>
     </row>
     <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="2"/>
@@ -4835,6 +5076,7 @@
       <c r="T172" s="3"/>
       <c r="U172" s="3"/>
       <c r="V172" s="3"/>
+      <c r="W172" s="3"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="2"/>
@@ -4859,6 +5101,7 @@
       <c r="T173" s="3"/>
       <c r="U173" s="3"/>
       <c r="V173" s="3"/>
+      <c r="W173" s="3"/>
     </row>
     <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
@@ -4883,6 +5126,7 @@
       <c r="T174" s="3"/>
       <c r="U174" s="3"/>
       <c r="V174" s="3"/>
+      <c r="W174" s="3"/>
     </row>
     <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
@@ -4907,6 +5151,7 @@
       <c r="T175" s="3"/>
       <c r="U175" s="3"/>
       <c r="V175" s="3"/>
+      <c r="W175" s="3"/>
     </row>
     <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
@@ -4931,6 +5176,7 @@
       <c r="T176" s="3"/>
       <c r="U176" s="3"/>
       <c r="V176" s="3"/>
+      <c r="W176" s="3"/>
     </row>
     <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
@@ -4955,6 +5201,7 @@
       <c r="T177" s="3"/>
       <c r="U177" s="3"/>
       <c r="V177" s="3"/>
+      <c r="W177" s="3"/>
     </row>
     <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
@@ -4979,6 +5226,7 @@
       <c r="T178" s="3"/>
       <c r="U178" s="3"/>
       <c r="V178" s="3"/>
+      <c r="W178" s="3"/>
     </row>
     <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="2"/>
@@ -5003,6 +5251,7 @@
       <c r="T179" s="3"/>
       <c r="U179" s="3"/>
       <c r="V179" s="3"/>
+      <c r="W179" s="3"/>
     </row>
     <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="2"/>
@@ -5027,6 +5276,7 @@
       <c r="T180" s="3"/>
       <c r="U180" s="3"/>
       <c r="V180" s="3"/>
+      <c r="W180" s="3"/>
     </row>
     <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="2"/>
@@ -5051,6 +5301,7 @@
       <c r="T181" s="3"/>
       <c r="U181" s="3"/>
       <c r="V181" s="3"/>
+      <c r="W181" s="3"/>
     </row>
     <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="2"/>
@@ -5075,6 +5326,7 @@
       <c r="T182" s="3"/>
       <c r="U182" s="3"/>
       <c r="V182" s="3"/>
+      <c r="W182" s="3"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
@@ -5099,6 +5351,7 @@
       <c r="T183" s="3"/>
       <c r="U183" s="3"/>
       <c r="V183" s="3"/>
+      <c r="W183" s="3"/>
     </row>
     <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
@@ -5123,6 +5376,7 @@
       <c r="T184" s="3"/>
       <c r="U184" s="3"/>
       <c r="V184" s="3"/>
+      <c r="W184" s="3"/>
     </row>
     <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
@@ -5147,6 +5401,7 @@
       <c r="T185" s="3"/>
       <c r="U185" s="3"/>
       <c r="V185" s="3"/>
+      <c r="W185" s="3"/>
     </row>
     <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="2"/>
@@ -5171,6 +5426,7 @@
       <c r="T186" s="3"/>
       <c r="U186" s="3"/>
       <c r="V186" s="3"/>
+      <c r="W186" s="3"/>
     </row>
     <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
@@ -5195,6 +5451,7 @@
       <c r="T187" s="3"/>
       <c r="U187" s="3"/>
       <c r="V187" s="3"/>
+      <c r="W187" s="3"/>
     </row>
     <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
@@ -5219,6 +5476,7 @@
       <c r="T188" s="3"/>
       <c r="U188" s="3"/>
       <c r="V188" s="3"/>
+      <c r="W188" s="3"/>
     </row>
     <row r="189" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
@@ -5243,6 +5501,7 @@
       <c r="T189" s="3"/>
       <c r="U189" s="3"/>
       <c r="V189" s="3"/>
+      <c r="W189" s="3"/>
     </row>
     <row r="190" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="2"/>
@@ -5267,6 +5526,7 @@
       <c r="T190" s="3"/>
       <c r="U190" s="3"/>
       <c r="V190" s="3"/>
+      <c r="W190" s="3"/>
     </row>
     <row r="191" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="2"/>
@@ -5291,6 +5551,7 @@
       <c r="T191" s="3"/>
       <c r="U191" s="3"/>
       <c r="V191" s="3"/>
+      <c r="W191" s="3"/>
     </row>
     <row r="192" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="2"/>
@@ -5315,6 +5576,7 @@
       <c r="T192" s="3"/>
       <c r="U192" s="3"/>
       <c r="V192" s="3"/>
+      <c r="W192" s="3"/>
     </row>
     <row r="193" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="2"/>
@@ -5339,6 +5601,7 @@
       <c r="T193" s="3"/>
       <c r="U193" s="3"/>
       <c r="V193" s="3"/>
+      <c r="W193" s="3"/>
     </row>
     <row r="194" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
@@ -5363,6 +5626,7 @@
       <c r="T194" s="3"/>
       <c r="U194" s="3"/>
       <c r="V194" s="3"/>
+      <c r="W194" s="3"/>
     </row>
     <row r="195" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
@@ -5387,6 +5651,7 @@
       <c r="T195" s="3"/>
       <c r="U195" s="3"/>
       <c r="V195" s="3"/>
+      <c r="W195" s="3"/>
     </row>
     <row r="196" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
@@ -5411,6 +5676,7 @@
       <c r="T196" s="3"/>
       <c r="U196" s="3"/>
       <c r="V196" s="3"/>
+      <c r="W196" s="3"/>
     </row>
     <row r="197" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
@@ -5435,6 +5701,7 @@
       <c r="T197" s="3"/>
       <c r="U197" s="3"/>
       <c r="V197" s="3"/>
+      <c r="W197" s="3"/>
     </row>
     <row r="198" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
@@ -5459,6 +5726,7 @@
       <c r="T198" s="3"/>
       <c r="U198" s="3"/>
       <c r="V198" s="3"/>
+      <c r="W198" s="3"/>
     </row>
     <row r="199" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
@@ -5483,6 +5751,7 @@
       <c r="T199" s="3"/>
       <c r="U199" s="3"/>
       <c r="V199" s="3"/>
+      <c r="W199" s="3"/>
     </row>
     <row r="200" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="2"/>
@@ -5507,6 +5776,7 @@
       <c r="T200" s="3"/>
       <c r="U200" s="3"/>
       <c r="V200" s="3"/>
+      <c r="W200" s="3"/>
     </row>
     <row r="201" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="2"/>
@@ -5531,6 +5801,7 @@
       <c r="T201" s="3"/>
       <c r="U201" s="3"/>
       <c r="V201" s="3"/>
+      <c r="W201" s="3"/>
     </row>
     <row r="202" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
@@ -5555,6 +5826,7 @@
       <c r="T202" s="3"/>
       <c r="U202" s="3"/>
       <c r="V202" s="3"/>
+      <c r="W202" s="3"/>
     </row>
     <row r="203" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
@@ -5579,6 +5851,7 @@
       <c r="T203" s="3"/>
       <c r="U203" s="3"/>
       <c r="V203" s="3"/>
+      <c r="W203" s="3"/>
     </row>
     <row r="204" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="2"/>
@@ -5603,6 +5876,7 @@
       <c r="T204" s="3"/>
       <c r="U204" s="3"/>
       <c r="V204" s="3"/>
+      <c r="W204" s="3"/>
     </row>
     <row r="205" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
@@ -5627,6 +5901,7 @@
       <c r="T205" s="3"/>
       <c r="U205" s="3"/>
       <c r="V205" s="3"/>
+      <c r="W205" s="3"/>
     </row>
     <row r="206" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
@@ -5651,6 +5926,7 @@
       <c r="T206" s="3"/>
       <c r="U206" s="3"/>
       <c r="V206" s="3"/>
+      <c r="W206" s="3"/>
     </row>
     <row r="207" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="2"/>
@@ -5675,6 +5951,7 @@
       <c r="T207" s="3"/>
       <c r="U207" s="3"/>
       <c r="V207" s="3"/>
+      <c r="W207" s="3"/>
     </row>
     <row r="208" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="2"/>
@@ -5699,6 +5976,7 @@
       <c r="T208" s="3"/>
       <c r="U208" s="3"/>
       <c r="V208" s="3"/>
+      <c r="W208" s="3"/>
     </row>
     <row r="209" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="2"/>
@@ -5723,6 +6001,7 @@
       <c r="T209" s="3"/>
       <c r="U209" s="3"/>
       <c r="V209" s="3"/>
+      <c r="W209" s="3"/>
     </row>
     <row r="210" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="2"/>
@@ -5747,6 +6026,7 @@
       <c r="T210" s="3"/>
       <c r="U210" s="3"/>
       <c r="V210" s="3"/>
+      <c r="W210" s="3"/>
     </row>
     <row r="211" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
@@ -5771,6 +6051,7 @@
       <c r="T211" s="3"/>
       <c r="U211" s="3"/>
       <c r="V211" s="3"/>
+      <c r="W211" s="3"/>
     </row>
     <row r="212" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="2"/>
@@ -5795,6 +6076,7 @@
       <c r="T212" s="3"/>
       <c r="U212" s="3"/>
       <c r="V212" s="3"/>
+      <c r="W212" s="3"/>
     </row>
     <row r="213" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="2"/>
@@ -5819,6 +6101,7 @@
       <c r="T213" s="3"/>
       <c r="U213" s="3"/>
       <c r="V213" s="3"/>
+      <c r="W213" s="3"/>
     </row>
     <row r="214" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="2"/>
@@ -5843,6 +6126,7 @@
       <c r="T214" s="3"/>
       <c r="U214" s="3"/>
       <c r="V214" s="3"/>
+      <c r="W214" s="3"/>
     </row>
     <row r="215" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
@@ -5867,6 +6151,7 @@
       <c r="T215" s="3"/>
       <c r="U215" s="3"/>
       <c r="V215" s="3"/>
+      <c r="W215" s="3"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="2"/>
@@ -5891,6 +6176,7 @@
       <c r="T216" s="3"/>
       <c r="U216" s="3"/>
       <c r="V216" s="3"/>
+      <c r="W216" s="3"/>
     </row>
     <row r="217" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="2"/>
@@ -5915,6 +6201,7 @@
       <c r="T217" s="3"/>
       <c r="U217" s="3"/>
       <c r="V217" s="3"/>
+      <c r="W217" s="3"/>
     </row>
     <row r="218" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
@@ -5939,6 +6226,7 @@
       <c r="T218" s="3"/>
       <c r="U218" s="3"/>
       <c r="V218" s="3"/>
+      <c r="W218" s="3"/>
     </row>
     <row r="219" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
@@ -5963,6 +6251,7 @@
       <c r="T219" s="3"/>
       <c r="U219" s="3"/>
       <c r="V219" s="3"/>
+      <c r="W219" s="3"/>
     </row>
     <row r="220" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="2"/>
@@ -5987,6 +6276,7 @@
       <c r="T220" s="3"/>
       <c r="U220" s="3"/>
       <c r="V220" s="3"/>
+      <c r="W220" s="3"/>
     </row>
     <row r="221" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="2"/>
@@ -6011,6 +6301,7 @@
       <c r="T221" s="3"/>
       <c r="U221" s="3"/>
       <c r="V221" s="3"/>
+      <c r="W221" s="3"/>
     </row>
     <row r="222" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="2"/>
@@ -6035,6 +6326,7 @@
       <c r="T222" s="3"/>
       <c r="U222" s="3"/>
       <c r="V222" s="3"/>
+      <c r="W222" s="3"/>
     </row>
     <row r="223" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="2"/>
@@ -6059,6 +6351,7 @@
       <c r="T223" s="3"/>
       <c r="U223" s="3"/>
       <c r="V223" s="3"/>
+      <c r="W223" s="3"/>
     </row>
     <row r="224" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
@@ -6083,6 +6376,7 @@
       <c r="T224" s="3"/>
       <c r="U224" s="3"/>
       <c r="V224" s="3"/>
+      <c r="W224" s="3"/>
     </row>
     <row r="225" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
@@ -6107,6 +6401,7 @@
       <c r="T225" s="3"/>
       <c r="U225" s="3"/>
       <c r="V225" s="3"/>
+      <c r="W225" s="3"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
@@ -6131,6 +6426,7 @@
       <c r="T226" s="3"/>
       <c r="U226" s="3"/>
       <c r="V226" s="3"/>
+      <c r="W226" s="3"/>
     </row>
     <row r="227" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
@@ -6155,6 +6451,7 @@
       <c r="T227" s="3"/>
       <c r="U227" s="3"/>
       <c r="V227" s="3"/>
+      <c r="W227" s="3"/>
     </row>
     <row r="228" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="2"/>
@@ -6179,6 +6476,7 @@
       <c r="T228" s="3"/>
       <c r="U228" s="3"/>
       <c r="V228" s="3"/>
+      <c r="W228" s="3"/>
     </row>
     <row r="229" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="2"/>
@@ -6203,6 +6501,7 @@
       <c r="T229" s="3"/>
       <c r="U229" s="3"/>
       <c r="V229" s="3"/>
+      <c r="W229" s="3"/>
     </row>
     <row r="230" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="2"/>
@@ -6227,6 +6526,7 @@
       <c r="T230" s="3"/>
       <c r="U230" s="3"/>
       <c r="V230" s="3"/>
+      <c r="W230" s="3"/>
     </row>
     <row r="231" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
@@ -6251,6 +6551,7 @@
       <c r="T231" s="3"/>
       <c r="U231" s="3"/>
       <c r="V231" s="3"/>
+      <c r="W231" s="3"/>
     </row>
     <row r="232" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
@@ -6275,6 +6576,7 @@
       <c r="T232" s="3"/>
       <c r="U232" s="3"/>
       <c r="V232" s="3"/>
+      <c r="W232" s="3"/>
     </row>
     <row r="233" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
@@ -6299,6 +6601,7 @@
       <c r="T233" s="3"/>
       <c r="U233" s="3"/>
       <c r="V233" s="3"/>
+      <c r="W233" s="3"/>
     </row>
     <row r="234" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
@@ -6323,6 +6626,7 @@
       <c r="T234" s="3"/>
       <c r="U234" s="3"/>
       <c r="V234" s="3"/>
+      <c r="W234" s="3"/>
     </row>
     <row r="235" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
@@ -6347,6 +6651,7 @@
       <c r="T235" s="3"/>
       <c r="U235" s="3"/>
       <c r="V235" s="3"/>
+      <c r="W235" s="3"/>
     </row>
     <row r="236" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
@@ -6371,6 +6676,7 @@
       <c r="T236" s="3"/>
       <c r="U236" s="3"/>
       <c r="V236" s="3"/>
+      <c r="W236" s="3"/>
     </row>
     <row r="237" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="2"/>
@@ -6395,6 +6701,7 @@
       <c r="T237" s="3"/>
       <c r="U237" s="3"/>
       <c r="V237" s="3"/>
+      <c r="W237" s="3"/>
     </row>
     <row r="238" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
@@ -6419,6 +6726,7 @@
       <c r="T238" s="3"/>
       <c r="U238" s="3"/>
       <c r="V238" s="3"/>
+      <c r="W238" s="3"/>
     </row>
     <row r="239" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
@@ -6443,6 +6751,7 @@
       <c r="T239" s="3"/>
       <c r="U239" s="3"/>
       <c r="V239" s="3"/>
+      <c r="W239" s="3"/>
     </row>
     <row r="240" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="2"/>
@@ -6467,6 +6776,7 @@
       <c r="T240" s="3"/>
       <c r="U240" s="3"/>
       <c r="V240" s="3"/>
+      <c r="W240" s="3"/>
     </row>
     <row r="241" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="2"/>
@@ -6491,6 +6801,7 @@
       <c r="T241" s="3"/>
       <c r="U241" s="3"/>
       <c r="V241" s="3"/>
+      <c r="W241" s="3"/>
     </row>
     <row r="242" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
@@ -6515,6 +6826,7 @@
       <c r="T242" s="3"/>
       <c r="U242" s="3"/>
       <c r="V242" s="3"/>
+      <c r="W242" s="3"/>
     </row>
     <row r="243" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="2"/>
@@ -6539,6 +6851,7 @@
       <c r="T243" s="3"/>
       <c r="U243" s="3"/>
       <c r="V243" s="3"/>
+      <c r="W243" s="3"/>
     </row>
     <row r="244" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
@@ -6563,6 +6876,7 @@
       <c r="T244" s="3"/>
       <c r="U244" s="3"/>
       <c r="V244" s="3"/>
+      <c r="W244" s="3"/>
     </row>
     <row r="245" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
@@ -6587,6 +6901,7 @@
       <c r="T245" s="3"/>
       <c r="U245" s="3"/>
       <c r="V245" s="3"/>
+      <c r="W245" s="3"/>
     </row>
     <row r="246" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="2"/>
@@ -6611,6 +6926,7 @@
       <c r="T246" s="3"/>
       <c r="U246" s="3"/>
       <c r="V246" s="3"/>
+      <c r="W246" s="3"/>
     </row>
     <row r="247" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
@@ -6635,6 +6951,7 @@
       <c r="T247" s="3"/>
       <c r="U247" s="3"/>
       <c r="V247" s="3"/>
+      <c r="W247" s="3"/>
     </row>
     <row r="248" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
@@ -6659,6 +6976,7 @@
       <c r="T248" s="3"/>
       <c r="U248" s="3"/>
       <c r="V248" s="3"/>
+      <c r="W248" s="3"/>
     </row>
     <row r="249" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
@@ -6683,6 +7001,7 @@
       <c r="T249" s="3"/>
       <c r="U249" s="3"/>
       <c r="V249" s="3"/>
+      <c r="W249" s="3"/>
     </row>
     <row r="250" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="2"/>
@@ -6707,6 +7026,7 @@
       <c r="T250" s="3"/>
       <c r="U250" s="3"/>
       <c r="V250" s="3"/>
+      <c r="W250" s="3"/>
     </row>
     <row r="251" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="2"/>
@@ -6731,6 +7051,7 @@
       <c r="T251" s="3"/>
       <c r="U251" s="3"/>
       <c r="V251" s="3"/>
+      <c r="W251" s="3"/>
     </row>
     <row r="252" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
@@ -6755,6 +7076,7 @@
       <c r="T252" s="3"/>
       <c r="U252" s="3"/>
       <c r="V252" s="3"/>
+      <c r="W252" s="3"/>
     </row>
     <row r="253" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
@@ -6779,6 +7101,7 @@
       <c r="T253" s="3"/>
       <c r="U253" s="3"/>
       <c r="V253" s="3"/>
+      <c r="W253" s="3"/>
     </row>
     <row r="254" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
@@ -6803,6 +7126,7 @@
       <c r="T254" s="3"/>
       <c r="U254" s="3"/>
       <c r="V254" s="3"/>
+      <c r="W254" s="3"/>
     </row>
     <row r="255" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
@@ -6827,6 +7151,7 @@
       <c r="T255" s="3"/>
       <c r="U255" s="3"/>
       <c r="V255" s="3"/>
+      <c r="W255" s="3"/>
     </row>
     <row r="256" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
@@ -6851,6 +7176,7 @@
       <c r="T256" s="3"/>
       <c r="U256" s="3"/>
       <c r="V256" s="3"/>
+      <c r="W256" s="3"/>
     </row>
     <row r="257" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
@@ -6875,6 +7201,7 @@
       <c r="T257" s="3"/>
       <c r="U257" s="3"/>
       <c r="V257" s="3"/>
+      <c r="W257" s="3"/>
     </row>
     <row r="258" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
@@ -6899,6 +7226,7 @@
       <c r="T258" s="3"/>
       <c r="U258" s="3"/>
       <c r="V258" s="3"/>
+      <c r="W258" s="3"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
@@ -6923,6 +7251,7 @@
       <c r="T259" s="3"/>
       <c r="U259" s="3"/>
       <c r="V259" s="3"/>
+      <c r="W259" s="3"/>
     </row>
     <row r="260" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
@@ -6947,6 +7276,7 @@
       <c r="T260" s="3"/>
       <c r="U260" s="3"/>
       <c r="V260" s="3"/>
+      <c r="W260" s="3"/>
     </row>
     <row r="261" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
@@ -6971,6 +7301,7 @@
       <c r="T261" s="3"/>
       <c r="U261" s="3"/>
       <c r="V261" s="3"/>
+      <c r="W261" s="3"/>
     </row>
     <row r="262" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="2"/>
@@ -6995,6 +7326,7 @@
       <c r="T262" s="3"/>
       <c r="U262" s="3"/>
       <c r="V262" s="3"/>
+      <c r="W262" s="3"/>
     </row>
     <row r="263" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="2"/>
@@ -7019,6 +7351,7 @@
       <c r="T263" s="3"/>
       <c r="U263" s="3"/>
       <c r="V263" s="3"/>
+      <c r="W263" s="3"/>
     </row>
     <row r="264" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="2"/>
@@ -7043,6 +7376,7 @@
       <c r="T264" s="3"/>
       <c r="U264" s="3"/>
       <c r="V264" s="3"/>
+      <c r="W264" s="3"/>
     </row>
     <row r="265" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
@@ -7067,6 +7401,7 @@
       <c r="T265" s="3"/>
       <c r="U265" s="3"/>
       <c r="V265" s="3"/>
+      <c r="W265" s="3"/>
     </row>
     <row r="266" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
@@ -7091,6 +7426,7 @@
       <c r="T266" s="3"/>
       <c r="U266" s="3"/>
       <c r="V266" s="3"/>
+      <c r="W266" s="3"/>
     </row>
     <row r="267" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
@@ -7115,6 +7451,7 @@
       <c r="T267" s="3"/>
       <c r="U267" s="3"/>
       <c r="V267" s="3"/>
+      <c r="W267" s="3"/>
     </row>
     <row r="268" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
@@ -7139,6 +7476,7 @@
       <c r="T268" s="3"/>
       <c r="U268" s="3"/>
       <c r="V268" s="3"/>
+      <c r="W268" s="3"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
@@ -7163,6 +7501,7 @@
       <c r="T269" s="3"/>
       <c r="U269" s="3"/>
       <c r="V269" s="3"/>
+      <c r="W269" s="3"/>
     </row>
     <row r="270" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
@@ -7187,6 +7526,7 @@
       <c r="T270" s="3"/>
       <c r="U270" s="3"/>
       <c r="V270" s="3"/>
+      <c r="W270" s="3"/>
     </row>
     <row r="271" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="2"/>
@@ -7211,6 +7551,7 @@
       <c r="T271" s="3"/>
       <c r="U271" s="3"/>
       <c r="V271" s="3"/>
+      <c r="W271" s="3"/>
     </row>
     <row r="272" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="2"/>
@@ -7235,6 +7576,7 @@
       <c r="T272" s="3"/>
       <c r="U272" s="3"/>
       <c r="V272" s="3"/>
+      <c r="W272" s="3"/>
     </row>
     <row r="273" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
@@ -7259,6 +7601,7 @@
       <c r="T273" s="3"/>
       <c r="U273" s="3"/>
       <c r="V273" s="3"/>
+      <c r="W273" s="3"/>
     </row>
     <row r="274" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
@@ -7283,6 +7626,7 @@
       <c r="T274" s="3"/>
       <c r="U274" s="3"/>
       <c r="V274" s="3"/>
+      <c r="W274" s="3"/>
     </row>
     <row r="275" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
@@ -7307,6 +7651,7 @@
       <c r="T275" s="3"/>
       <c r="U275" s="3"/>
       <c r="V275" s="3"/>
+      <c r="W275" s="3"/>
     </row>
     <row r="276" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
@@ -7331,6 +7676,7 @@
       <c r="T276" s="3"/>
       <c r="U276" s="3"/>
       <c r="V276" s="3"/>
+      <c r="W276" s="3"/>
     </row>
     <row r="277" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
@@ -7355,6 +7701,7 @@
       <c r="T277" s="3"/>
       <c r="U277" s="3"/>
       <c r="V277" s="3"/>
+      <c r="W277" s="3"/>
     </row>
     <row r="278" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
@@ -7379,6 +7726,7 @@
       <c r="T278" s="3"/>
       <c r="U278" s="3"/>
       <c r="V278" s="3"/>
+      <c r="W278" s="3"/>
     </row>
     <row r="279" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
@@ -7403,6 +7751,7 @@
       <c r="T279" s="3"/>
       <c r="U279" s="3"/>
       <c r="V279" s="3"/>
+      <c r="W279" s="3"/>
     </row>
     <row r="280" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
@@ -7427,6 +7776,7 @@
       <c r="T280" s="3"/>
       <c r="U280" s="3"/>
       <c r="V280" s="3"/>
+      <c r="W280" s="3"/>
     </row>
     <row r="281" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
@@ -7451,6 +7801,7 @@
       <c r="T281" s="3"/>
       <c r="U281" s="3"/>
       <c r="V281" s="3"/>
+      <c r="W281" s="3"/>
     </row>
     <row r="282" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
@@ -7475,6 +7826,7 @@
       <c r="T282" s="3"/>
       <c r="U282" s="3"/>
       <c r="V282" s="3"/>
+      <c r="W282" s="3"/>
     </row>
     <row r="283" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
@@ -7499,6 +7851,7 @@
       <c r="T283" s="3"/>
       <c r="U283" s="3"/>
       <c r="V283" s="3"/>
+      <c r="W283" s="3"/>
     </row>
     <row r="284" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
@@ -7523,6 +7876,7 @@
       <c r="T284" s="3"/>
       <c r="U284" s="3"/>
       <c r="V284" s="3"/>
+      <c r="W284" s="3"/>
     </row>
     <row r="285" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
@@ -7547,6 +7901,7 @@
       <c r="T285" s="3"/>
       <c r="U285" s="3"/>
       <c r="V285" s="3"/>
+      <c r="W285" s="3"/>
     </row>
     <row r="286" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="2"/>
@@ -7571,6 +7926,7 @@
       <c r="T286" s="3"/>
       <c r="U286" s="3"/>
       <c r="V286" s="3"/>
+      <c r="W286" s="3"/>
     </row>
     <row r="287" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="2"/>
@@ -7595,6 +7951,7 @@
       <c r="T287" s="3"/>
       <c r="U287" s="3"/>
       <c r="V287" s="3"/>
+      <c r="W287" s="3"/>
     </row>
     <row r="288" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
@@ -7619,6 +7976,7 @@
       <c r="T288" s="3"/>
       <c r="U288" s="3"/>
       <c r="V288" s="3"/>
+      <c r="W288" s="3"/>
     </row>
     <row r="289" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
@@ -7643,6 +8001,7 @@
       <c r="T289" s="3"/>
       <c r="U289" s="3"/>
       <c r="V289" s="3"/>
+      <c r="W289" s="3"/>
     </row>
     <row r="290" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
@@ -7667,6 +8026,7 @@
       <c r="T290" s="3"/>
       <c r="U290" s="3"/>
       <c r="V290" s="3"/>
+      <c r="W290" s="3"/>
     </row>
     <row r="291" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
@@ -7691,6 +8051,7 @@
       <c r="T291" s="3"/>
       <c r="U291" s="3"/>
       <c r="V291" s="3"/>
+      <c r="W291" s="3"/>
     </row>
     <row r="292" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
@@ -7715,6 +8076,7 @@
       <c r="T292" s="3"/>
       <c r="U292" s="3"/>
       <c r="V292" s="3"/>
+      <c r="W292" s="3"/>
     </row>
     <row r="293" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
@@ -7739,6 +8101,7 @@
       <c r="T293" s="3"/>
       <c r="U293" s="3"/>
       <c r="V293" s="3"/>
+      <c r="W293" s="3"/>
     </row>
     <row r="294" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
@@ -7763,6 +8126,7 @@
       <c r="T294" s="3"/>
       <c r="U294" s="3"/>
       <c r="V294" s="3"/>
+      <c r="W294" s="3"/>
     </row>
     <row r="295" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
@@ -7787,6 +8151,7 @@
       <c r="T295" s="3"/>
       <c r="U295" s="3"/>
       <c r="V295" s="3"/>
+      <c r="W295" s="3"/>
     </row>
     <row r="296" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="2"/>
@@ -7811,6 +8176,7 @@
       <c r="T296" s="3"/>
       <c r="U296" s="3"/>
       <c r="V296" s="3"/>
+      <c r="W296" s="3"/>
     </row>
     <row r="297" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
@@ -7835,6 +8201,7 @@
       <c r="T297" s="3"/>
       <c r="U297" s="3"/>
       <c r="V297" s="3"/>
+      <c r="W297" s="3"/>
     </row>
     <row r="298" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="2"/>
@@ -7859,6 +8226,7 @@
       <c r="T298" s="3"/>
       <c r="U298" s="3"/>
       <c r="V298" s="3"/>
+      <c r="W298" s="3"/>
     </row>
     <row r="299" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
@@ -7883,6 +8251,7 @@
       <c r="T299" s="3"/>
       <c r="U299" s="3"/>
       <c r="V299" s="3"/>
+      <c r="W299" s="3"/>
     </row>
     <row r="300" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="2"/>
@@ -7907,6 +8276,7 @@
       <c r="T300" s="3"/>
       <c r="U300" s="3"/>
       <c r="V300" s="3"/>
+      <c r="W300" s="3"/>
     </row>
     <row r="301" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
@@ -7931,6 +8301,7 @@
       <c r="T301" s="3"/>
       <c r="U301" s="3"/>
       <c r="V301" s="3"/>
+      <c r="W301" s="3"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
@@ -7955,6 +8326,7 @@
       <c r="T302" s="3"/>
       <c r="U302" s="3"/>
       <c r="V302" s="3"/>
+      <c r="W302" s="3"/>
     </row>
     <row r="303" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
@@ -7979,6 +8351,7 @@
       <c r="T303" s="3"/>
       <c r="U303" s="3"/>
       <c r="V303" s="3"/>
+      <c r="W303" s="3"/>
     </row>
     <row r="304" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
@@ -8003,6 +8376,7 @@
       <c r="T304" s="3"/>
       <c r="U304" s="3"/>
       <c r="V304" s="3"/>
+      <c r="W304" s="3"/>
     </row>
     <row r="305" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="2"/>
@@ -8027,6 +8401,7 @@
       <c r="T305" s="3"/>
       <c r="U305" s="3"/>
       <c r="V305" s="3"/>
+      <c r="W305" s="3"/>
     </row>
     <row r="306" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
@@ -8051,6 +8426,7 @@
       <c r="T306" s="3"/>
       <c r="U306" s="3"/>
       <c r="V306" s="3"/>
+      <c r="W306" s="3"/>
     </row>
     <row r="307" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="2"/>
@@ -8075,6 +8451,7 @@
       <c r="T307" s="3"/>
       <c r="U307" s="3"/>
       <c r="V307" s="3"/>
+      <c r="W307" s="3"/>
     </row>
     <row r="308" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
@@ -8099,6 +8476,7 @@
       <c r="T308" s="3"/>
       <c r="U308" s="3"/>
       <c r="V308" s="3"/>
+      <c r="W308" s="3"/>
     </row>
     <row r="309" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
@@ -8123,6 +8501,7 @@
       <c r="T309" s="3"/>
       <c r="U309" s="3"/>
       <c r="V309" s="3"/>
+      <c r="W309" s="3"/>
     </row>
     <row r="310" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="2"/>
@@ -8147,6 +8526,7 @@
       <c r="T310" s="3"/>
       <c r="U310" s="3"/>
       <c r="V310" s="3"/>
+      <c r="W310" s="3"/>
     </row>
     <row r="311" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
@@ -8171,6 +8551,7 @@
       <c r="T311" s="3"/>
       <c r="U311" s="3"/>
       <c r="V311" s="3"/>
+      <c r="W311" s="3"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="2"/>
@@ -8195,6 +8576,7 @@
       <c r="T312" s="3"/>
       <c r="U312" s="3"/>
       <c r="V312" s="3"/>
+      <c r="W312" s="3"/>
     </row>
     <row r="313" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="2"/>
@@ -8219,6 +8601,7 @@
       <c r="T313" s="3"/>
       <c r="U313" s="3"/>
       <c r="V313" s="3"/>
+      <c r="W313" s="3"/>
     </row>
     <row r="314" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
@@ -8243,6 +8626,7 @@
       <c r="T314" s="3"/>
       <c r="U314" s="3"/>
       <c r="V314" s="3"/>
+      <c r="W314" s="3"/>
     </row>
     <row r="315" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
@@ -8267,6 +8651,7 @@
       <c r="T315" s="3"/>
       <c r="U315" s="3"/>
       <c r="V315" s="3"/>
+      <c r="W315" s="3"/>
     </row>
     <row r="316" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="2"/>
@@ -8291,6 +8676,7 @@
       <c r="T316" s="3"/>
       <c r="U316" s="3"/>
       <c r="V316" s="3"/>
+      <c r="W316" s="3"/>
     </row>
     <row r="317" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
@@ -8315,6 +8701,7 @@
       <c r="T317" s="3"/>
       <c r="U317" s="3"/>
       <c r="V317" s="3"/>
+      <c r="W317" s="3"/>
     </row>
     <row r="318" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
@@ -8339,6 +8726,7 @@
       <c r="T318" s="3"/>
       <c r="U318" s="3"/>
       <c r="V318" s="3"/>
+      <c r="W318" s="3"/>
     </row>
     <row r="319" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="2"/>
@@ -8363,6 +8751,7 @@
       <c r="T319" s="3"/>
       <c r="U319" s="3"/>
       <c r="V319" s="3"/>
+      <c r="W319" s="3"/>
     </row>
     <row r="320" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="2"/>
@@ -8387,6 +8776,7 @@
       <c r="T320" s="3"/>
       <c r="U320" s="3"/>
       <c r="V320" s="3"/>
+      <c r="W320" s="3"/>
     </row>
     <row r="321" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="2"/>
@@ -8411,6 +8801,7 @@
       <c r="T321" s="3"/>
       <c r="U321" s="3"/>
       <c r="V321" s="3"/>
+      <c r="W321" s="3"/>
     </row>
     <row r="322" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="2"/>
@@ -8435,6 +8826,7 @@
       <c r="T322" s="3"/>
       <c r="U322" s="3"/>
       <c r="V322" s="3"/>
+      <c r="W322" s="3"/>
     </row>
     <row r="323" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
@@ -8459,6 +8851,7 @@
       <c r="T323" s="3"/>
       <c r="U323" s="3"/>
       <c r="V323" s="3"/>
+      <c r="W323" s="3"/>
     </row>
     <row r="324" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="2"/>
@@ -8483,6 +8876,7 @@
       <c r="T324" s="3"/>
       <c r="U324" s="3"/>
       <c r="V324" s="3"/>
+      <c r="W324" s="3"/>
     </row>
     <row r="325" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="2"/>
@@ -8507,6 +8901,7 @@
       <c r="T325" s="3"/>
       <c r="U325" s="3"/>
       <c r="V325" s="3"/>
+      <c r="W325" s="3"/>
     </row>
     <row r="326" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="2"/>
@@ -8531,6 +8926,7 @@
       <c r="T326" s="3"/>
       <c r="U326" s="3"/>
       <c r="V326" s="3"/>
+      <c r="W326" s="3"/>
     </row>
     <row r="327" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
@@ -8555,6 +8951,7 @@
       <c r="T327" s="3"/>
       <c r="U327" s="3"/>
       <c r="V327" s="3"/>
+      <c r="W327" s="3"/>
     </row>
     <row r="328" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="2"/>
@@ -8579,6 +8976,7 @@
       <c r="T328" s="3"/>
       <c r="U328" s="3"/>
       <c r="V328" s="3"/>
+      <c r="W328" s="3"/>
     </row>
     <row r="329" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
@@ -8603,6 +9001,7 @@
       <c r="T329" s="3"/>
       <c r="U329" s="3"/>
       <c r="V329" s="3"/>
+      <c r="W329" s="3"/>
     </row>
     <row r="330" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
@@ -8627,6 +9026,7 @@
       <c r="T330" s="3"/>
       <c r="U330" s="3"/>
       <c r="V330" s="3"/>
+      <c r="W330" s="3"/>
     </row>
     <row r="331" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
@@ -8651,6 +9051,7 @@
       <c r="T331" s="3"/>
       <c r="U331" s="3"/>
       <c r="V331" s="3"/>
+      <c r="W331" s="3"/>
     </row>
     <row r="332" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
@@ -8675,6 +9076,7 @@
       <c r="T332" s="3"/>
       <c r="U332" s="3"/>
       <c r="V332" s="3"/>
+      <c r="W332" s="3"/>
     </row>
     <row r="333" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="2"/>
@@ -8699,6 +9101,7 @@
       <c r="T333" s="3"/>
       <c r="U333" s="3"/>
       <c r="V333" s="3"/>
+      <c r="W333" s="3"/>
     </row>
     <row r="334" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="2"/>
@@ -8723,6 +9126,7 @@
       <c r="T334" s="3"/>
       <c r="U334" s="3"/>
       <c r="V334" s="3"/>
+      <c r="W334" s="3"/>
     </row>
     <row r="335" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
@@ -8747,6 +9151,7 @@
       <c r="T335" s="3"/>
       <c r="U335" s="3"/>
       <c r="V335" s="3"/>
+      <c r="W335" s="3"/>
     </row>
     <row r="336" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="2"/>
@@ -8771,6 +9176,7 @@
       <c r="T336" s="3"/>
       <c r="U336" s="3"/>
       <c r="V336" s="3"/>
+      <c r="W336" s="3"/>
     </row>
     <row r="337" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="2"/>
@@ -8795,6 +9201,7 @@
       <c r="T337" s="3"/>
       <c r="U337" s="3"/>
       <c r="V337" s="3"/>
+      <c r="W337" s="3"/>
     </row>
     <row r="338" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
@@ -8819,6 +9226,7 @@
       <c r="T338" s="3"/>
       <c r="U338" s="3"/>
       <c r="V338" s="3"/>
+      <c r="W338" s="3"/>
     </row>
     <row r="339" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
@@ -8843,6 +9251,7 @@
       <c r="T339" s="3"/>
       <c r="U339" s="3"/>
       <c r="V339" s="3"/>
+      <c r="W339" s="3"/>
     </row>
     <row r="340" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
@@ -8867,6 +9276,7 @@
       <c r="T340" s="3"/>
       <c r="U340" s="3"/>
       <c r="V340" s="3"/>
+      <c r="W340" s="3"/>
     </row>
     <row r="341" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
@@ -8891,6 +9301,7 @@
       <c r="T341" s="3"/>
       <c r="U341" s="3"/>
       <c r="V341" s="3"/>
+      <c r="W341" s="3"/>
     </row>
     <row r="342" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
@@ -8915,6 +9326,7 @@
       <c r="T342" s="3"/>
       <c r="U342" s="3"/>
       <c r="V342" s="3"/>
+      <c r="W342" s="3"/>
     </row>
     <row r="343" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
@@ -8939,6 +9351,7 @@
       <c r="T343" s="3"/>
       <c r="U343" s="3"/>
       <c r="V343" s="3"/>
+      <c r="W343" s="3"/>
     </row>
     <row r="344" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
@@ -8963,6 +9376,7 @@
       <c r="T344" s="3"/>
       <c r="U344" s="3"/>
       <c r="V344" s="3"/>
+      <c r="W344" s="3"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="2"/>
@@ -8987,6 +9401,7 @@
       <c r="T345" s="3"/>
       <c r="U345" s="3"/>
       <c r="V345" s="3"/>
+      <c r="W345" s="3"/>
     </row>
     <row r="346" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="2"/>
@@ -9011,6 +9426,7 @@
       <c r="T346" s="3"/>
       <c r="U346" s="3"/>
       <c r="V346" s="3"/>
+      <c r="W346" s="3"/>
     </row>
     <row r="347" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="2"/>
@@ -9035,6 +9451,7 @@
       <c r="T347" s="3"/>
       <c r="U347" s="3"/>
       <c r="V347" s="3"/>
+      <c r="W347" s="3"/>
     </row>
     <row r="348" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="2"/>
@@ -9059,6 +9476,7 @@
       <c r="T348" s="3"/>
       <c r="U348" s="3"/>
       <c r="V348" s="3"/>
+      <c r="W348" s="3"/>
     </row>
     <row r="349" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="2"/>
@@ -9083,6 +9501,7 @@
       <c r="T349" s="3"/>
       <c r="U349" s="3"/>
       <c r="V349" s="3"/>
+      <c r="W349" s="3"/>
     </row>
     <row r="350" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="2"/>
@@ -9107,6 +9526,7 @@
       <c r="T350" s="3"/>
       <c r="U350" s="3"/>
       <c r="V350" s="3"/>
+      <c r="W350" s="3"/>
     </row>
     <row r="351" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
@@ -9131,6 +9551,7 @@
       <c r="T351" s="3"/>
       <c r="U351" s="3"/>
       <c r="V351" s="3"/>
+      <c r="W351" s="3"/>
     </row>
     <row r="352" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
@@ -9155,6 +9576,7 @@
       <c r="T352" s="3"/>
       <c r="U352" s="3"/>
       <c r="V352" s="3"/>
+      <c r="W352" s="3"/>
     </row>
     <row r="353" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="2"/>
@@ -9179,6 +9601,7 @@
       <c r="T353" s="3"/>
       <c r="U353" s="3"/>
       <c r="V353" s="3"/>
+      <c r="W353" s="3"/>
     </row>
     <row r="354" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="2"/>
@@ -9203,6 +9626,7 @@
       <c r="T354" s="3"/>
       <c r="U354" s="3"/>
       <c r="V354" s="3"/>
+      <c r="W354" s="3"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="2"/>
@@ -9227,6 +9651,7 @@
       <c r="T355" s="3"/>
       <c r="U355" s="3"/>
       <c r="V355" s="3"/>
+      <c r="W355" s="3"/>
     </row>
     <row r="356" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="2"/>
@@ -9251,6 +9676,7 @@
       <c r="T356" s="3"/>
       <c r="U356" s="3"/>
       <c r="V356" s="3"/>
+      <c r="W356" s="3"/>
     </row>
     <row r="357" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="2"/>
@@ -9275,6 +9701,7 @@
       <c r="T357" s="3"/>
       <c r="U357" s="3"/>
       <c r="V357" s="3"/>
+      <c r="W357" s="3"/>
     </row>
     <row r="358" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="2"/>
@@ -9299,6 +9726,7 @@
       <c r="T358" s="3"/>
       <c r="U358" s="3"/>
       <c r="V358" s="3"/>
+      <c r="W358" s="3"/>
     </row>
     <row r="359" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="2"/>
@@ -9323,6 +9751,7 @@
       <c r="T359" s="3"/>
       <c r="U359" s="3"/>
       <c r="V359" s="3"/>
+      <c r="W359" s="3"/>
     </row>
     <row r="360" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="2"/>
@@ -9347,6 +9776,7 @@
       <c r="T360" s="3"/>
       <c r="U360" s="3"/>
       <c r="V360" s="3"/>
+      <c r="W360" s="3"/>
     </row>
     <row r="361" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="2"/>
@@ -9371,6 +9801,7 @@
       <c r="T361" s="3"/>
       <c r="U361" s="3"/>
       <c r="V361" s="3"/>
+      <c r="W361" s="3"/>
     </row>
     <row r="362" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="2"/>
@@ -9395,6 +9826,7 @@
       <c r="T362" s="3"/>
       <c r="U362" s="3"/>
       <c r="V362" s="3"/>
+      <c r="W362" s="3"/>
     </row>
     <row r="363" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="2"/>
@@ -9419,6 +9851,7 @@
       <c r="T363" s="3"/>
       <c r="U363" s="3"/>
       <c r="V363" s="3"/>
+      <c r="W363" s="3"/>
     </row>
     <row r="364" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="2"/>
@@ -9443,6 +9876,7 @@
       <c r="T364" s="3"/>
       <c r="U364" s="3"/>
       <c r="V364" s="3"/>
+      <c r="W364" s="3"/>
     </row>
     <row r="365" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="2"/>
@@ -9467,6 +9901,7 @@
       <c r="T365" s="3"/>
       <c r="U365" s="3"/>
       <c r="V365" s="3"/>
+      <c r="W365" s="3"/>
     </row>
     <row r="366" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="2"/>
@@ -9491,6 +9926,7 @@
       <c r="T366" s="3"/>
       <c r="U366" s="3"/>
       <c r="V366" s="3"/>
+      <c r="W366" s="3"/>
     </row>
     <row r="367" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="2"/>
@@ -9515,6 +9951,7 @@
       <c r="T367" s="3"/>
       <c r="U367" s="3"/>
       <c r="V367" s="3"/>
+      <c r="W367" s="3"/>
     </row>
     <row r="368" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="2"/>
@@ -9539,6 +9976,7 @@
       <c r="T368" s="3"/>
       <c r="U368" s="3"/>
       <c r="V368" s="3"/>
+      <c r="W368" s="3"/>
     </row>
     <row r="369" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="2"/>
@@ -9563,6 +10001,7 @@
       <c r="T369" s="3"/>
       <c r="U369" s="3"/>
       <c r="V369" s="3"/>
+      <c r="W369" s="3"/>
     </row>
     <row r="370" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="2"/>
@@ -9587,6 +10026,7 @@
       <c r="T370" s="3"/>
       <c r="U370" s="3"/>
       <c r="V370" s="3"/>
+      <c r="W370" s="3"/>
     </row>
     <row r="371" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="2"/>
@@ -9611,6 +10051,7 @@
       <c r="T371" s="3"/>
       <c r="U371" s="3"/>
       <c r="V371" s="3"/>
+      <c r="W371" s="3"/>
     </row>
     <row r="372" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="2"/>
@@ -9635,6 +10076,7 @@
       <c r="T372" s="3"/>
       <c r="U372" s="3"/>
       <c r="V372" s="3"/>
+      <c r="W372" s="3"/>
     </row>
     <row r="373" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="2"/>
@@ -9659,6 +10101,7 @@
       <c r="T373" s="3"/>
       <c r="U373" s="3"/>
       <c r="V373" s="3"/>
+      <c r="W373" s="3"/>
     </row>
     <row r="374" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="2"/>
@@ -9683,6 +10126,7 @@
       <c r="T374" s="3"/>
       <c r="U374" s="3"/>
       <c r="V374" s="3"/>
+      <c r="W374" s="3"/>
     </row>
     <row r="375" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="2"/>
@@ -9707,6 +10151,7 @@
       <c r="T375" s="3"/>
       <c r="U375" s="3"/>
       <c r="V375" s="3"/>
+      <c r="W375" s="3"/>
     </row>
     <row r="376" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="2"/>
@@ -9731,6 +10176,7 @@
       <c r="T376" s="3"/>
       <c r="U376" s="3"/>
       <c r="V376" s="3"/>
+      <c r="W376" s="3"/>
     </row>
     <row r="377" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="2"/>
@@ -9755,6 +10201,7 @@
       <c r="T377" s="3"/>
       <c r="U377" s="3"/>
       <c r="V377" s="3"/>
+      <c r="W377" s="3"/>
     </row>
     <row r="378" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="2"/>
@@ -9779,6 +10226,7 @@
       <c r="T378" s="3"/>
       <c r="U378" s="3"/>
       <c r="V378" s="3"/>
+      <c r="W378" s="3"/>
     </row>
     <row r="379" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="2"/>
@@ -9803,6 +10251,7 @@
       <c r="T379" s="3"/>
       <c r="U379" s="3"/>
       <c r="V379" s="3"/>
+      <c r="W379" s="3"/>
     </row>
     <row r="380" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="2"/>
@@ -9827,6 +10276,7 @@
       <c r="T380" s="3"/>
       <c r="U380" s="3"/>
       <c r="V380" s="3"/>
+      <c r="W380" s="3"/>
     </row>
     <row r="381" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="2"/>
@@ -9851,6 +10301,7 @@
       <c r="T381" s="3"/>
       <c r="U381" s="3"/>
       <c r="V381" s="3"/>
+      <c r="W381" s="3"/>
     </row>
     <row r="382" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="2"/>
@@ -9875,6 +10326,7 @@
       <c r="T382" s="3"/>
       <c r="U382" s="3"/>
       <c r="V382" s="3"/>
+      <c r="W382" s="3"/>
     </row>
     <row r="383" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="2"/>
@@ -9899,6 +10351,7 @@
       <c r="T383" s="3"/>
       <c r="U383" s="3"/>
       <c r="V383" s="3"/>
+      <c r="W383" s="3"/>
     </row>
     <row r="384" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="2"/>
@@ -9923,6 +10376,7 @@
       <c r="T384" s="3"/>
       <c r="U384" s="3"/>
       <c r="V384" s="3"/>
+      <c r="W384" s="3"/>
     </row>
     <row r="385" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="2"/>
@@ -9947,6 +10401,7 @@
       <c r="T385" s="3"/>
       <c r="U385" s="3"/>
       <c r="V385" s="3"/>
+      <c r="W385" s="3"/>
     </row>
     <row r="386" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="2"/>
@@ -9971,6 +10426,7 @@
       <c r="T386" s="3"/>
       <c r="U386" s="3"/>
       <c r="V386" s="3"/>
+      <c r="W386" s="3"/>
     </row>
     <row r="387" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="2"/>
@@ -9995,6 +10451,7 @@
       <c r="T387" s="3"/>
       <c r="U387" s="3"/>
       <c r="V387" s="3"/>
+      <c r="W387" s="3"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="2"/>
@@ -10019,6 +10476,7 @@
       <c r="T388" s="3"/>
       <c r="U388" s="3"/>
       <c r="V388" s="3"/>
+      <c r="W388" s="3"/>
     </row>
     <row r="389" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="2"/>
@@ -10043,6 +10501,7 @@
       <c r="T389" s="3"/>
       <c r="U389" s="3"/>
       <c r="V389" s="3"/>
+      <c r="W389" s="3"/>
     </row>
     <row r="390" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="2"/>
@@ -10067,6 +10526,7 @@
       <c r="T390" s="3"/>
       <c r="U390" s="3"/>
       <c r="V390" s="3"/>
+      <c r="W390" s="3"/>
     </row>
     <row r="391" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="2"/>
@@ -10091,6 +10551,7 @@
       <c r="T391" s="3"/>
       <c r="U391" s="3"/>
       <c r="V391" s="3"/>
+      <c r="W391" s="3"/>
     </row>
     <row r="392" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="2"/>
@@ -10115,6 +10576,7 @@
       <c r="T392" s="3"/>
       <c r="U392" s="3"/>
       <c r="V392" s="3"/>
+      <c r="W392" s="3"/>
     </row>
     <row r="393" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="2"/>
@@ -10139,6 +10601,7 @@
       <c r="T393" s="3"/>
       <c r="U393" s="3"/>
       <c r="V393" s="3"/>
+      <c r="W393" s="3"/>
     </row>
     <row r="394" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="2"/>
@@ -10163,6 +10626,7 @@
       <c r="T394" s="3"/>
       <c r="U394" s="3"/>
       <c r="V394" s="3"/>
+      <c r="W394" s="3"/>
     </row>
     <row r="395" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="2"/>
@@ -10187,6 +10651,7 @@
       <c r="T395" s="3"/>
       <c r="U395" s="3"/>
       <c r="V395" s="3"/>
+      <c r="W395" s="3"/>
     </row>
     <row r="396" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="2"/>
@@ -10211,6 +10676,7 @@
       <c r="T396" s="3"/>
       <c r="U396" s="3"/>
       <c r="V396" s="3"/>
+      <c r="W396" s="3"/>
     </row>
     <row r="397" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="2"/>
@@ -10235,6 +10701,7 @@
       <c r="T397" s="3"/>
       <c r="U397" s="3"/>
       <c r="V397" s="3"/>
+      <c r="W397" s="3"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="2"/>
@@ -10259,6 +10726,7 @@
       <c r="T398" s="3"/>
       <c r="U398" s="3"/>
       <c r="V398" s="3"/>
+      <c r="W398" s="3"/>
     </row>
     <row r="399" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="2"/>
@@ -10283,6 +10751,7 @@
       <c r="T399" s="3"/>
       <c r="U399" s="3"/>
       <c r="V399" s="3"/>
+      <c r="W399" s="3"/>
     </row>
     <row r="400" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="2"/>
@@ -10307,6 +10776,7 @@
       <c r="T400" s="3"/>
       <c r="U400" s="3"/>
       <c r="V400" s="3"/>
+      <c r="W400" s="3"/>
     </row>
     <row r="401" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="2"/>
@@ -10331,6 +10801,7 @@
       <c r="T401" s="3"/>
       <c r="U401" s="3"/>
       <c r="V401" s="3"/>
+      <c r="W401" s="3"/>
     </row>
     <row r="402" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="2"/>
@@ -10355,6 +10826,7 @@
       <c r="T402" s="3"/>
       <c r="U402" s="3"/>
       <c r="V402" s="3"/>
+      <c r="W402" s="3"/>
     </row>
     <row r="403" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="2"/>
@@ -10379,6 +10851,7 @@
       <c r="T403" s="3"/>
       <c r="U403" s="3"/>
       <c r="V403" s="3"/>
+      <c r="W403" s="3"/>
     </row>
     <row r="404" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
@@ -10403,6 +10876,7 @@
       <c r="T404" s="3"/>
       <c r="U404" s="3"/>
       <c r="V404" s="3"/>
+      <c r="W404" s="3"/>
     </row>
     <row r="405" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="2"/>
@@ -10427,6 +10901,7 @@
       <c r="T405" s="3"/>
       <c r="U405" s="3"/>
       <c r="V405" s="3"/>
+      <c r="W405" s="3"/>
     </row>
     <row r="406" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="2"/>
@@ -10451,6 +10926,7 @@
       <c r="T406" s="3"/>
       <c r="U406" s="3"/>
       <c r="V406" s="3"/>
+      <c r="W406" s="3"/>
     </row>
     <row r="407" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="2"/>
@@ -10475,6 +10951,7 @@
       <c r="T407" s="3"/>
       <c r="U407" s="3"/>
       <c r="V407" s="3"/>
+      <c r="W407" s="3"/>
     </row>
     <row r="408" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="2"/>
@@ -10499,6 +10976,7 @@
       <c r="T408" s="3"/>
       <c r="U408" s="3"/>
       <c r="V408" s="3"/>
+      <c r="W408" s="3"/>
     </row>
     <row r="409" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="2"/>
@@ -10523,6 +11001,7 @@
       <c r="T409" s="3"/>
       <c r="U409" s="3"/>
       <c r="V409" s="3"/>
+      <c r="W409" s="3"/>
     </row>
     <row r="410" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="2"/>
@@ -10547,6 +11026,7 @@
       <c r="T410" s="3"/>
       <c r="U410" s="3"/>
       <c r="V410" s="3"/>
+      <c r="W410" s="3"/>
     </row>
     <row r="411" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="2"/>
@@ -10571,6 +11051,7 @@
       <c r="T411" s="3"/>
       <c r="U411" s="3"/>
       <c r="V411" s="3"/>
+      <c r="W411" s="3"/>
     </row>
     <row r="412" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="2"/>
@@ -10595,6 +11076,7 @@
       <c r="T412" s="3"/>
       <c r="U412" s="3"/>
       <c r="V412" s="3"/>
+      <c r="W412" s="3"/>
     </row>
     <row r="413" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="2"/>
@@ -10619,6 +11101,7 @@
       <c r="T413" s="3"/>
       <c r="U413" s="3"/>
       <c r="V413" s="3"/>
+      <c r="W413" s="3"/>
     </row>
     <row r="414" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="2"/>
@@ -10643,6 +11126,7 @@
       <c r="T414" s="3"/>
       <c r="U414" s="3"/>
       <c r="V414" s="3"/>
+      <c r="W414" s="3"/>
     </row>
     <row r="415" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="2"/>
@@ -10667,6 +11151,7 @@
       <c r="T415" s="3"/>
       <c r="U415" s="3"/>
       <c r="V415" s="3"/>
+      <c r="W415" s="3"/>
     </row>
     <row r="416" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="2"/>
@@ -10691,6 +11176,7 @@
       <c r="T416" s="3"/>
       <c r="U416" s="3"/>
       <c r="V416" s="3"/>
+      <c r="W416" s="3"/>
     </row>
     <row r="417" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="2"/>
@@ -10715,6 +11201,7 @@
       <c r="T417" s="3"/>
       <c r="U417" s="3"/>
       <c r="V417" s="3"/>
+      <c r="W417" s="3"/>
     </row>
     <row r="418" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="2"/>
@@ -10739,6 +11226,7 @@
       <c r="T418" s="3"/>
       <c r="U418" s="3"/>
       <c r="V418" s="3"/>
+      <c r="W418" s="3"/>
     </row>
     <row r="419" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
@@ -10763,6 +11251,7 @@
       <c r="T419" s="3"/>
       <c r="U419" s="3"/>
       <c r="V419" s="3"/>
+      <c r="W419" s="3"/>
     </row>
     <row r="420" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
@@ -10787,6 +11276,7 @@
       <c r="T420" s="3"/>
       <c r="U420" s="3"/>
       <c r="V420" s="3"/>
+      <c r="W420" s="3"/>
     </row>
     <row r="421" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="2"/>
@@ -10811,6 +11301,7 @@
       <c r="T421" s="3"/>
       <c r="U421" s="3"/>
       <c r="V421" s="3"/>
+      <c r="W421" s="3"/>
     </row>
     <row r="422" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="2"/>
@@ -10835,6 +11326,7 @@
       <c r="T422" s="3"/>
       <c r="U422" s="3"/>
       <c r="V422" s="3"/>
+      <c r="W422" s="3"/>
     </row>
     <row r="423" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="2"/>
@@ -10859,6 +11351,7 @@
       <c r="T423" s="3"/>
       <c r="U423" s="3"/>
       <c r="V423" s="3"/>
+      <c r="W423" s="3"/>
     </row>
     <row r="424" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="2"/>
@@ -10883,6 +11376,7 @@
       <c r="T424" s="3"/>
       <c r="U424" s="3"/>
       <c r="V424" s="3"/>
+      <c r="W424" s="3"/>
     </row>
     <row r="425" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="2"/>
@@ -10907,6 +11401,7 @@
       <c r="T425" s="3"/>
       <c r="U425" s="3"/>
       <c r="V425" s="3"/>
+      <c r="W425" s="3"/>
     </row>
     <row r="426" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="2"/>
@@ -10931,6 +11426,7 @@
       <c r="T426" s="3"/>
       <c r="U426" s="3"/>
       <c r="V426" s="3"/>
+      <c r="W426" s="3"/>
     </row>
     <row r="427" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="2"/>
@@ -10955,6 +11451,7 @@
       <c r="T427" s="3"/>
       <c r="U427" s="3"/>
       <c r="V427" s="3"/>
+      <c r="W427" s="3"/>
     </row>
     <row r="428" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
@@ -10979,6 +11476,7 @@
       <c r="T428" s="3"/>
       <c r="U428" s="3"/>
       <c r="V428" s="3"/>
+      <c r="W428" s="3"/>
     </row>
     <row r="429" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
@@ -11003,6 +11501,7 @@
       <c r="T429" s="3"/>
       <c r="U429" s="3"/>
       <c r="V429" s="3"/>
+      <c r="W429" s="3"/>
     </row>
     <row r="430" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
@@ -11027,6 +11526,7 @@
       <c r="T430" s="3"/>
       <c r="U430" s="3"/>
       <c r="V430" s="3"/>
+      <c r="W430" s="3"/>
     </row>
     <row r="431" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="2"/>
@@ -11051,6 +11551,7 @@
       <c r="T431" s="3"/>
       <c r="U431" s="3"/>
       <c r="V431" s="3"/>
+      <c r="W431" s="3"/>
     </row>
     <row r="432" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="2"/>
@@ -11075,6 +11576,7 @@
       <c r="T432" s="3"/>
       <c r="U432" s="3"/>
       <c r="V432" s="3"/>
+      <c r="W432" s="3"/>
     </row>
     <row r="433" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="2"/>
@@ -11099,6 +11601,7 @@
       <c r="T433" s="3"/>
       <c r="U433" s="3"/>
       <c r="V433" s="3"/>
+      <c r="W433" s="3"/>
     </row>
     <row r="434" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="2"/>
@@ -11123,6 +11626,7 @@
       <c r="T434" s="3"/>
       <c r="U434" s="3"/>
       <c r="V434" s="3"/>
+      <c r="W434" s="3"/>
     </row>
     <row r="435" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="2"/>
@@ -11147,6 +11651,7 @@
       <c r="T435" s="3"/>
       <c r="U435" s="3"/>
       <c r="V435" s="3"/>
+      <c r="W435" s="3"/>
     </row>
     <row r="436" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="2"/>
@@ -11171,6 +11676,7 @@
       <c r="T436" s="3"/>
       <c r="U436" s="3"/>
       <c r="V436" s="3"/>
+      <c r="W436" s="3"/>
     </row>
     <row r="437" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="2"/>
@@ -11195,6 +11701,7 @@
       <c r="T437" s="3"/>
       <c r="U437" s="3"/>
       <c r="V437" s="3"/>
+      <c r="W437" s="3"/>
     </row>
     <row r="438" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="2"/>
@@ -11219,6 +11726,7 @@
       <c r="T438" s="3"/>
       <c r="U438" s="3"/>
       <c r="V438" s="3"/>
+      <c r="W438" s="3"/>
     </row>
     <row r="439" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="2"/>
@@ -11243,6 +11751,7 @@
       <c r="T439" s="3"/>
       <c r="U439" s="3"/>
       <c r="V439" s="3"/>
+      <c r="W439" s="3"/>
     </row>
     <row r="440" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="2"/>
@@ -11267,6 +11776,7 @@
       <c r="T440" s="3"/>
       <c r="U440" s="3"/>
       <c r="V440" s="3"/>
+      <c r="W440" s="3"/>
     </row>
     <row r="441" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="2"/>
@@ -11291,6 +11801,7 @@
       <c r="T441" s="3"/>
       <c r="U441" s="3"/>
       <c r="V441" s="3"/>
+      <c r="W441" s="3"/>
     </row>
     <row r="442" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="2"/>
@@ -11315,6 +11826,7 @@
       <c r="T442" s="3"/>
       <c r="U442" s="3"/>
       <c r="V442" s="3"/>
+      <c r="W442" s="3"/>
     </row>
     <row r="443" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="2"/>
@@ -11339,6 +11851,7 @@
       <c r="T443" s="3"/>
       <c r="U443" s="3"/>
       <c r="V443" s="3"/>
+      <c r="W443" s="3"/>
     </row>
     <row r="444" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="2"/>
@@ -11363,6 +11876,7 @@
       <c r="T444" s="3"/>
       <c r="U444" s="3"/>
       <c r="V444" s="3"/>
+      <c r="W444" s="3"/>
     </row>
     <row r="445" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="2"/>
@@ -11387,6 +11901,7 @@
       <c r="T445" s="3"/>
       <c r="U445" s="3"/>
       <c r="V445" s="3"/>
+      <c r="W445" s="3"/>
     </row>
     <row r="446" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="2"/>
@@ -11411,6 +11926,7 @@
       <c r="T446" s="3"/>
       <c r="U446" s="3"/>
       <c r="V446" s="3"/>
+      <c r="W446" s="3"/>
     </row>
     <row r="447" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="2"/>
@@ -11435,6 +11951,7 @@
       <c r="T447" s="3"/>
       <c r="U447" s="3"/>
       <c r="V447" s="3"/>
+      <c r="W447" s="3"/>
     </row>
     <row r="448" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="2"/>
@@ -11459,6 +11976,7 @@
       <c r="T448" s="3"/>
       <c r="U448" s="3"/>
       <c r="V448" s="3"/>
+      <c r="W448" s="3"/>
     </row>
     <row r="449" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="2"/>
@@ -11483,6 +12001,7 @@
       <c r="T449" s="3"/>
       <c r="U449" s="3"/>
       <c r="V449" s="3"/>
+      <c r="W449" s="3"/>
     </row>
     <row r="450" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="2"/>
@@ -11507,6 +12026,7 @@
       <c r="T450" s="3"/>
       <c r="U450" s="3"/>
       <c r="V450" s="3"/>
+      <c r="W450" s="3"/>
     </row>
     <row r="451" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="2"/>
@@ -11531,6 +12051,7 @@
       <c r="T451" s="3"/>
       <c r="U451" s="3"/>
       <c r="V451" s="3"/>
+      <c r="W451" s="3"/>
     </row>
     <row r="452" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="2"/>
@@ -11555,6 +12076,7 @@
       <c r="T452" s="3"/>
       <c r="U452" s="3"/>
       <c r="V452" s="3"/>
+      <c r="W452" s="3"/>
     </row>
     <row r="453" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="2"/>
@@ -11579,6 +12101,7 @@
       <c r="T453" s="3"/>
       <c r="U453" s="3"/>
       <c r="V453" s="3"/>
+      <c r="W453" s="3"/>
     </row>
     <row r="454" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="2"/>
@@ -11603,6 +12126,7 @@
       <c r="T454" s="3"/>
       <c r="U454" s="3"/>
       <c r="V454" s="3"/>
+      <c r="W454" s="3"/>
     </row>
     <row r="455" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="2"/>
@@ -11627,6 +12151,7 @@
       <c r="T455" s="3"/>
       <c r="U455" s="3"/>
       <c r="V455" s="3"/>
+      <c r="W455" s="3"/>
     </row>
     <row r="456" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="2"/>
@@ -11651,6 +12176,7 @@
       <c r="T456" s="3"/>
       <c r="U456" s="3"/>
       <c r="V456" s="3"/>
+      <c r="W456" s="3"/>
     </row>
     <row r="457" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="2"/>
@@ -11675,6 +12201,7 @@
       <c r="T457" s="3"/>
       <c r="U457" s="3"/>
       <c r="V457" s="3"/>
+      <c r="W457" s="3"/>
     </row>
     <row r="458" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="2"/>
@@ -11699,6 +12226,7 @@
       <c r="T458" s="3"/>
       <c r="U458" s="3"/>
       <c r="V458" s="3"/>
+      <c r="W458" s="3"/>
     </row>
     <row r="459" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="2"/>
@@ -11723,6 +12251,7 @@
       <c r="T459" s="3"/>
       <c r="U459" s="3"/>
       <c r="V459" s="3"/>
+      <c r="W459" s="3"/>
     </row>
     <row r="460" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="2"/>
@@ -11747,6 +12276,7 @@
       <c r="T460" s="3"/>
       <c r="U460" s="3"/>
       <c r="V460" s="3"/>
+      <c r="W460" s="3"/>
     </row>
     <row r="461" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="2"/>
@@ -11771,6 +12301,7 @@
       <c r="T461" s="3"/>
       <c r="U461" s="3"/>
       <c r="V461" s="3"/>
+      <c r="W461" s="3"/>
     </row>
     <row r="462" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="2"/>
@@ -11795,6 +12326,7 @@
       <c r="T462" s="3"/>
       <c r="U462" s="3"/>
       <c r="V462" s="3"/>
+      <c r="W462" s="3"/>
     </row>
     <row r="463" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="2"/>
@@ -11819,6 +12351,7 @@
       <c r="T463" s="3"/>
       <c r="U463" s="3"/>
       <c r="V463" s="3"/>
+      <c r="W463" s="3"/>
     </row>
     <row r="464" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="2"/>
@@ -11843,6 +12376,7 @@
       <c r="T464" s="3"/>
       <c r="U464" s="3"/>
       <c r="V464" s="3"/>
+      <c r="W464" s="3"/>
     </row>
     <row r="465" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="2"/>
@@ -11867,6 +12401,7 @@
       <c r="T465" s="3"/>
       <c r="U465" s="3"/>
       <c r="V465" s="3"/>
+      <c r="W465" s="3"/>
     </row>
     <row r="466" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="2"/>
@@ -11891,6 +12426,7 @@
       <c r="T466" s="3"/>
       <c r="U466" s="3"/>
       <c r="V466" s="3"/>
+      <c r="W466" s="3"/>
     </row>
     <row r="467" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="2"/>
@@ -11915,6 +12451,7 @@
       <c r="T467" s="3"/>
       <c r="U467" s="3"/>
       <c r="V467" s="3"/>
+      <c r="W467" s="3"/>
     </row>
     <row r="468" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="2"/>
@@ -11939,6 +12476,7 @@
       <c r="T468" s="3"/>
       <c r="U468" s="3"/>
       <c r="V468" s="3"/>
+      <c r="W468" s="3"/>
     </row>
     <row r="469" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="2"/>
@@ -11963,6 +12501,7 @@
       <c r="T469" s="3"/>
       <c r="U469" s="3"/>
       <c r="V469" s="3"/>
+      <c r="W469" s="3"/>
     </row>
     <row r="470" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="2"/>
@@ -11987,6 +12526,7 @@
       <c r="T470" s="3"/>
       <c r="U470" s="3"/>
       <c r="V470" s="3"/>
+      <c r="W470" s="3"/>
     </row>
     <row r="471" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="2"/>
@@ -12011,6 +12551,7 @@
       <c r="T471" s="3"/>
       <c r="U471" s="3"/>
       <c r="V471" s="3"/>
+      <c r="W471" s="3"/>
     </row>
     <row r="472" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="2"/>
@@ -12035,6 +12576,7 @@
       <c r="T472" s="3"/>
       <c r="U472" s="3"/>
       <c r="V472" s="3"/>
+      <c r="W472" s="3"/>
     </row>
     <row r="473" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="2"/>
@@ -12059,6 +12601,7 @@
       <c r="T473" s="3"/>
       <c r="U473" s="3"/>
       <c r="V473" s="3"/>
+      <c r="W473" s="3"/>
     </row>
     <row r="474" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="2"/>
@@ -12083,6 +12626,7 @@
       <c r="T474" s="3"/>
       <c r="U474" s="3"/>
       <c r="V474" s="3"/>
+      <c r="W474" s="3"/>
     </row>
     <row r="475" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="2"/>
@@ -12107,6 +12651,7 @@
       <c r="T475" s="3"/>
       <c r="U475" s="3"/>
       <c r="V475" s="3"/>
+      <c r="W475" s="3"/>
     </row>
     <row r="476" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="2"/>
@@ -12131,6 +12676,7 @@
       <c r="T476" s="3"/>
       <c r="U476" s="3"/>
       <c r="V476" s="3"/>
+      <c r="W476" s="3"/>
     </row>
     <row r="477" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="2"/>
@@ -12155,6 +12701,7 @@
       <c r="T477" s="3"/>
       <c r="U477" s="3"/>
       <c r="V477" s="3"/>
+      <c r="W477" s="3"/>
     </row>
     <row r="478" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="2"/>
@@ -12179,6 +12726,7 @@
       <c r="T478" s="3"/>
       <c r="U478" s="3"/>
       <c r="V478" s="3"/>
+      <c r="W478" s="3"/>
     </row>
     <row r="479" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="2"/>
@@ -12203,6 +12751,7 @@
       <c r="T479" s="3"/>
       <c r="U479" s="3"/>
       <c r="V479" s="3"/>
+      <c r="W479" s="3"/>
     </row>
     <row r="480" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="2"/>
@@ -12227,6 +12776,7 @@
       <c r="T480" s="3"/>
       <c r="U480" s="3"/>
       <c r="V480" s="3"/>
+      <c r="W480" s="3"/>
     </row>
     <row r="481" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="2"/>
@@ -12251,6 +12801,7 @@
       <c r="T481" s="3"/>
       <c r="U481" s="3"/>
       <c r="V481" s="3"/>
+      <c r="W481" s="3"/>
     </row>
     <row r="482" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="2"/>
@@ -12275,6 +12826,7 @@
       <c r="T482" s="3"/>
       <c r="U482" s="3"/>
       <c r="V482" s="3"/>
+      <c r="W482" s="3"/>
     </row>
     <row r="483" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="2"/>
@@ -12299,6 +12851,7 @@
       <c r="T483" s="3"/>
       <c r="U483" s="3"/>
       <c r="V483" s="3"/>
+      <c r="W483" s="3"/>
     </row>
     <row r="484" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="2"/>
@@ -12323,6 +12876,7 @@
       <c r="T484" s="3"/>
       <c r="U484" s="3"/>
       <c r="V484" s="3"/>
+      <c r="W484" s="3"/>
     </row>
     <row r="485" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="2"/>
@@ -12347,6 +12901,7 @@
       <c r="T485" s="3"/>
       <c r="U485" s="3"/>
       <c r="V485" s="3"/>
+      <c r="W485" s="3"/>
     </row>
     <row r="486" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="2"/>
@@ -12371,6 +12926,7 @@
       <c r="T486" s="3"/>
       <c r="U486" s="3"/>
       <c r="V486" s="3"/>
+      <c r="W486" s="3"/>
     </row>
     <row r="487" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="2"/>
@@ -12395,6 +12951,7 @@
       <c r="T487" s="3"/>
       <c r="U487" s="3"/>
       <c r="V487" s="3"/>
+      <c r="W487" s="3"/>
     </row>
     <row r="488" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="2"/>
@@ -12419,6 +12976,7 @@
       <c r="T488" s="3"/>
       <c r="U488" s="3"/>
       <c r="V488" s="3"/>
+      <c r="W488" s="3"/>
     </row>
     <row r="489" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="2"/>
@@ -12443,6 +13001,7 @@
       <c r="T489" s="3"/>
       <c r="U489" s="3"/>
       <c r="V489" s="3"/>
+      <c r="W489" s="3"/>
     </row>
     <row r="490" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="2"/>
@@ -12467,6 +13026,7 @@
       <c r="T490" s="3"/>
       <c r="U490" s="3"/>
       <c r="V490" s="3"/>
+      <c r="W490" s="3"/>
     </row>
     <row r="491" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="2"/>
@@ -12491,6 +13051,7 @@
       <c r="T491" s="3"/>
       <c r="U491" s="3"/>
       <c r="V491" s="3"/>
+      <c r="W491" s="3"/>
     </row>
     <row r="492" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="2"/>
@@ -12515,6 +13076,7 @@
       <c r="T492" s="3"/>
       <c r="U492" s="3"/>
       <c r="V492" s="3"/>
+      <c r="W492" s="3"/>
     </row>
     <row r="493" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="2"/>
@@ -12539,6 +13101,7 @@
       <c r="T493" s="3"/>
       <c r="U493" s="3"/>
       <c r="V493" s="3"/>
+      <c r="W493" s="3"/>
     </row>
     <row r="494" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="2"/>
@@ -12563,6 +13126,7 @@
       <c r="T494" s="3"/>
       <c r="U494" s="3"/>
       <c r="V494" s="3"/>
+      <c r="W494" s="3"/>
     </row>
     <row r="495" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="2"/>
@@ -12587,6 +13151,7 @@
       <c r="T495" s="3"/>
       <c r="U495" s="3"/>
       <c r="V495" s="3"/>
+      <c r="W495" s="3"/>
     </row>
     <row r="496" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="2"/>
@@ -12611,6 +13176,7 @@
       <c r="T496" s="3"/>
       <c r="U496" s="3"/>
       <c r="V496" s="3"/>
+      <c r="W496" s="3"/>
     </row>
     <row r="497" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="2"/>
@@ -12635,6 +13201,7 @@
       <c r="T497" s="3"/>
       <c r="U497" s="3"/>
       <c r="V497" s="3"/>
+      <c r="W497" s="3"/>
     </row>
     <row r="498" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="2"/>
@@ -12659,6 +13226,7 @@
       <c r="T498" s="3"/>
       <c r="U498" s="3"/>
       <c r="V498" s="3"/>
+      <c r="W498" s="3"/>
     </row>
     <row r="499" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="2"/>
@@ -12683,6 +13251,7 @@
       <c r="T499" s="3"/>
       <c r="U499" s="3"/>
       <c r="V499" s="3"/>
+      <c r="W499" s="3"/>
     </row>
     <row r="500" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="2"/>
@@ -12707,6 +13276,7 @@
       <c r="T500" s="3"/>
       <c r="U500" s="3"/>
       <c r="V500" s="3"/>
+      <c r="W500" s="3"/>
     </row>
     <row r="501" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="2"/>
@@ -12731,6 +13301,7 @@
       <c r="T501" s="3"/>
       <c r="U501" s="3"/>
       <c r="V501" s="3"/>
+      <c r="W501" s="3"/>
     </row>
     <row r="502" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="2"/>
@@ -12755,6 +13326,7 @@
       <c r="T502" s="3"/>
       <c r="U502" s="3"/>
       <c r="V502" s="3"/>
+      <c r="W502" s="3"/>
     </row>
     <row r="503" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="2"/>
@@ -12779,6 +13351,7 @@
       <c r="T503" s="3"/>
       <c r="U503" s="3"/>
       <c r="V503" s="3"/>
+      <c r="W503" s="3"/>
     </row>
     <row r="504" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="2"/>
@@ -12803,6 +13376,7 @@
       <c r="T504" s="3"/>
       <c r="U504" s="3"/>
       <c r="V504" s="3"/>
+      <c r="W504" s="3"/>
     </row>
     <row r="505" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="2"/>
@@ -12827,6 +13401,7 @@
       <c r="T505" s="3"/>
       <c r="U505" s="3"/>
       <c r="V505" s="3"/>
+      <c r="W505" s="3"/>
     </row>
     <row r="506" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="2"/>
@@ -12851,6 +13426,7 @@
       <c r="T506" s="3"/>
       <c r="U506" s="3"/>
       <c r="V506" s="3"/>
+      <c r="W506" s="3"/>
     </row>
     <row r="507" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="2"/>
@@ -12875,6 +13451,7 @@
       <c r="T507" s="3"/>
       <c r="U507" s="3"/>
       <c r="V507" s="3"/>
+      <c r="W507" s="3"/>
     </row>
     <row r="508" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="2"/>
@@ -12899,6 +13476,7 @@
       <c r="T508" s="3"/>
       <c r="U508" s="3"/>
       <c r="V508" s="3"/>
+      <c r="W508" s="3"/>
     </row>
     <row r="509" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="2"/>
@@ -12923,6 +13501,7 @@
       <c r="T509" s="3"/>
       <c r="U509" s="3"/>
       <c r="V509" s="3"/>
+      <c r="W509" s="3"/>
     </row>
     <row r="510" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="2"/>
@@ -12947,6 +13526,7 @@
       <c r="T510" s="3"/>
       <c r="U510" s="3"/>
       <c r="V510" s="3"/>
+      <c r="W510" s="3"/>
     </row>
     <row r="511" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="2"/>
@@ -12971,6 +13551,7 @@
       <c r="T511" s="3"/>
       <c r="U511" s="3"/>
       <c r="V511" s="3"/>
+      <c r="W511" s="3"/>
     </row>
     <row r="512" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="2"/>
@@ -12995,6 +13576,7 @@
       <c r="T512" s="3"/>
       <c r="U512" s="3"/>
       <c r="V512" s="3"/>
+      <c r="W512" s="3"/>
     </row>
     <row r="513" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="2"/>
@@ -13019,6 +13601,7 @@
       <c r="T513" s="3"/>
       <c r="U513" s="3"/>
       <c r="V513" s="3"/>
+      <c r="W513" s="3"/>
     </row>
     <row r="514" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="2"/>
@@ -13043,6 +13626,7 @@
       <c r="T514" s="3"/>
       <c r="U514" s="3"/>
       <c r="V514" s="3"/>
+      <c r="W514" s="3"/>
     </row>
     <row r="515" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="2"/>
@@ -13067,6 +13651,7 @@
       <c r="T515" s="3"/>
       <c r="U515" s="3"/>
       <c r="V515" s="3"/>
+      <c r="W515" s="3"/>
     </row>
     <row r="516" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="2"/>
@@ -13091,6 +13676,7 @@
       <c r="T516" s="3"/>
       <c r="U516" s="3"/>
       <c r="V516" s="3"/>
+      <c r="W516" s="3"/>
     </row>
     <row r="517" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="2"/>
@@ -13115,6 +13701,7 @@
       <c r="T517" s="3"/>
       <c r="U517" s="3"/>
       <c r="V517" s="3"/>
+      <c r="W517" s="3"/>
     </row>
     <row r="518" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="2"/>
@@ -13139,6 +13726,7 @@
       <c r="T518" s="3"/>
       <c r="U518" s="3"/>
       <c r="V518" s="3"/>
+      <c r="W518" s="3"/>
     </row>
     <row r="519" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="2"/>
@@ -13163,6 +13751,7 @@
       <c r="T519" s="3"/>
       <c r="U519" s="3"/>
       <c r="V519" s="3"/>
+      <c r="W519" s="3"/>
     </row>
     <row r="520" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="2"/>
@@ -13187,6 +13776,7 @@
       <c r="T520" s="3"/>
       <c r="U520" s="3"/>
       <c r="V520" s="3"/>
+      <c r="W520" s="3"/>
     </row>
     <row r="521" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="2"/>
@@ -13211,6 +13801,7 @@
       <c r="T521" s="3"/>
       <c r="U521" s="3"/>
       <c r="V521" s="3"/>
+      <c r="W521" s="3"/>
     </row>
     <row r="522" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="2"/>
@@ -13235,6 +13826,7 @@
       <c r="T522" s="3"/>
       <c r="U522" s="3"/>
       <c r="V522" s="3"/>
+      <c r="W522" s="3"/>
     </row>
     <row r="523" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="2"/>
@@ -13259,6 +13851,7 @@
       <c r="T523" s="3"/>
       <c r="U523" s="3"/>
       <c r="V523" s="3"/>
+      <c r="W523" s="3"/>
     </row>
     <row r="524" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="2"/>
@@ -13283,6 +13876,7 @@
       <c r="T524" s="3"/>
       <c r="U524" s="3"/>
       <c r="V524" s="3"/>
+      <c r="W524" s="3"/>
     </row>
     <row r="525" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="2"/>
@@ -13307,6 +13901,7 @@
       <c r="T525" s="3"/>
       <c r="U525" s="3"/>
       <c r="V525" s="3"/>
+      <c r="W525" s="3"/>
     </row>
     <row r="526" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="2"/>
@@ -13331,6 +13926,7 @@
       <c r="T526" s="3"/>
       <c r="U526" s="3"/>
       <c r="V526" s="3"/>
+      <c r="W526" s="3"/>
     </row>
     <row r="527" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="2"/>
@@ -13355,6 +13951,7 @@
       <c r="T527" s="3"/>
       <c r="U527" s="3"/>
       <c r="V527" s="3"/>
+      <c r="W527" s="3"/>
     </row>
     <row r="528" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="2"/>
@@ -13379,6 +13976,7 @@
       <c r="T528" s="3"/>
       <c r="U528" s="3"/>
       <c r="V528" s="3"/>
+      <c r="W528" s="3"/>
     </row>
     <row r="529" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="2"/>
@@ -13403,6 +14001,7 @@
       <c r="T529" s="3"/>
       <c r="U529" s="3"/>
       <c r="V529" s="3"/>
+      <c r="W529" s="3"/>
     </row>
     <row r="530" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="2"/>
@@ -13427,6 +14026,7 @@
       <c r="T530" s="3"/>
       <c r="U530" s="3"/>
       <c r="V530" s="3"/>
+      <c r="W530" s="3"/>
     </row>
     <row r="531" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="2"/>
@@ -13451,6 +14051,7 @@
       <c r="T531" s="3"/>
       <c r="U531" s="3"/>
       <c r="V531" s="3"/>
+      <c r="W531" s="3"/>
     </row>
     <row r="532" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="2"/>
@@ -13475,6 +14076,7 @@
       <c r="T532" s="3"/>
       <c r="U532" s="3"/>
       <c r="V532" s="3"/>
+      <c r="W532" s="3"/>
     </row>
     <row r="533" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="2"/>
@@ -13499,6 +14101,7 @@
       <c r="T533" s="3"/>
       <c r="U533" s="3"/>
       <c r="V533" s="3"/>
+      <c r="W533" s="3"/>
     </row>
     <row r="534" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="2"/>
@@ -13523,6 +14126,7 @@
       <c r="T534" s="3"/>
       <c r="U534" s="3"/>
       <c r="V534" s="3"/>
+      <c r="W534" s="3"/>
     </row>
     <row r="535" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="2"/>
@@ -13547,6 +14151,7 @@
       <c r="T535" s="3"/>
       <c r="U535" s="3"/>
       <c r="V535" s="3"/>
+      <c r="W535" s="3"/>
     </row>
     <row r="536" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="2"/>
@@ -13571,6 +14176,7 @@
       <c r="T536" s="3"/>
       <c r="U536" s="3"/>
       <c r="V536" s="3"/>
+      <c r="W536" s="3"/>
     </row>
     <row r="537" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="2"/>
@@ -13595,6 +14201,7 @@
       <c r="T537" s="3"/>
       <c r="U537" s="3"/>
       <c r="V537" s="3"/>
+      <c r="W537" s="3"/>
     </row>
     <row r="538" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="2"/>
@@ -13619,6 +14226,7 @@
       <c r="T538" s="3"/>
       <c r="U538" s="3"/>
       <c r="V538" s="3"/>
+      <c r="W538" s="3"/>
     </row>
     <row r="539" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="2"/>
@@ -13643,6 +14251,7 @@
       <c r="T539" s="3"/>
       <c r="U539" s="3"/>
       <c r="V539" s="3"/>
+      <c r="W539" s="3"/>
     </row>
     <row r="540" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="2"/>
@@ -13667,6 +14276,7 @@
       <c r="T540" s="3"/>
       <c r="U540" s="3"/>
       <c r="V540" s="3"/>
+      <c r="W540" s="3"/>
     </row>
     <row r="541" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="2"/>
@@ -13691,6 +14301,7 @@
       <c r="T541" s="3"/>
       <c r="U541" s="3"/>
       <c r="V541" s="3"/>
+      <c r="W541" s="3"/>
     </row>
     <row r="542" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="2"/>
@@ -13715,6 +14326,7 @@
       <c r="T542" s="3"/>
       <c r="U542" s="3"/>
       <c r="V542" s="3"/>
+      <c r="W542" s="3"/>
     </row>
     <row r="543" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="2"/>
@@ -13739,6 +14351,7 @@
       <c r="T543" s="3"/>
       <c r="U543" s="3"/>
       <c r="V543" s="3"/>
+      <c r="W543" s="3"/>
     </row>
     <row r="544" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="2"/>
@@ -13763,6 +14376,7 @@
       <c r="T544" s="3"/>
       <c r="U544" s="3"/>
       <c r="V544" s="3"/>
+      <c r="W544" s="3"/>
     </row>
     <row r="545" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="2"/>
@@ -13787,6 +14401,7 @@
       <c r="T545" s="3"/>
       <c r="U545" s="3"/>
       <c r="V545" s="3"/>
+      <c r="W545" s="3"/>
     </row>
     <row r="546" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="2"/>
@@ -13811,6 +14426,7 @@
       <c r="T546" s="3"/>
       <c r="U546" s="3"/>
       <c r="V546" s="3"/>
+      <c r="W546" s="3"/>
     </row>
     <row r="547" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="2"/>
@@ -13835,6 +14451,7 @@
       <c r="T547" s="3"/>
       <c r="U547" s="3"/>
       <c r="V547" s="3"/>
+      <c r="W547" s="3"/>
     </row>
     <row r="548" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="2"/>
@@ -13859,6 +14476,7 @@
       <c r="T548" s="3"/>
       <c r="U548" s="3"/>
       <c r="V548" s="3"/>
+      <c r="W548" s="3"/>
     </row>
     <row r="549" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="2"/>
@@ -13883,6 +14501,7 @@
       <c r="T549" s="3"/>
       <c r="U549" s="3"/>
       <c r="V549" s="3"/>
+      <c r="W549" s="3"/>
     </row>
     <row r="550" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="2"/>
@@ -13907,6 +14526,7 @@
       <c r="T550" s="3"/>
       <c r="U550" s="3"/>
       <c r="V550" s="3"/>
+      <c r="W550" s="3"/>
     </row>
     <row r="551" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="2"/>
@@ -13931,6 +14551,7 @@
       <c r="T551" s="3"/>
       <c r="U551" s="3"/>
       <c r="V551" s="3"/>
+      <c r="W551" s="3"/>
     </row>
     <row r="552" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="2"/>
@@ -13955,6 +14576,7 @@
       <c r="T552" s="3"/>
       <c r="U552" s="3"/>
       <c r="V552" s="3"/>
+      <c r="W552" s="3"/>
     </row>
     <row r="553" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="2"/>
@@ -13979,6 +14601,7 @@
       <c r="T553" s="3"/>
       <c r="U553" s="3"/>
       <c r="V553" s="3"/>
+      <c r="W553" s="3"/>
     </row>
     <row r="554" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="2"/>
@@ -14003,6 +14626,7 @@
       <c r="T554" s="3"/>
       <c r="U554" s="3"/>
       <c r="V554" s="3"/>
+      <c r="W554" s="3"/>
     </row>
     <row r="555" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="2"/>
@@ -14027,6 +14651,7 @@
       <c r="T555" s="3"/>
       <c r="U555" s="3"/>
       <c r="V555" s="3"/>
+      <c r="W555" s="3"/>
     </row>
     <row r="556" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="2"/>
@@ -14051,6 +14676,7 @@
       <c r="T556" s="3"/>
       <c r="U556" s="3"/>
       <c r="V556" s="3"/>
+      <c r="W556" s="3"/>
     </row>
     <row r="557" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="2"/>
@@ -14075,6 +14701,7 @@
       <c r="T557" s="3"/>
       <c r="U557" s="3"/>
       <c r="V557" s="3"/>
+      <c r="W557" s="3"/>
     </row>
     <row r="558" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="2"/>
@@ -14099,6 +14726,7 @@
       <c r="T558" s="3"/>
       <c r="U558" s="3"/>
       <c r="V558" s="3"/>
+      <c r="W558" s="3"/>
     </row>
     <row r="559" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="2"/>
@@ -14123,6 +14751,7 @@
       <c r="T559" s="3"/>
       <c r="U559" s="3"/>
       <c r="V559" s="3"/>
+      <c r="W559" s="3"/>
     </row>
     <row r="560" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="2"/>
@@ -14147,6 +14776,7 @@
       <c r="T560" s="3"/>
       <c r="U560" s="3"/>
       <c r="V560" s="3"/>
+      <c r="W560" s="3"/>
     </row>
     <row r="561" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="2"/>
@@ -14171,6 +14801,7 @@
       <c r="T561" s="3"/>
       <c r="U561" s="3"/>
       <c r="V561" s="3"/>
+      <c r="W561" s="3"/>
     </row>
     <row r="562" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="2"/>
@@ -14195,6 +14826,7 @@
       <c r="T562" s="3"/>
       <c r="U562" s="3"/>
       <c r="V562" s="3"/>
+      <c r="W562" s="3"/>
     </row>
     <row r="563" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="2"/>
@@ -14219,6 +14851,7 @@
       <c r="T563" s="3"/>
       <c r="U563" s="3"/>
       <c r="V563" s="3"/>
+      <c r="W563" s="3"/>
     </row>
     <row r="564" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="2"/>
@@ -14243,6 +14876,7 @@
       <c r="T564" s="3"/>
       <c r="U564" s="3"/>
       <c r="V564" s="3"/>
+      <c r="W564" s="3"/>
     </row>
     <row r="565" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="2"/>
@@ -14267,6 +14901,7 @@
       <c r="T565" s="3"/>
       <c r="U565" s="3"/>
       <c r="V565" s="3"/>
+      <c r="W565" s="3"/>
     </row>
     <row r="566" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="2"/>
@@ -14291,6 +14926,7 @@
       <c r="T566" s="3"/>
       <c r="U566" s="3"/>
       <c r="V566" s="3"/>
+      <c r="W566" s="3"/>
     </row>
     <row r="567" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="2"/>
@@ -14315,6 +14951,7 @@
       <c r="T567" s="3"/>
       <c r="U567" s="3"/>
       <c r="V567" s="3"/>
+      <c r="W567" s="3"/>
     </row>
     <row r="568" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="2"/>
@@ -14339,6 +14976,7 @@
       <c r="T568" s="3"/>
       <c r="U568" s="3"/>
       <c r="V568" s="3"/>
+      <c r="W568" s="3"/>
     </row>
     <row r="569" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="2"/>
@@ -14363,6 +15001,7 @@
       <c r="T569" s="3"/>
       <c r="U569" s="3"/>
       <c r="V569" s="3"/>
+      <c r="W569" s="3"/>
     </row>
     <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="2"/>
@@ -14387,6 +15026,7 @@
       <c r="T570" s="3"/>
       <c r="U570" s="3"/>
       <c r="V570" s="3"/>
+      <c r="W570" s="3"/>
     </row>
     <row r="571" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="2"/>
@@ -14411,6 +15051,7 @@
       <c r="T571" s="3"/>
       <c r="U571" s="3"/>
       <c r="V571" s="3"/>
+      <c r="W571" s="3"/>
     </row>
     <row r="572" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="2"/>
@@ -14435,6 +15076,7 @@
       <c r="T572" s="3"/>
       <c r="U572" s="3"/>
       <c r="V572" s="3"/>
+      <c r="W572" s="3"/>
     </row>
     <row r="573" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="2"/>
@@ -14459,6 +15101,7 @@
       <c r="T573" s="3"/>
       <c r="U573" s="3"/>
       <c r="V573" s="3"/>
+      <c r="W573" s="3"/>
     </row>
     <row r="574" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="2"/>
@@ -14483,6 +15126,7 @@
       <c r="T574" s="3"/>
       <c r="U574" s="3"/>
       <c r="V574" s="3"/>
+      <c r="W574" s="3"/>
     </row>
     <row r="575" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="2"/>
@@ -14507,6 +15151,7 @@
       <c r="T575" s="3"/>
       <c r="U575" s="3"/>
       <c r="V575" s="3"/>
+      <c r="W575" s="3"/>
     </row>
     <row r="576" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="2"/>
@@ -14531,6 +15176,7 @@
       <c r="T576" s="3"/>
       <c r="U576" s="3"/>
       <c r="V576" s="3"/>
+      <c r="W576" s="3"/>
     </row>
     <row r="577" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="2"/>
@@ -14555,6 +15201,7 @@
       <c r="T577" s="3"/>
       <c r="U577" s="3"/>
       <c r="V577" s="3"/>
+      <c r="W577" s="3"/>
     </row>
     <row r="578" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="2"/>
@@ -14579,6 +15226,7 @@
       <c r="T578" s="3"/>
       <c r="U578" s="3"/>
       <c r="V578" s="3"/>
+      <c r="W578" s="3"/>
     </row>
     <row r="579" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="2"/>
@@ -14603,6 +15251,7 @@
       <c r="T579" s="3"/>
       <c r="U579" s="3"/>
       <c r="V579" s="3"/>
+      <c r="W579" s="3"/>
     </row>
     <row r="580" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="2"/>
@@ -14627,6 +15276,7 @@
       <c r="T580" s="3"/>
       <c r="U580" s="3"/>
       <c r="V580" s="3"/>
+      <c r="W580" s="3"/>
     </row>
     <row r="581" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="2"/>
@@ -14651,6 +15301,7 @@
       <c r="T581" s="3"/>
       <c r="U581" s="3"/>
       <c r="V581" s="3"/>
+      <c r="W581" s="3"/>
     </row>
     <row r="582" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="2"/>
@@ -14675,6 +15326,7 @@
       <c r="T582" s="3"/>
       <c r="U582" s="3"/>
       <c r="V582" s="3"/>
+      <c r="W582" s="3"/>
     </row>
     <row r="583" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="2"/>
@@ -14699,6 +15351,7 @@
       <c r="T583" s="3"/>
       <c r="U583" s="3"/>
       <c r="V583" s="3"/>
+      <c r="W583" s="3"/>
     </row>
     <row r="584" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="2"/>
@@ -14723,6 +15376,7 @@
       <c r="T584" s="3"/>
       <c r="U584" s="3"/>
       <c r="V584" s="3"/>
+      <c r="W584" s="3"/>
     </row>
     <row r="585" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="2"/>
@@ -14747,6 +15401,7 @@
       <c r="T585" s="3"/>
       <c r="U585" s="3"/>
       <c r="V585" s="3"/>
+      <c r="W585" s="3"/>
     </row>
     <row r="586" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="2"/>
@@ -14771,6 +15426,7 @@
       <c r="T586" s="3"/>
       <c r="U586" s="3"/>
       <c r="V586" s="3"/>
+      <c r="W586" s="3"/>
     </row>
     <row r="587" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="2"/>
@@ -14795,6 +15451,7 @@
       <c r="T587" s="3"/>
       <c r="U587" s="3"/>
       <c r="V587" s="3"/>
+      <c r="W587" s="3"/>
     </row>
     <row r="588" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="2"/>
@@ -14819,6 +15476,7 @@
       <c r="T588" s="3"/>
       <c r="U588" s="3"/>
       <c r="V588" s="3"/>
+      <c r="W588" s="3"/>
     </row>
     <row r="589" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="2"/>
@@ -14843,6 +15501,7 @@
       <c r="T589" s="3"/>
       <c r="U589" s="3"/>
       <c r="V589" s="3"/>
+      <c r="W589" s="3"/>
     </row>
     <row r="590" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="2"/>
@@ -14867,6 +15526,7 @@
       <c r="T590" s="3"/>
       <c r="U590" s="3"/>
       <c r="V590" s="3"/>
+      <c r="W590" s="3"/>
     </row>
     <row r="591" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="2"/>
@@ -14891,6 +15551,7 @@
       <c r="T591" s="3"/>
       <c r="U591" s="3"/>
       <c r="V591" s="3"/>
+      <c r="W591" s="3"/>
     </row>
     <row r="592" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="2"/>
@@ -14915,6 +15576,7 @@
       <c r="T592" s="3"/>
       <c r="U592" s="3"/>
       <c r="V592" s="3"/>
+      <c r="W592" s="3"/>
     </row>
     <row r="593" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="2"/>
@@ -14939,6 +15601,7 @@
       <c r="T593" s="3"/>
       <c r="U593" s="3"/>
       <c r="V593" s="3"/>
+      <c r="W593" s="3"/>
     </row>
     <row r="594" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="2"/>
@@ -14963,6 +15626,7 @@
       <c r="T594" s="3"/>
       <c r="U594" s="3"/>
       <c r="V594" s="3"/>
+      <c r="W594" s="3"/>
     </row>
     <row r="595" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="2"/>
@@ -14987,6 +15651,7 @@
       <c r="T595" s="3"/>
       <c r="U595" s="3"/>
       <c r="V595" s="3"/>
+      <c r="W595" s="3"/>
     </row>
     <row r="596" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="2"/>
@@ -15011,6 +15676,7 @@
       <c r="T596" s="3"/>
       <c r="U596" s="3"/>
       <c r="V596" s="3"/>
+      <c r="W596" s="3"/>
     </row>
     <row r="597" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="2"/>
@@ -15035,6 +15701,7 @@
       <c r="T597" s="3"/>
       <c r="U597" s="3"/>
       <c r="V597" s="3"/>
+      <c r="W597" s="3"/>
     </row>
     <row r="598" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="2"/>
@@ -15059,6 +15726,7 @@
       <c r="T598" s="3"/>
       <c r="U598" s="3"/>
       <c r="V598" s="3"/>
+      <c r="W598" s="3"/>
     </row>
     <row r="599" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="2"/>
@@ -15083,6 +15751,7 @@
       <c r="T599" s="3"/>
       <c r="U599" s="3"/>
       <c r="V599" s="3"/>
+      <c r="W599" s="3"/>
     </row>
     <row r="600" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="2"/>
@@ -15107,6 +15776,7 @@
       <c r="T600" s="3"/>
       <c r="U600" s="3"/>
       <c r="V600" s="3"/>
+      <c r="W600" s="3"/>
     </row>
     <row r="601" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="2"/>
@@ -15131,6 +15801,7 @@
       <c r="T601" s="3"/>
       <c r="U601" s="3"/>
       <c r="V601" s="3"/>
+      <c r="W601" s="3"/>
     </row>
     <row r="602" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="2"/>
@@ -15155,6 +15826,7 @@
       <c r="T602" s="3"/>
       <c r="U602" s="3"/>
       <c r="V602" s="3"/>
+      <c r="W602" s="3"/>
     </row>
     <row r="603" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="2"/>
@@ -15179,6 +15851,7 @@
       <c r="T603" s="3"/>
       <c r="U603" s="3"/>
       <c r="V603" s="3"/>
+      <c r="W603" s="3"/>
     </row>
     <row r="604" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="2"/>
@@ -15203,6 +15876,7 @@
       <c r="T604" s="3"/>
       <c r="U604" s="3"/>
       <c r="V604" s="3"/>
+      <c r="W604" s="3"/>
     </row>
     <row r="605" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="2"/>
@@ -15227,6 +15901,7 @@
       <c r="T605" s="3"/>
       <c r="U605" s="3"/>
       <c r="V605" s="3"/>
+      <c r="W605" s="3"/>
     </row>
     <row r="606" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="2"/>
@@ -15251,6 +15926,7 @@
       <c r="T606" s="3"/>
       <c r="U606" s="3"/>
       <c r="V606" s="3"/>
+      <c r="W606" s="3"/>
     </row>
     <row r="607" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="2"/>
@@ -15275,6 +15951,7 @@
       <c r="T607" s="3"/>
       <c r="U607" s="3"/>
       <c r="V607" s="3"/>
+      <c r="W607" s="3"/>
     </row>
     <row r="608" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="2"/>
@@ -15299,6 +15976,7 @@
       <c r="T608" s="3"/>
       <c r="U608" s="3"/>
       <c r="V608" s="3"/>
+      <c r="W608" s="3"/>
     </row>
     <row r="609" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="2"/>
@@ -15323,6 +16001,7 @@
       <c r="T609" s="3"/>
       <c r="U609" s="3"/>
       <c r="V609" s="3"/>
+      <c r="W609" s="3"/>
     </row>
     <row r="610" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="2"/>
@@ -15347,6 +16026,7 @@
       <c r="T610" s="3"/>
       <c r="U610" s="3"/>
       <c r="V610" s="3"/>
+      <c r="W610" s="3"/>
     </row>
     <row r="611" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="2"/>
@@ -15371,6 +16051,7 @@
       <c r="T611" s="3"/>
       <c r="U611" s="3"/>
       <c r="V611" s="3"/>
+      <c r="W611" s="3"/>
     </row>
     <row r="612" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="2"/>
@@ -15395,6 +16076,7 @@
       <c r="T612" s="3"/>
       <c r="U612" s="3"/>
       <c r="V612" s="3"/>
+      <c r="W612" s="3"/>
     </row>
     <row r="613" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="2"/>
@@ -15419,6 +16101,7 @@
       <c r="T613" s="3"/>
       <c r="U613" s="3"/>
       <c r="V613" s="3"/>
+      <c r="W613" s="3"/>
     </row>
     <row r="614" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="2"/>
@@ -15443,6 +16126,7 @@
       <c r="T614" s="3"/>
       <c r="U614" s="3"/>
       <c r="V614" s="3"/>
+      <c r="W614" s="3"/>
     </row>
     <row r="615" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="2"/>
@@ -15467,6 +16151,7 @@
       <c r="T615" s="3"/>
       <c r="U615" s="3"/>
       <c r="V615" s="3"/>
+      <c r="W615" s="3"/>
     </row>
     <row r="616" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="2"/>
@@ -15491,6 +16176,7 @@
       <c r="T616" s="3"/>
       <c r="U616" s="3"/>
       <c r="V616" s="3"/>
+      <c r="W616" s="3"/>
     </row>
     <row r="617" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="2"/>
@@ -15515,6 +16201,7 @@
       <c r="T617" s="3"/>
       <c r="U617" s="3"/>
       <c r="V617" s="3"/>
+      <c r="W617" s="3"/>
     </row>
     <row r="618" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="2"/>
@@ -15539,6 +16226,7 @@
       <c r="T618" s="3"/>
       <c r="U618" s="3"/>
       <c r="V618" s="3"/>
+      <c r="W618" s="3"/>
     </row>
     <row r="619" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="2"/>
@@ -15563,6 +16251,7 @@
       <c r="T619" s="3"/>
       <c r="U619" s="3"/>
       <c r="V619" s="3"/>
+      <c r="W619" s="3"/>
     </row>
     <row r="620" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="2"/>
@@ -15587,6 +16276,7 @@
       <c r="T620" s="3"/>
       <c r="U620" s="3"/>
       <c r="V620" s="3"/>
+      <c r="W620" s="3"/>
     </row>
     <row r="621" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="2"/>
@@ -15611,6 +16301,7 @@
       <c r="T621" s="3"/>
       <c r="U621" s="3"/>
       <c r="V621" s="3"/>
+      <c r="W621" s="3"/>
     </row>
     <row r="622" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="2"/>
@@ -15635,6 +16326,7 @@
       <c r="T622" s="3"/>
       <c r="U622" s="3"/>
       <c r="V622" s="3"/>
+      <c r="W622" s="3"/>
     </row>
     <row r="623" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="2"/>
@@ -15659,6 +16351,7 @@
       <c r="T623" s="3"/>
       <c r="U623" s="3"/>
       <c r="V623" s="3"/>
+      <c r="W623" s="3"/>
     </row>
     <row r="624" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="2"/>
@@ -15683,6 +16376,7 @@
       <c r="T624" s="3"/>
       <c r="U624" s="3"/>
       <c r="V624" s="3"/>
+      <c r="W624" s="3"/>
     </row>
     <row r="625" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="2"/>
@@ -15707,6 +16401,7 @@
       <c r="T625" s="3"/>
       <c r="U625" s="3"/>
       <c r="V625" s="3"/>
+      <c r="W625" s="3"/>
     </row>
     <row r="626" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="2"/>
@@ -15731,6 +16426,7 @@
       <c r="T626" s="3"/>
       <c r="U626" s="3"/>
       <c r="V626" s="3"/>
+      <c r="W626" s="3"/>
     </row>
     <row r="627" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="2"/>
@@ -15755,6 +16451,7 @@
       <c r="T627" s="3"/>
       <c r="U627" s="3"/>
       <c r="V627" s="3"/>
+      <c r="W627" s="3"/>
     </row>
     <row r="628" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="2"/>
@@ -15779,6 +16476,7 @@
       <c r="T628" s="3"/>
       <c r="U628" s="3"/>
       <c r="V628" s="3"/>
+      <c r="W628" s="3"/>
     </row>
     <row r="629" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="2"/>
@@ -15803,6 +16501,7 @@
       <c r="T629" s="3"/>
       <c r="U629" s="3"/>
       <c r="V629" s="3"/>
+      <c r="W629" s="3"/>
     </row>
     <row r="630" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="2"/>
@@ -15827,6 +16526,7 @@
       <c r="T630" s="3"/>
       <c r="U630" s="3"/>
       <c r="V630" s="3"/>
+      <c r="W630" s="3"/>
     </row>
     <row r="631" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="2"/>
@@ -15851,6 +16551,7 @@
       <c r="T631" s="3"/>
       <c r="U631" s="3"/>
       <c r="V631" s="3"/>
+      <c r="W631" s="3"/>
     </row>
     <row r="632" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="2"/>
@@ -15875,6 +16576,7 @@
       <c r="T632" s="3"/>
       <c r="U632" s="3"/>
       <c r="V632" s="3"/>
+      <c r="W632" s="3"/>
     </row>
     <row r="633" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="2"/>
@@ -15899,6 +16601,7 @@
       <c r="T633" s="3"/>
       <c r="U633" s="3"/>
       <c r="V633" s="3"/>
+      <c r="W633" s="3"/>
     </row>
     <row r="634" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="2"/>
@@ -15923,6 +16626,7 @@
       <c r="T634" s="3"/>
       <c r="U634" s="3"/>
       <c r="V634" s="3"/>
+      <c r="W634" s="3"/>
     </row>
     <row r="635" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="2"/>
@@ -15947,6 +16651,7 @@
       <c r="T635" s="3"/>
       <c r="U635" s="3"/>
       <c r="V635" s="3"/>
+      <c r="W635" s="3"/>
     </row>
     <row r="636" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="2"/>
@@ -15971,6 +16676,7 @@
       <c r="T636" s="3"/>
       <c r="U636" s="3"/>
       <c r="V636" s="3"/>
+      <c r="W636" s="3"/>
     </row>
     <row r="637" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="2"/>
@@ -15995,6 +16701,7 @@
       <c r="T637" s="3"/>
       <c r="U637" s="3"/>
       <c r="V637" s="3"/>
+      <c r="W637" s="3"/>
     </row>
     <row r="638" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="2"/>
@@ -16019,6 +16726,7 @@
       <c r="T638" s="3"/>
       <c r="U638" s="3"/>
       <c r="V638" s="3"/>
+      <c r="W638" s="3"/>
     </row>
     <row r="639" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="2"/>
@@ -16043,6 +16751,7 @@
       <c r="T639" s="3"/>
       <c r="U639" s="3"/>
       <c r="V639" s="3"/>
+      <c r="W639" s="3"/>
     </row>
     <row r="640" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="2"/>
@@ -16067,6 +16776,7 @@
       <c r="T640" s="3"/>
       <c r="U640" s="3"/>
       <c r="V640" s="3"/>
+      <c r="W640" s="3"/>
     </row>
     <row r="641" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="2"/>
@@ -16091,6 +16801,7 @@
       <c r="T641" s="3"/>
       <c r="U641" s="3"/>
       <c r="V641" s="3"/>
+      <c r="W641" s="3"/>
     </row>
     <row r="642" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="2"/>
@@ -16115,6 +16826,7 @@
       <c r="T642" s="3"/>
       <c r="U642" s="3"/>
       <c r="V642" s="3"/>
+      <c r="W642" s="3"/>
     </row>
     <row r="643" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="2"/>
@@ -16139,6 +16851,7 @@
       <c r="T643" s="3"/>
       <c r="U643" s="3"/>
       <c r="V643" s="3"/>
+      <c r="W643" s="3"/>
     </row>
     <row r="644" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="2"/>
@@ -16163,6 +16876,7 @@
       <c r="T644" s="3"/>
       <c r="U644" s="3"/>
       <c r="V644" s="3"/>
+      <c r="W644" s="3"/>
     </row>
     <row r="645" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="2"/>
@@ -16187,6 +16901,7 @@
       <c r="T645" s="3"/>
       <c r="U645" s="3"/>
       <c r="V645" s="3"/>
+      <c r="W645" s="3"/>
     </row>
     <row r="646" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="2"/>
@@ -16211,6 +16926,7 @@
       <c r="T646" s="3"/>
       <c r="U646" s="3"/>
       <c r="V646" s="3"/>
+      <c r="W646" s="3"/>
     </row>
     <row r="647" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="2"/>
@@ -16235,6 +16951,7 @@
       <c r="T647" s="3"/>
       <c r="U647" s="3"/>
       <c r="V647" s="3"/>
+      <c r="W647" s="3"/>
     </row>
     <row r="648" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="2"/>
@@ -16259,6 +16976,7 @@
       <c r="T648" s="3"/>
       <c r="U648" s="3"/>
       <c r="V648" s="3"/>
+      <c r="W648" s="3"/>
     </row>
     <row r="649" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="2"/>
@@ -16283,6 +17001,7 @@
       <c r="T649" s="3"/>
       <c r="U649" s="3"/>
       <c r="V649" s="3"/>
+      <c r="W649" s="3"/>
     </row>
     <row r="650" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="2"/>
@@ -16307,6 +17026,7 @@
       <c r="T650" s="3"/>
       <c r="U650" s="3"/>
       <c r="V650" s="3"/>
+      <c r="W650" s="3"/>
     </row>
     <row r="651" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="2"/>
@@ -16331,6 +17051,7 @@
       <c r="T651" s="3"/>
       <c r="U651" s="3"/>
       <c r="V651" s="3"/>
+      <c r="W651" s="3"/>
     </row>
     <row r="652" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="2"/>
@@ -16355,6 +17076,7 @@
       <c r="T652" s="3"/>
       <c r="U652" s="3"/>
       <c r="V652" s="3"/>
+      <c r="W652" s="3"/>
     </row>
     <row r="653" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="2"/>
@@ -16379,6 +17101,7 @@
       <c r="T653" s="3"/>
       <c r="U653" s="3"/>
       <c r="V653" s="3"/>
+      <c r="W653" s="3"/>
     </row>
     <row r="654" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="2"/>
@@ -16403,6 +17126,7 @@
       <c r="T654" s="3"/>
       <c r="U654" s="3"/>
       <c r="V654" s="3"/>
+      <c r="W654" s="3"/>
     </row>
     <row r="655" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="2"/>
@@ -16427,6 +17151,7 @@
       <c r="T655" s="3"/>
       <c r="U655" s="3"/>
       <c r="V655" s="3"/>
+      <c r="W655" s="3"/>
     </row>
     <row r="656" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="2"/>
@@ -16451,6 +17176,7 @@
       <c r="T656" s="3"/>
       <c r="U656" s="3"/>
       <c r="V656" s="3"/>
+      <c r="W656" s="3"/>
     </row>
     <row r="657" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="2"/>
@@ -16475,6 +17201,7 @@
       <c r="T657" s="3"/>
       <c r="U657" s="3"/>
       <c r="V657" s="3"/>
+      <c r="W657" s="3"/>
     </row>
     <row r="658" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="2"/>
@@ -16499,6 +17226,7 @@
       <c r="T658" s="3"/>
       <c r="U658" s="3"/>
       <c r="V658" s="3"/>
+      <c r="W658" s="3"/>
     </row>
     <row r="659" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="2"/>
@@ -16523,6 +17251,7 @@
       <c r="T659" s="3"/>
       <c r="U659" s="3"/>
       <c r="V659" s="3"/>
+      <c r="W659" s="3"/>
     </row>
     <row r="660" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="2"/>
@@ -16547,6 +17276,7 @@
       <c r="T660" s="3"/>
       <c r="U660" s="3"/>
       <c r="V660" s="3"/>
+      <c r="W660" s="3"/>
     </row>
     <row r="661" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="2"/>
@@ -16571,6 +17301,7 @@
       <c r="T661" s="3"/>
       <c r="U661" s="3"/>
       <c r="V661" s="3"/>
+      <c r="W661" s="3"/>
     </row>
     <row r="662" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="2"/>
@@ -16595,6 +17326,7 @@
       <c r="T662" s="3"/>
       <c r="U662" s="3"/>
       <c r="V662" s="3"/>
+      <c r="W662" s="3"/>
     </row>
     <row r="663" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="2"/>
@@ -16619,6 +17351,7 @@
       <c r="T663" s="3"/>
       <c r="U663" s="3"/>
       <c r="V663" s="3"/>
+      <c r="W663" s="3"/>
     </row>
     <row r="664" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="2"/>
@@ -16643,6 +17376,7 @@
       <c r="T664" s="3"/>
       <c r="U664" s="3"/>
       <c r="V664" s="3"/>
+      <c r="W664" s="3"/>
     </row>
     <row r="665" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="2"/>
@@ -16667,6 +17401,7 @@
       <c r="T665" s="3"/>
       <c r="U665" s="3"/>
       <c r="V665" s="3"/>
+      <c r="W665" s="3"/>
     </row>
     <row r="666" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="2"/>
@@ -16691,6 +17426,7 @@
       <c r="T666" s="3"/>
       <c r="U666" s="3"/>
       <c r="V666" s="3"/>
+      <c r="W666" s="3"/>
     </row>
     <row r="667" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="2"/>
@@ -16715,6 +17451,7 @@
       <c r="T667" s="3"/>
       <c r="U667" s="3"/>
       <c r="V667" s="3"/>
+      <c r="W667" s="3"/>
     </row>
     <row r="668" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="2"/>
@@ -16739,6 +17476,7 @@
       <c r="T668" s="3"/>
       <c r="U668" s="3"/>
       <c r="V668" s="3"/>
+      <c r="W668" s="3"/>
     </row>
     <row r="669" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="2"/>
@@ -16763,6 +17501,7 @@
       <c r="T669" s="3"/>
       <c r="U669" s="3"/>
       <c r="V669" s="3"/>
+      <c r="W669" s="3"/>
     </row>
     <row r="670" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="2"/>
@@ -16787,6 +17526,7 @@
       <c r="T670" s="3"/>
       <c r="U670" s="3"/>
       <c r="V670" s="3"/>
+      <c r="W670" s="3"/>
     </row>
     <row r="671" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="2"/>
@@ -16811,6 +17551,7 @@
       <c r="T671" s="3"/>
       <c r="U671" s="3"/>
       <c r="V671" s="3"/>
+      <c r="W671" s="3"/>
     </row>
     <row r="672" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="2"/>
@@ -16835,6 +17576,7 @@
       <c r="T672" s="3"/>
       <c r="U672" s="3"/>
       <c r="V672" s="3"/>
+      <c r="W672" s="3"/>
     </row>
     <row r="673" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="2"/>
@@ -16859,6 +17601,7 @@
       <c r="T673" s="3"/>
       <c r="U673" s="3"/>
       <c r="V673" s="3"/>
+      <c r="W673" s="3"/>
     </row>
     <row r="674" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="2"/>
@@ -16883,6 +17626,7 @@
       <c r="T674" s="3"/>
       <c r="U674" s="3"/>
       <c r="V674" s="3"/>
+      <c r="W674" s="3"/>
     </row>
     <row r="675" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="2"/>
@@ -16907,6 +17651,7 @@
       <c r="T675" s="3"/>
       <c r="U675" s="3"/>
       <c r="V675" s="3"/>
+      <c r="W675" s="3"/>
     </row>
     <row r="676" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="2"/>
@@ -16931,6 +17676,7 @@
       <c r="T676" s="3"/>
       <c r="U676" s="3"/>
       <c r="V676" s="3"/>
+      <c r="W676" s="3"/>
     </row>
     <row r="677" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="2"/>
@@ -16955,6 +17701,7 @@
       <c r="T677" s="3"/>
       <c r="U677" s="3"/>
       <c r="V677" s="3"/>
+      <c r="W677" s="3"/>
     </row>
     <row r="678" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="2"/>
@@ -16979,6 +17726,7 @@
       <c r="T678" s="3"/>
       <c r="U678" s="3"/>
       <c r="V678" s="3"/>
+      <c r="W678" s="3"/>
     </row>
     <row r="679" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="2"/>
@@ -17003,6 +17751,7 @@
       <c r="T679" s="3"/>
       <c r="U679" s="3"/>
       <c r="V679" s="3"/>
+      <c r="W679" s="3"/>
     </row>
     <row r="680" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="2"/>
@@ -17027,6 +17776,7 @@
       <c r="T680" s="3"/>
       <c r="U680" s="3"/>
       <c r="V680" s="3"/>
+      <c r="W680" s="3"/>
     </row>
     <row r="681" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="2"/>
@@ -17051,6 +17801,7 @@
       <c r="T681" s="3"/>
       <c r="U681" s="3"/>
       <c r="V681" s="3"/>
+      <c r="W681" s="3"/>
     </row>
     <row r="682" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="2"/>
@@ -17075,6 +17826,7 @@
       <c r="T682" s="3"/>
       <c r="U682" s="3"/>
       <c r="V682" s="3"/>
+      <c r="W682" s="3"/>
     </row>
     <row r="683" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="2"/>
@@ -17099,6 +17851,7 @@
       <c r="T683" s="3"/>
       <c r="U683" s="3"/>
       <c r="V683" s="3"/>
+      <c r="W683" s="3"/>
     </row>
     <row r="684" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="2"/>
@@ -17123,6 +17876,7 @@
       <c r="T684" s="3"/>
       <c r="U684" s="3"/>
       <c r="V684" s="3"/>
+      <c r="W684" s="3"/>
     </row>
     <row r="685" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="2"/>
@@ -17147,6 +17901,7 @@
       <c r="T685" s="3"/>
       <c r="U685" s="3"/>
       <c r="V685" s="3"/>
+      <c r="W685" s="3"/>
     </row>
     <row r="686" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="2"/>
@@ -17171,6 +17926,7 @@
       <c r="T686" s="3"/>
       <c r="U686" s="3"/>
       <c r="V686" s="3"/>
+      <c r="W686" s="3"/>
     </row>
     <row r="687" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="2"/>
@@ -17195,6 +17951,7 @@
       <c r="T687" s="3"/>
       <c r="U687" s="3"/>
       <c r="V687" s="3"/>
+      <c r="W687" s="3"/>
     </row>
     <row r="688" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="2"/>
@@ -17219,6 +17976,7 @@
       <c r="T688" s="3"/>
       <c r="U688" s="3"/>
       <c r="V688" s="3"/>
+      <c r="W688" s="3"/>
     </row>
     <row r="689" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="2"/>
@@ -17243,6 +18001,7 @@
       <c r="T689" s="3"/>
       <c r="U689" s="3"/>
       <c r="V689" s="3"/>
+      <c r="W689" s="3"/>
     </row>
     <row r="690" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="2"/>
@@ -17267,6 +18026,7 @@
       <c r="T690" s="3"/>
       <c r="U690" s="3"/>
       <c r="V690" s="3"/>
+      <c r="W690" s="3"/>
     </row>
     <row r="691" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="2"/>
@@ -17291,6 +18051,7 @@
       <c r="T691" s="3"/>
       <c r="U691" s="3"/>
       <c r="V691" s="3"/>
+      <c r="W691" s="3"/>
     </row>
     <row r="692" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="2"/>
@@ -17315,6 +18076,7 @@
       <c r="T692" s="3"/>
       <c r="U692" s="3"/>
       <c r="V692" s="3"/>
+      <c r="W692" s="3"/>
     </row>
     <row r="693" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="2"/>
@@ -17339,6 +18101,7 @@
       <c r="T693" s="3"/>
       <c r="U693" s="3"/>
       <c r="V693" s="3"/>
+      <c r="W693" s="3"/>
     </row>
     <row r="694" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="2"/>
@@ -17363,6 +18126,7 @@
       <c r="T694" s="3"/>
       <c r="U694" s="3"/>
       <c r="V694" s="3"/>
+      <c r="W694" s="3"/>
     </row>
     <row r="695" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="2"/>
@@ -17387,6 +18151,7 @@
       <c r="T695" s="3"/>
       <c r="U695" s="3"/>
       <c r="V695" s="3"/>
+      <c r="W695" s="3"/>
     </row>
     <row r="696" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="2"/>
@@ -17411,6 +18176,7 @@
       <c r="T696" s="3"/>
       <c r="U696" s="3"/>
       <c r="V696" s="3"/>
+      <c r="W696" s="3"/>
     </row>
     <row r="697" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="2"/>
@@ -17435,6 +18201,7 @@
       <c r="T697" s="3"/>
       <c r="U697" s="3"/>
       <c r="V697" s="3"/>
+      <c r="W697" s="3"/>
     </row>
     <row r="698" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="2"/>
@@ -17459,6 +18226,7 @@
       <c r="T698" s="3"/>
       <c r="U698" s="3"/>
       <c r="V698" s="3"/>
+      <c r="W698" s="3"/>
     </row>
     <row r="699" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="2"/>
@@ -17483,6 +18251,7 @@
       <c r="T699" s="3"/>
       <c r="U699" s="3"/>
       <c r="V699" s="3"/>
+      <c r="W699" s="3"/>
     </row>
     <row r="700" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="2"/>
@@ -17507,6 +18276,7 @@
       <c r="T700" s="3"/>
       <c r="U700" s="3"/>
       <c r="V700" s="3"/>
+      <c r="W700" s="3"/>
     </row>
     <row r="701" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="2"/>
@@ -17531,6 +18301,7 @@
       <c r="T701" s="3"/>
       <c r="U701" s="3"/>
       <c r="V701" s="3"/>
+      <c r="W701" s="3"/>
     </row>
     <row r="702" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="2"/>
@@ -17555,6 +18326,7 @@
       <c r="T702" s="3"/>
       <c r="U702" s="3"/>
       <c r="V702" s="3"/>
+      <c r="W702" s="3"/>
     </row>
     <row r="703" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="2"/>
@@ -17579,6 +18351,7 @@
       <c r="T703" s="3"/>
       <c r="U703" s="3"/>
       <c r="V703" s="3"/>
+      <c r="W703" s="3"/>
     </row>
     <row r="704" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="2"/>
@@ -17603,6 +18376,7 @@
       <c r="T704" s="3"/>
       <c r="U704" s="3"/>
       <c r="V704" s="3"/>
+      <c r="W704" s="3"/>
     </row>
     <row r="705" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="2"/>
@@ -17627,6 +18401,7 @@
       <c r="T705" s="3"/>
       <c r="U705" s="3"/>
       <c r="V705" s="3"/>
+      <c r="W705" s="3"/>
     </row>
     <row r="706" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="2"/>
@@ -17651,6 +18426,7 @@
       <c r="T706" s="3"/>
       <c r="U706" s="3"/>
       <c r="V706" s="3"/>
+      <c r="W706" s="3"/>
     </row>
     <row r="707" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="2"/>
@@ -17675,6 +18451,7 @@
       <c r="T707" s="3"/>
       <c r="U707" s="3"/>
       <c r="V707" s="3"/>
+      <c r="W707" s="3"/>
     </row>
     <row r="708" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="2"/>
@@ -17699,6 +18476,7 @@
       <c r="T708" s="3"/>
       <c r="U708" s="3"/>
       <c r="V708" s="3"/>
+      <c r="W708" s="3"/>
     </row>
     <row r="709" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="2"/>
@@ -17723,6 +18501,7 @@
       <c r="T709" s="3"/>
       <c r="U709" s="3"/>
       <c r="V709" s="3"/>
+      <c r="W709" s="3"/>
     </row>
     <row r="710" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="2"/>
@@ -17747,6 +18526,7 @@
       <c r="T710" s="3"/>
       <c r="U710" s="3"/>
       <c r="V710" s="3"/>
+      <c r="W710" s="3"/>
     </row>
     <row r="711" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="2"/>
@@ -17771,6 +18551,7 @@
       <c r="T711" s="3"/>
       <c r="U711" s="3"/>
       <c r="V711" s="3"/>
+      <c r="W711" s="3"/>
     </row>
     <row r="712" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="2"/>
@@ -17795,6 +18576,7 @@
       <c r="T712" s="3"/>
       <c r="U712" s="3"/>
       <c r="V712" s="3"/>
+      <c r="W712" s="3"/>
     </row>
     <row r="713" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="2"/>
@@ -17819,6 +18601,7 @@
       <c r="T713" s="3"/>
       <c r="U713" s="3"/>
       <c r="V713" s="3"/>
+      <c r="W713" s="3"/>
     </row>
     <row r="714" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="2"/>
@@ -17843,6 +18626,7 @@
       <c r="T714" s="3"/>
       <c r="U714" s="3"/>
       <c r="V714" s="3"/>
+      <c r="W714" s="3"/>
     </row>
     <row r="715" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="2"/>
@@ -17867,6 +18651,7 @@
       <c r="T715" s="3"/>
       <c r="U715" s="3"/>
       <c r="V715" s="3"/>
+      <c r="W715" s="3"/>
     </row>
     <row r="716" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="2"/>
@@ -17891,6 +18676,7 @@
       <c r="T716" s="3"/>
       <c r="U716" s="3"/>
       <c r="V716" s="3"/>
+      <c r="W716" s="3"/>
     </row>
     <row r="717" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="2"/>
@@ -17915,6 +18701,7 @@
       <c r="T717" s="3"/>
       <c r="U717" s="3"/>
       <c r="V717" s="3"/>
+      <c r="W717" s="3"/>
     </row>
     <row r="718" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="2"/>
@@ -17939,6 +18726,7 @@
       <c r="T718" s="3"/>
       <c r="U718" s="3"/>
       <c r="V718" s="3"/>
+      <c r="W718" s="3"/>
     </row>
     <row r="719" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="2"/>
@@ -17963,6 +18751,7 @@
       <c r="T719" s="3"/>
       <c r="U719" s="3"/>
       <c r="V719" s="3"/>
+      <c r="W719" s="3"/>
     </row>
     <row r="720" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="2"/>
@@ -17987,6 +18776,7 @@
       <c r="T720" s="3"/>
       <c r="U720" s="3"/>
       <c r="V720" s="3"/>
+      <c r="W720" s="3"/>
     </row>
     <row r="721" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="2"/>
@@ -18011,6 +18801,7 @@
       <c r="T721" s="3"/>
       <c r="U721" s="3"/>
       <c r="V721" s="3"/>
+      <c r="W721" s="3"/>
     </row>
     <row r="722" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="2"/>
@@ -18035,6 +18826,7 @@
       <c r="T722" s="3"/>
       <c r="U722" s="3"/>
       <c r="V722" s="3"/>
+      <c r="W722" s="3"/>
     </row>
     <row r="723" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="2"/>
@@ -18059,6 +18851,7 @@
       <c r="T723" s="3"/>
       <c r="U723" s="3"/>
       <c r="V723" s="3"/>
+      <c r="W723" s="3"/>
     </row>
     <row r="724" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="2"/>
@@ -18083,6 +18876,7 @@
       <c r="T724" s="3"/>
       <c r="U724" s="3"/>
       <c r="V724" s="3"/>
+      <c r="W724" s="3"/>
     </row>
     <row r="725" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="2"/>
@@ -18107,6 +18901,7 @@
       <c r="T725" s="3"/>
       <c r="U725" s="3"/>
       <c r="V725" s="3"/>
+      <c r="W725" s="3"/>
     </row>
     <row r="726" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="2"/>
@@ -18131,6 +18926,7 @@
       <c r="T726" s="3"/>
       <c r="U726" s="3"/>
       <c r="V726" s="3"/>
+      <c r="W726" s="3"/>
     </row>
     <row r="727" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="2"/>
@@ -18155,6 +18951,7 @@
       <c r="T727" s="3"/>
       <c r="U727" s="3"/>
       <c r="V727" s="3"/>
+      <c r="W727" s="3"/>
     </row>
     <row r="728" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="2"/>
@@ -18179,6 +18976,7 @@
       <c r="T728" s="3"/>
       <c r="U728" s="3"/>
       <c r="V728" s="3"/>
+      <c r="W728" s="3"/>
     </row>
     <row r="729" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="2"/>
@@ -18203,6 +19001,7 @@
       <c r="T729" s="3"/>
       <c r="U729" s="3"/>
       <c r="V729" s="3"/>
+      <c r="W729" s="3"/>
     </row>
     <row r="730" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="2"/>
@@ -18227,6 +19026,7 @@
       <c r="T730" s="3"/>
       <c r="U730" s="3"/>
       <c r="V730" s="3"/>
+      <c r="W730" s="3"/>
     </row>
     <row r="731" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="2"/>
@@ -18251,6 +19051,7 @@
       <c r="T731" s="3"/>
       <c r="U731" s="3"/>
       <c r="V731" s="3"/>
+      <c r="W731" s="3"/>
     </row>
     <row r="732" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="2"/>
@@ -18275,6 +19076,7 @@
       <c r="T732" s="3"/>
       <c r="U732" s="3"/>
       <c r="V732" s="3"/>
+      <c r="W732" s="3"/>
     </row>
     <row r="733" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="2"/>
@@ -18299,6 +19101,7 @@
       <c r="T733" s="3"/>
       <c r="U733" s="3"/>
       <c r="V733" s="3"/>
+      <c r="W733" s="3"/>
     </row>
     <row r="734" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="2"/>
@@ -18323,6 +19126,7 @@
       <c r="T734" s="3"/>
       <c r="U734" s="3"/>
       <c r="V734" s="3"/>
+      <c r="W734" s="3"/>
     </row>
     <row r="735" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="2"/>
@@ -18347,6 +19151,7 @@
       <c r="T735" s="3"/>
       <c r="U735" s="3"/>
       <c r="V735" s="3"/>
+      <c r="W735" s="3"/>
     </row>
     <row r="736" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="2"/>
@@ -18371,6 +19176,7 @@
       <c r="T736" s="3"/>
       <c r="U736" s="3"/>
       <c r="V736" s="3"/>
+      <c r="W736" s="3"/>
     </row>
     <row r="737" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="2"/>
@@ -18395,6 +19201,7 @@
       <c r="T737" s="3"/>
       <c r="U737" s="3"/>
       <c r="V737" s="3"/>
+      <c r="W737" s="3"/>
     </row>
     <row r="738" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="2"/>
@@ -18419,6 +19226,7 @@
       <c r="T738" s="3"/>
       <c r="U738" s="3"/>
       <c r="V738" s="3"/>
+      <c r="W738" s="3"/>
     </row>
     <row r="739" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="2"/>
@@ -18443,6 +19251,7 @@
       <c r="T739" s="3"/>
       <c r="U739" s="3"/>
       <c r="V739" s="3"/>
+      <c r="W739" s="3"/>
     </row>
     <row r="740" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="2"/>
@@ -18467,6 +19276,7 @@
       <c r="T740" s="3"/>
       <c r="U740" s="3"/>
       <c r="V740" s="3"/>
+      <c r="W740" s="3"/>
     </row>
     <row r="741" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="2"/>
@@ -18491,6 +19301,7 @@
       <c r="T741" s="3"/>
       <c r="U741" s="3"/>
       <c r="V741" s="3"/>
+      <c r="W741" s="3"/>
     </row>
     <row r="742" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="2"/>
@@ -18515,6 +19326,7 @@
       <c r="T742" s="3"/>
       <c r="U742" s="3"/>
       <c r="V742" s="3"/>
+      <c r="W742" s="3"/>
     </row>
     <row r="743" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="2"/>
@@ -18539,6 +19351,7 @@
       <c r="T743" s="3"/>
       <c r="U743" s="3"/>
       <c r="V743" s="3"/>
+      <c r="W743" s="3"/>
     </row>
     <row r="744" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="2"/>
@@ -18563,6 +19376,7 @@
       <c r="T744" s="3"/>
       <c r="U744" s="3"/>
       <c r="V744" s="3"/>
+      <c r="W744" s="3"/>
     </row>
     <row r="745" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="2"/>
@@ -18587,6 +19401,7 @@
       <c r="T745" s="3"/>
       <c r="U745" s="3"/>
       <c r="V745" s="3"/>
+      <c r="W745" s="3"/>
     </row>
     <row r="746" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="2"/>
@@ -18611,6 +19426,7 @@
       <c r="T746" s="3"/>
       <c r="U746" s="3"/>
       <c r="V746" s="3"/>
+      <c r="W746" s="3"/>
     </row>
     <row r="747" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="2"/>
@@ -18635,6 +19451,7 @@
       <c r="T747" s="3"/>
       <c r="U747" s="3"/>
       <c r="V747" s="3"/>
+      <c r="W747" s="3"/>
     </row>
     <row r="748" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="2"/>
@@ -18659,6 +19476,7 @@
       <c r="T748" s="3"/>
       <c r="U748" s="3"/>
       <c r="V748" s="3"/>
+      <c r="W748" s="3"/>
     </row>
     <row r="749" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="2"/>
@@ -18683,6 +19501,7 @@
       <c r="T749" s="3"/>
       <c r="U749" s="3"/>
       <c r="V749" s="3"/>
+      <c r="W749" s="3"/>
     </row>
     <row r="750" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="2"/>
@@ -18707,6 +19526,7 @@
       <c r="T750" s="3"/>
       <c r="U750" s="3"/>
       <c r="V750" s="3"/>
+      <c r="W750" s="3"/>
     </row>
     <row r="751" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="2"/>
@@ -18731,6 +19551,7 @@
       <c r="T751" s="3"/>
       <c r="U751" s="3"/>
       <c r="V751" s="3"/>
+      <c r="W751" s="3"/>
     </row>
     <row r="752" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="2"/>
@@ -18755,6 +19576,7 @@
       <c r="T752" s="3"/>
       <c r="U752" s="3"/>
       <c r="V752" s="3"/>
+      <c r="W752" s="3"/>
     </row>
     <row r="753" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="2"/>
@@ -18779,6 +19601,7 @@
       <c r="T753" s="3"/>
       <c r="U753" s="3"/>
       <c r="V753" s="3"/>
+      <c r="W753" s="3"/>
     </row>
     <row r="754" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="2"/>
@@ -18803,6 +19626,7 @@
       <c r="T754" s="3"/>
       <c r="U754" s="3"/>
       <c r="V754" s="3"/>
+      <c r="W754" s="3"/>
     </row>
     <row r="755" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="2"/>
@@ -18827,6 +19651,7 @@
       <c r="T755" s="3"/>
       <c r="U755" s="3"/>
       <c r="V755" s="3"/>
+      <c r="W755" s="3"/>
     </row>
     <row r="756" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="2"/>
@@ -18851,6 +19676,7 @@
       <c r="T756" s="3"/>
       <c r="U756" s="3"/>
       <c r="V756" s="3"/>
+      <c r="W756" s="3"/>
     </row>
     <row r="757" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="2"/>
@@ -18875,6 +19701,7 @@
       <c r="T757" s="3"/>
       <c r="U757" s="3"/>
       <c r="V757" s="3"/>
+      <c r="W757" s="3"/>
     </row>
     <row r="758" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="2"/>
@@ -18899,6 +19726,7 @@
       <c r="T758" s="3"/>
       <c r="U758" s="3"/>
       <c r="V758" s="3"/>
+      <c r="W758" s="3"/>
     </row>
     <row r="759" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="2"/>
@@ -18923,6 +19751,7 @@
       <c r="T759" s="3"/>
       <c r="U759" s="3"/>
       <c r="V759" s="3"/>
+      <c r="W759" s="3"/>
     </row>
     <row r="760" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="2"/>
@@ -18947,6 +19776,7 @@
       <c r="T760" s="3"/>
       <c r="U760" s="3"/>
       <c r="V760" s="3"/>
+      <c r="W760" s="3"/>
     </row>
     <row r="761" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="2"/>
@@ -18971,6 +19801,7 @@
       <c r="T761" s="3"/>
       <c r="U761" s="3"/>
       <c r="V761" s="3"/>
+      <c r="W761" s="3"/>
     </row>
     <row r="762" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="2"/>
@@ -18995,6 +19826,7 @@
       <c r="T762" s="3"/>
       <c r="U762" s="3"/>
       <c r="V762" s="3"/>
+      <c r="W762" s="3"/>
     </row>
     <row r="763" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="2"/>
@@ -19019,6 +19851,7 @@
       <c r="T763" s="3"/>
       <c r="U763" s="3"/>
       <c r="V763" s="3"/>
+      <c r="W763" s="3"/>
     </row>
     <row r="764" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="2"/>
@@ -19043,6 +19876,7 @@
       <c r="T764" s="3"/>
       <c r="U764" s="3"/>
       <c r="V764" s="3"/>
+      <c r="W764" s="3"/>
     </row>
     <row r="765" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="2"/>
@@ -19067,6 +19901,7 @@
       <c r="T765" s="3"/>
       <c r="U765" s="3"/>
       <c r="V765" s="3"/>
+      <c r="W765" s="3"/>
     </row>
     <row r="766" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="2"/>
@@ -19091,6 +19926,7 @@
       <c r="T766" s="3"/>
       <c r="U766" s="3"/>
       <c r="V766" s="3"/>
+      <c r="W766" s="3"/>
     </row>
     <row r="767" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="2"/>
@@ -19115,6 +19951,7 @@
       <c r="T767" s="3"/>
       <c r="U767" s="3"/>
       <c r="V767" s="3"/>
+      <c r="W767" s="3"/>
     </row>
     <row r="768" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="2"/>
@@ -19139,6 +19976,7 @@
       <c r="T768" s="3"/>
       <c r="U768" s="3"/>
       <c r="V768" s="3"/>
+      <c r="W768" s="3"/>
     </row>
     <row r="769" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="2"/>
@@ -19163,6 +20001,7 @@
       <c r="T769" s="3"/>
       <c r="U769" s="3"/>
       <c r="V769" s="3"/>
+      <c r="W769" s="3"/>
     </row>
     <row r="770" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="2"/>
@@ -19187,6 +20026,7 @@
       <c r="T770" s="3"/>
       <c r="U770" s="3"/>
       <c r="V770" s="3"/>
+      <c r="W770" s="3"/>
     </row>
     <row r="771" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="2"/>
@@ -19211,6 +20051,7 @@
       <c r="T771" s="3"/>
       <c r="U771" s="3"/>
       <c r="V771" s="3"/>
+      <c r="W771" s="3"/>
     </row>
     <row r="772" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="2"/>
@@ -19235,6 +20076,7 @@
       <c r="T772" s="3"/>
       <c r="U772" s="3"/>
       <c r="V772" s="3"/>
+      <c r="W772" s="3"/>
     </row>
     <row r="773" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="2"/>
@@ -19259,6 +20101,7 @@
       <c r="T773" s="3"/>
       <c r="U773" s="3"/>
       <c r="V773" s="3"/>
+      <c r="W773" s="3"/>
     </row>
     <row r="774" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="2"/>
@@ -19283,6 +20126,7 @@
       <c r="T774" s="3"/>
       <c r="U774" s="3"/>
       <c r="V774" s="3"/>
+      <c r="W774" s="3"/>
     </row>
     <row r="775" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="2"/>
@@ -19307,6 +20151,7 @@
       <c r="T775" s="3"/>
       <c r="U775" s="3"/>
       <c r="V775" s="3"/>
+      <c r="W775" s="3"/>
     </row>
     <row r="776" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="2"/>
@@ -19331,6 +20176,7 @@
       <c r="T776" s="3"/>
       <c r="U776" s="3"/>
       <c r="V776" s="3"/>
+      <c r="W776" s="3"/>
     </row>
     <row r="777" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="2"/>
@@ -19355,6 +20201,7 @@
       <c r="T777" s="3"/>
       <c r="U777" s="3"/>
       <c r="V777" s="3"/>
+      <c r="W777" s="3"/>
     </row>
     <row r="778" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="2"/>
@@ -19379,6 +20226,7 @@
       <c r="T778" s="3"/>
       <c r="U778" s="3"/>
       <c r="V778" s="3"/>
+      <c r="W778" s="3"/>
     </row>
     <row r="779" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="2"/>
@@ -19403,6 +20251,7 @@
       <c r="T779" s="3"/>
       <c r="U779" s="3"/>
       <c r="V779" s="3"/>
+      <c r="W779" s="3"/>
     </row>
     <row r="780" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="2"/>
@@ -19427,6 +20276,7 @@
       <c r="T780" s="3"/>
       <c r="U780" s="3"/>
       <c r="V780" s="3"/>
+      <c r="W780" s="3"/>
     </row>
     <row r="781" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="2"/>
@@ -19451,6 +20301,7 @@
       <c r="T781" s="3"/>
       <c r="U781" s="3"/>
       <c r="V781" s="3"/>
+      <c r="W781" s="3"/>
     </row>
     <row r="782" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="2"/>
@@ -19475,6 +20326,7 @@
       <c r="T782" s="3"/>
       <c r="U782" s="3"/>
       <c r="V782" s="3"/>
+      <c r="W782" s="3"/>
     </row>
     <row r="783" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="2"/>
@@ -19499,6 +20351,7 @@
       <c r="T783" s="3"/>
       <c r="U783" s="3"/>
       <c r="V783" s="3"/>
+      <c r="W783" s="3"/>
     </row>
     <row r="784" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="2"/>
@@ -19523,6 +20376,7 @@
       <c r="T784" s="3"/>
       <c r="U784" s="3"/>
       <c r="V784" s="3"/>
+      <c r="W784" s="3"/>
     </row>
     <row r="785" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="2"/>
@@ -19547,6 +20401,7 @@
       <c r="T785" s="3"/>
       <c r="U785" s="3"/>
       <c r="V785" s="3"/>
+      <c r="W785" s="3"/>
     </row>
     <row r="786" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="2"/>
@@ -19571,6 +20426,7 @@
       <c r="T786" s="3"/>
       <c r="U786" s="3"/>
       <c r="V786" s="3"/>
+      <c r="W786" s="3"/>
     </row>
     <row r="787" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="2"/>
@@ -19595,6 +20451,7 @@
       <c r="T787" s="3"/>
       <c r="U787" s="3"/>
       <c r="V787" s="3"/>
+      <c r="W787" s="3"/>
     </row>
     <row r="788" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="2"/>
@@ -19619,6 +20476,7 @@
       <c r="T788" s="3"/>
       <c r="U788" s="3"/>
       <c r="V788" s="3"/>
+      <c r="W788" s="3"/>
     </row>
     <row r="789" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="2"/>
@@ -19643,6 +20501,7 @@
       <c r="T789" s="3"/>
       <c r="U789" s="3"/>
       <c r="V789" s="3"/>
+      <c r="W789" s="3"/>
     </row>
     <row r="790" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="2"/>
@@ -19667,6 +20526,7 @@
       <c r="T790" s="3"/>
       <c r="U790" s="3"/>
       <c r="V790" s="3"/>
+      <c r="W790" s="3"/>
     </row>
     <row r="791" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="2"/>
@@ -19691,6 +20551,7 @@
       <c r="T791" s="3"/>
       <c r="U791" s="3"/>
       <c r="V791" s="3"/>
+      <c r="W791" s="3"/>
     </row>
     <row r="792" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="2"/>
@@ -19715,6 +20576,7 @@
       <c r="T792" s="3"/>
       <c r="U792" s="3"/>
       <c r="V792" s="3"/>
+      <c r="W792" s="3"/>
     </row>
     <row r="793" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="2"/>
@@ -19739,6 +20601,7 @@
       <c r="T793" s="3"/>
       <c r="U793" s="3"/>
       <c r="V793" s="3"/>
+      <c r="W793" s="3"/>
     </row>
     <row r="794" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="2"/>
@@ -19763,6 +20626,7 @@
       <c r="T794" s="3"/>
       <c r="U794" s="3"/>
       <c r="V794" s="3"/>
+      <c r="W794" s="3"/>
     </row>
     <row r="795" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="2"/>
@@ -19787,6 +20651,7 @@
       <c r="T795" s="3"/>
       <c r="U795" s="3"/>
       <c r="V795" s="3"/>
+      <c r="W795" s="3"/>
     </row>
     <row r="796" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="2"/>
@@ -19811,6 +20676,7 @@
       <c r="T796" s="3"/>
       <c r="U796" s="3"/>
       <c r="V796" s="3"/>
+      <c r="W796" s="3"/>
     </row>
     <row r="797" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="2"/>
@@ -19835,6 +20701,7 @@
       <c r="T797" s="3"/>
       <c r="U797" s="3"/>
       <c r="V797" s="3"/>
+      <c r="W797" s="3"/>
     </row>
     <row r="798" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="2"/>
@@ -19859,6 +20726,7 @@
       <c r="T798" s="3"/>
       <c r="U798" s="3"/>
       <c r="V798" s="3"/>
+      <c r="W798" s="3"/>
     </row>
     <row r="799" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="2"/>
@@ -19883,6 +20751,7 @@
       <c r="T799" s="3"/>
       <c r="U799" s="3"/>
       <c r="V799" s="3"/>
+      <c r="W799" s="3"/>
     </row>
     <row r="800" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="2"/>
@@ -19907,6 +20776,7 @@
       <c r="T800" s="3"/>
       <c r="U800" s="3"/>
       <c r="V800" s="3"/>
+      <c r="W800" s="3"/>
     </row>
     <row r="801" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="2"/>
@@ -19931,6 +20801,7 @@
       <c r="T801" s="3"/>
       <c r="U801" s="3"/>
       <c r="V801" s="3"/>
+      <c r="W801" s="3"/>
     </row>
     <row r="802" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="2"/>
@@ -19955,6 +20826,7 @@
       <c r="T802" s="3"/>
       <c r="U802" s="3"/>
       <c r="V802" s="3"/>
+      <c r="W802" s="3"/>
     </row>
     <row r="803" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="2"/>
@@ -19979,6 +20851,7 @@
       <c r="T803" s="3"/>
       <c r="U803" s="3"/>
       <c r="V803" s="3"/>
+      <c r="W803" s="3"/>
     </row>
     <row r="804" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="2"/>
@@ -20003,6 +20876,7 @@
       <c r="T804" s="3"/>
       <c r="U804" s="3"/>
       <c r="V804" s="3"/>
+      <c r="W804" s="3"/>
     </row>
     <row r="805" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="2"/>
@@ -20027,6 +20901,7 @@
       <c r="T805" s="3"/>
       <c r="U805" s="3"/>
       <c r="V805" s="3"/>
+      <c r="W805" s="3"/>
     </row>
     <row r="806" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="2"/>
@@ -20051,6 +20926,7 @@
       <c r="T806" s="3"/>
       <c r="U806" s="3"/>
       <c r="V806" s="3"/>
+      <c r="W806" s="3"/>
     </row>
     <row r="807" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="2"/>
@@ -20075,6 +20951,7 @@
       <c r="T807" s="3"/>
       <c r="U807" s="3"/>
       <c r="V807" s="3"/>
+      <c r="W807" s="3"/>
     </row>
     <row r="808" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="2"/>
@@ -20099,6 +20976,7 @@
       <c r="T808" s="3"/>
       <c r="U808" s="3"/>
       <c r="V808" s="3"/>
+      <c r="W808" s="3"/>
     </row>
     <row r="809" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="2"/>
@@ -20123,6 +21001,7 @@
       <c r="T809" s="3"/>
       <c r="U809" s="3"/>
       <c r="V809" s="3"/>
+      <c r="W809" s="3"/>
     </row>
     <row r="810" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="2"/>
@@ -20147,6 +21026,7 @@
       <c r="T810" s="3"/>
       <c r="U810" s="3"/>
       <c r="V810" s="3"/>
+      <c r="W810" s="3"/>
     </row>
     <row r="811" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="2"/>
@@ -20171,6 +21051,7 @@
       <c r="T811" s="3"/>
       <c r="U811" s="3"/>
       <c r="V811" s="3"/>
+      <c r="W811" s="3"/>
     </row>
     <row r="812" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="2"/>
@@ -20195,6 +21076,7 @@
       <c r="T812" s="3"/>
       <c r="U812" s="3"/>
       <c r="V812" s="3"/>
+      <c r="W812" s="3"/>
     </row>
     <row r="813" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="2"/>
@@ -20219,6 +21101,7 @@
       <c r="T813" s="3"/>
       <c r="U813" s="3"/>
       <c r="V813" s="3"/>
+      <c r="W813" s="3"/>
     </row>
     <row r="814" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="2"/>
@@ -20243,6 +21126,7 @@
       <c r="T814" s="3"/>
       <c r="U814" s="3"/>
       <c r="V814" s="3"/>
+      <c r="W814" s="3"/>
     </row>
     <row r="815" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="2"/>
@@ -20267,6 +21151,7 @@
       <c r="T815" s="3"/>
       <c r="U815" s="3"/>
       <c r="V815" s="3"/>
+      <c r="W815" s="3"/>
     </row>
     <row r="816" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="2"/>
@@ -20291,6 +21176,7 @@
       <c r="T816" s="3"/>
       <c r="U816" s="3"/>
       <c r="V816" s="3"/>
+      <c r="W816" s="3"/>
     </row>
     <row r="817" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="2"/>
@@ -20315,6 +21201,7 @@
       <c r="T817" s="3"/>
       <c r="U817" s="3"/>
       <c r="V817" s="3"/>
+      <c r="W817" s="3"/>
     </row>
     <row r="818" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="2"/>
@@ -20339,6 +21226,7 @@
       <c r="T818" s="3"/>
       <c r="U818" s="3"/>
       <c r="V818" s="3"/>
+      <c r="W818" s="3"/>
     </row>
     <row r="819" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="2"/>
@@ -20363,6 +21251,7 @@
       <c r="T819" s="3"/>
       <c r="U819" s="3"/>
       <c r="V819" s="3"/>
+      <c r="W819" s="3"/>
     </row>
     <row r="820" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="2"/>
@@ -20387,6 +21276,7 @@
       <c r="T820" s="3"/>
       <c r="U820" s="3"/>
       <c r="V820" s="3"/>
+      <c r="W820" s="3"/>
     </row>
     <row r="821" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="2"/>
@@ -20411,6 +21301,7 @@
       <c r="T821" s="3"/>
       <c r="U821" s="3"/>
       <c r="V821" s="3"/>
+      <c r="W821" s="3"/>
     </row>
     <row r="822" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="2"/>
@@ -20435,6 +21326,7 @@
       <c r="T822" s="3"/>
       <c r="U822" s="3"/>
       <c r="V822" s="3"/>
+      <c r="W822" s="3"/>
     </row>
     <row r="823" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="2"/>
@@ -20459,6 +21351,7 @@
       <c r="T823" s="3"/>
       <c r="U823" s="3"/>
       <c r="V823" s="3"/>
+      <c r="W823" s="3"/>
     </row>
     <row r="824" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="2"/>
@@ -20483,6 +21376,7 @@
       <c r="T824" s="3"/>
       <c r="U824" s="3"/>
       <c r="V824" s="3"/>
+      <c r="W824" s="3"/>
     </row>
     <row r="825" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="2"/>
@@ -20507,6 +21401,7 @@
       <c r="T825" s="3"/>
       <c r="U825" s="3"/>
       <c r="V825" s="3"/>
+      <c r="W825" s="3"/>
     </row>
     <row r="826" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="2"/>
@@ -20531,6 +21426,7 @@
       <c r="T826" s="3"/>
       <c r="U826" s="3"/>
       <c r="V826" s="3"/>
+      <c r="W826" s="3"/>
     </row>
     <row r="827" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="2"/>
@@ -20555,6 +21451,7 @@
       <c r="T827" s="3"/>
       <c r="U827" s="3"/>
       <c r="V827" s="3"/>
+      <c r="W827" s="3"/>
     </row>
     <row r="828" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="2"/>
@@ -20579,6 +21476,7 @@
       <c r="T828" s="3"/>
       <c r="U828" s="3"/>
       <c r="V828" s="3"/>
+      <c r="W828" s="3"/>
     </row>
     <row r="829" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="2"/>
@@ -20603,6 +21501,7 @@
       <c r="T829" s="3"/>
       <c r="U829" s="3"/>
       <c r="V829" s="3"/>
+      <c r="W829" s="3"/>
     </row>
     <row r="830" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="2"/>
@@ -20627,6 +21526,7 @@
       <c r="T830" s="3"/>
       <c r="U830" s="3"/>
       <c r="V830" s="3"/>
+      <c r="W830" s="3"/>
     </row>
     <row r="831" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="2"/>
@@ -20651,6 +21551,7 @@
       <c r="T831" s="3"/>
       <c r="U831" s="3"/>
       <c r="V831" s="3"/>
+      <c r="W831" s="3"/>
     </row>
     <row r="832" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="2"/>
@@ -20675,6 +21576,7 @@
       <c r="T832" s="3"/>
       <c r="U832" s="3"/>
       <c r="V832" s="3"/>
+      <c r="W832" s="3"/>
     </row>
     <row r="833" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="2"/>
@@ -20699,6 +21601,7 @@
       <c r="T833" s="3"/>
       <c r="U833" s="3"/>
       <c r="V833" s="3"/>
+      <c r="W833" s="3"/>
     </row>
     <row r="834" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="2"/>
@@ -20723,6 +21626,7 @@
       <c r="T834" s="3"/>
       <c r="U834" s="3"/>
       <c r="V834" s="3"/>
+      <c r="W834" s="3"/>
     </row>
     <row r="835" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="2"/>
@@ -20747,6 +21651,7 @@
       <c r="T835" s="3"/>
       <c r="U835" s="3"/>
       <c r="V835" s="3"/>
+      <c r="W835" s="3"/>
     </row>
     <row r="836" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="2"/>
@@ -20771,6 +21676,7 @@
       <c r="T836" s="3"/>
       <c r="U836" s="3"/>
       <c r="V836" s="3"/>
+      <c r="W836" s="3"/>
     </row>
     <row r="837" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="2"/>
@@ -20795,6 +21701,7 @@
       <c r="T837" s="3"/>
       <c r="U837" s="3"/>
       <c r="V837" s="3"/>
+      <c r="W837" s="3"/>
     </row>
     <row r="838" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="2"/>
@@ -20819,6 +21726,7 @@
       <c r="T838" s="3"/>
       <c r="U838" s="3"/>
       <c r="V838" s="3"/>
+      <c r="W838" s="3"/>
     </row>
     <row r="839" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="2"/>
@@ -20843,6 +21751,7 @@
       <c r="T839" s="3"/>
       <c r="U839" s="3"/>
       <c r="V839" s="3"/>
+      <c r="W839" s="3"/>
     </row>
     <row r="840" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="2"/>
@@ -20867,6 +21776,7 @@
       <c r="T840" s="3"/>
       <c r="U840" s="3"/>
       <c r="V840" s="3"/>
+      <c r="W840" s="3"/>
     </row>
     <row r="841" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="2"/>
@@ -20891,6 +21801,7 @@
       <c r="T841" s="3"/>
       <c r="U841" s="3"/>
       <c r="V841" s="3"/>
+      <c r="W841" s="3"/>
     </row>
     <row r="842" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="2"/>
@@ -20915,6 +21826,7 @@
       <c r="T842" s="3"/>
       <c r="U842" s="3"/>
       <c r="V842" s="3"/>
+      <c r="W842" s="3"/>
     </row>
     <row r="843" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="2"/>
@@ -20939,6 +21851,7 @@
       <c r="T843" s="3"/>
       <c r="U843" s="3"/>
       <c r="V843" s="3"/>
+      <c r="W843" s="3"/>
     </row>
     <row r="844" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="2"/>
@@ -20963,6 +21876,7 @@
       <c r="T844" s="3"/>
       <c r="U844" s="3"/>
       <c r="V844" s="3"/>
+      <c r="W844" s="3"/>
     </row>
     <row r="845" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="2"/>
@@ -20987,6 +21901,7 @@
       <c r="T845" s="3"/>
       <c r="U845" s="3"/>
       <c r="V845" s="3"/>
+      <c r="W845" s="3"/>
     </row>
     <row r="846" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="2"/>
@@ -21011,6 +21926,7 @@
       <c r="T846" s="3"/>
       <c r="U846" s="3"/>
       <c r="V846" s="3"/>
+      <c r="W846" s="3"/>
     </row>
     <row r="847" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="2"/>
@@ -21035,6 +21951,7 @@
       <c r="T847" s="3"/>
       <c r="U847" s="3"/>
       <c r="V847" s="3"/>
+      <c r="W847" s="3"/>
     </row>
     <row r="848" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="2"/>
@@ -21059,6 +21976,7 @@
       <c r="T848" s="3"/>
       <c r="U848" s="3"/>
       <c r="V848" s="3"/>
+      <c r="W848" s="3"/>
     </row>
     <row r="849" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="2"/>
@@ -21083,6 +22001,7 @@
       <c r="T849" s="3"/>
       <c r="U849" s="3"/>
       <c r="V849" s="3"/>
+      <c r="W849" s="3"/>
     </row>
     <row r="850" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="2"/>
@@ -21107,6 +22026,7 @@
       <c r="T850" s="3"/>
       <c r="U850" s="3"/>
       <c r="V850" s="3"/>
+      <c r="W850" s="3"/>
     </row>
     <row r="851" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="2"/>
@@ -21131,6 +22051,7 @@
       <c r="T851" s="3"/>
       <c r="U851" s="3"/>
       <c r="V851" s="3"/>
+      <c r="W851" s="3"/>
     </row>
     <row r="852" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="2"/>
@@ -21155,6 +22076,7 @@
       <c r="T852" s="3"/>
       <c r="U852" s="3"/>
       <c r="V852" s="3"/>
+      <c r="W852" s="3"/>
     </row>
     <row r="853" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="2"/>
@@ -21179,6 +22101,7 @@
       <c r="T853" s="3"/>
       <c r="U853" s="3"/>
       <c r="V853" s="3"/>
+      <c r="W853" s="3"/>
     </row>
     <row r="854" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="2"/>
@@ -21203,6 +22126,7 @@
       <c r="T854" s="3"/>
       <c r="U854" s="3"/>
       <c r="V854" s="3"/>
+      <c r="W854" s="3"/>
     </row>
     <row r="855" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="2"/>
@@ -21227,6 +22151,7 @@
       <c r="T855" s="3"/>
       <c r="U855" s="3"/>
       <c r="V855" s="3"/>
+      <c r="W855" s="3"/>
     </row>
     <row r="856" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="2"/>
@@ -21251,6 +22176,7 @@
       <c r="T856" s="3"/>
       <c r="U856" s="3"/>
       <c r="V856" s="3"/>
+      <c r="W856" s="3"/>
     </row>
     <row r="857" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="2"/>
@@ -21275,6 +22201,7 @@
       <c r="T857" s="3"/>
       <c r="U857" s="3"/>
       <c r="V857" s="3"/>
+      <c r="W857" s="3"/>
     </row>
     <row r="858" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="2"/>
@@ -21299,6 +22226,7 @@
       <c r="T858" s="3"/>
       <c r="U858" s="3"/>
       <c r="V858" s="3"/>
+      <c r="W858" s="3"/>
     </row>
     <row r="859" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="2"/>
@@ -21323,6 +22251,7 @@
       <c r="T859" s="3"/>
       <c r="U859" s="3"/>
       <c r="V859" s="3"/>
+      <c r="W859" s="3"/>
     </row>
     <row r="860" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="2"/>
@@ -21347,6 +22276,7 @@
       <c r="T860" s="3"/>
       <c r="U860" s="3"/>
       <c r="V860" s="3"/>
+      <c r="W860" s="3"/>
     </row>
     <row r="861" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="2"/>
@@ -21371,6 +22301,7 @@
       <c r="T861" s="3"/>
       <c r="U861" s="3"/>
       <c r="V861" s="3"/>
+      <c r="W861" s="3"/>
     </row>
     <row r="862" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="2"/>
@@ -21395,6 +22326,7 @@
       <c r="T862" s="3"/>
       <c r="U862" s="3"/>
       <c r="V862" s="3"/>
+      <c r="W862" s="3"/>
     </row>
     <row r="863" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="2"/>
@@ -21419,6 +22351,7 @@
       <c r="T863" s="3"/>
       <c r="U863" s="3"/>
       <c r="V863" s="3"/>
+      <c r="W863" s="3"/>
     </row>
     <row r="864" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="2"/>
@@ -21443,6 +22376,7 @@
       <c r="T864" s="3"/>
       <c r="U864" s="3"/>
       <c r="V864" s="3"/>
+      <c r="W864" s="3"/>
     </row>
     <row r="865" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="2"/>
@@ -21467,6 +22401,7 @@
       <c r="T865" s="3"/>
       <c r="U865" s="3"/>
       <c r="V865" s="3"/>
+      <c r="W865" s="3"/>
     </row>
     <row r="866" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="2"/>
@@ -21491,6 +22426,7 @@
       <c r="T866" s="3"/>
       <c r="U866" s="3"/>
       <c r="V866" s="3"/>
+      <c r="W866" s="3"/>
     </row>
     <row r="867" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="2"/>
@@ -21515,6 +22451,7 @@
       <c r="T867" s="3"/>
       <c r="U867" s="3"/>
       <c r="V867" s="3"/>
+      <c r="W867" s="3"/>
     </row>
     <row r="868" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="2"/>
@@ -21539,6 +22476,7 @@
       <c r="T868" s="3"/>
       <c r="U868" s="3"/>
       <c r="V868" s="3"/>
+      <c r="W868" s="3"/>
     </row>
     <row r="869" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="2"/>
@@ -21563,6 +22501,7 @@
       <c r="T869" s="3"/>
       <c r="U869" s="3"/>
       <c r="V869" s="3"/>
+      <c r="W869" s="3"/>
     </row>
     <row r="870" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="2"/>
@@ -21587,6 +22526,7 @@
       <c r="T870" s="3"/>
       <c r="U870" s="3"/>
       <c r="V870" s="3"/>
+      <c r="W870" s="3"/>
     </row>
     <row r="871" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="2"/>
@@ -21611,6 +22551,7 @@
       <c r="T871" s="3"/>
       <c r="U871" s="3"/>
       <c r="V871" s="3"/>
+      <c r="W871" s="3"/>
     </row>
     <row r="872" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="2"/>
@@ -21635,6 +22576,7 @@
       <c r="T872" s="3"/>
       <c r="U872" s="3"/>
       <c r="V872" s="3"/>
+      <c r="W872" s="3"/>
     </row>
     <row r="873" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="2"/>
@@ -21659,6 +22601,7 @@
       <c r="T873" s="3"/>
       <c r="U873" s="3"/>
       <c r="V873" s="3"/>
+      <c r="W873" s="3"/>
     </row>
     <row r="874" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="2"/>
@@ -21683,6 +22626,7 @@
       <c r="T874" s="3"/>
       <c r="U874" s="3"/>
       <c r="V874" s="3"/>
+      <c r="W874" s="3"/>
     </row>
     <row r="875" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="2"/>
@@ -21707,6 +22651,7 @@
       <c r="T875" s="3"/>
       <c r="U875" s="3"/>
       <c r="V875" s="3"/>
+      <c r="W875" s="3"/>
     </row>
     <row r="876" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="2"/>
@@ -21731,6 +22676,7 @@
       <c r="T876" s="3"/>
       <c r="U876" s="3"/>
       <c r="V876" s="3"/>
+      <c r="W876" s="3"/>
     </row>
     <row r="877" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="2"/>
@@ -21755,6 +22701,7 @@
       <c r="T877" s="3"/>
       <c r="U877" s="3"/>
       <c r="V877" s="3"/>
+      <c r="W877" s="3"/>
     </row>
     <row r="878" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="2"/>
@@ -21779,6 +22726,7 @@
       <c r="T878" s="3"/>
       <c r="U878" s="3"/>
       <c r="V878" s="3"/>
+      <c r="W878" s="3"/>
     </row>
     <row r="879" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="2"/>
@@ -21803,6 +22751,7 @@
       <c r="T879" s="3"/>
       <c r="U879" s="3"/>
       <c r="V879" s="3"/>
+      <c r="W879" s="3"/>
     </row>
     <row r="880" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="2"/>
@@ -21827,6 +22776,7 @@
       <c r="T880" s="3"/>
       <c r="U880" s="3"/>
       <c r="V880" s="3"/>
+      <c r="W880" s="3"/>
     </row>
     <row r="881" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="2"/>
@@ -21851,6 +22801,7 @@
       <c r="T881" s="3"/>
       <c r="U881" s="3"/>
       <c r="V881" s="3"/>
+      <c r="W881" s="3"/>
     </row>
     <row r="882" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="2"/>
@@ -21875,6 +22826,7 @@
       <c r="T882" s="3"/>
       <c r="U882" s="3"/>
       <c r="V882" s="3"/>
+      <c r="W882" s="3"/>
     </row>
     <row r="883" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="2"/>
@@ -21899,6 +22851,7 @@
       <c r="T883" s="3"/>
       <c r="U883" s="3"/>
       <c r="V883" s="3"/>
+      <c r="W883" s="3"/>
     </row>
     <row r="884" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="2"/>
@@ -21923,6 +22876,7 @@
       <c r="T884" s="3"/>
       <c r="U884" s="3"/>
       <c r="V884" s="3"/>
+      <c r="W884" s="3"/>
     </row>
     <row r="885" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="2"/>
@@ -21947,6 +22901,7 @@
       <c r="T885" s="3"/>
       <c r="U885" s="3"/>
       <c r="V885" s="3"/>
+      <c r="W885" s="3"/>
     </row>
     <row r="886" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="2"/>
@@ -21971,6 +22926,7 @@
       <c r="T886" s="3"/>
       <c r="U886" s="3"/>
       <c r="V886" s="3"/>
+      <c r="W886" s="3"/>
     </row>
     <row r="887" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="2"/>
@@ -21995,6 +22951,7 @@
       <c r="T887" s="3"/>
       <c r="U887" s="3"/>
       <c r="V887" s="3"/>
+      <c r="W887" s="3"/>
     </row>
     <row r="888" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="2"/>
@@ -22019,6 +22976,7 @@
       <c r="T888" s="3"/>
       <c r="U888" s="3"/>
       <c r="V888" s="3"/>
+      <c r="W888" s="3"/>
     </row>
     <row r="889" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="2"/>
@@ -22043,6 +23001,7 @@
       <c r="T889" s="3"/>
       <c r="U889" s="3"/>
       <c r="V889" s="3"/>
+      <c r="W889" s="3"/>
     </row>
     <row r="890" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="2"/>
@@ -22067,6 +23026,7 @@
       <c r="T890" s="3"/>
       <c r="U890" s="3"/>
       <c r="V890" s="3"/>
+      <c r="W890" s="3"/>
     </row>
     <row r="891" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="2"/>
@@ -22091,6 +23051,7 @@
       <c r="T891" s="3"/>
       <c r="U891" s="3"/>
       <c r="V891" s="3"/>
+      <c r="W891" s="3"/>
     </row>
     <row r="892" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="2"/>
@@ -22115,6 +23076,7 @@
       <c r="T892" s="3"/>
       <c r="U892" s="3"/>
       <c r="V892" s="3"/>
+      <c r="W892" s="3"/>
     </row>
     <row r="893" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="2"/>
@@ -22139,6 +23101,7 @@
       <c r="T893" s="3"/>
       <c r="U893" s="3"/>
       <c r="V893" s="3"/>
+      <c r="W893" s="3"/>
     </row>
     <row r="894" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="2"/>
@@ -22163,6 +23126,7 @@
       <c r="T894" s="3"/>
       <c r="U894" s="3"/>
       <c r="V894" s="3"/>
+      <c r="W894" s="3"/>
     </row>
     <row r="895" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="2"/>
@@ -22187,6 +23151,7 @@
       <c r="T895" s="3"/>
       <c r="U895" s="3"/>
       <c r="V895" s="3"/>
+      <c r="W895" s="3"/>
     </row>
     <row r="896" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="2"/>
@@ -22211,6 +23176,7 @@
       <c r="T896" s="3"/>
       <c r="U896" s="3"/>
       <c r="V896" s="3"/>
+      <c r="W896" s="3"/>
     </row>
     <row r="897" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="2"/>
@@ -22235,6 +23201,7 @@
       <c r="T897" s="3"/>
       <c r="U897" s="3"/>
       <c r="V897" s="3"/>
+      <c r="W897" s="3"/>
     </row>
     <row r="898" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="2"/>
@@ -22259,6 +23226,7 @@
       <c r="T898" s="3"/>
       <c r="U898" s="3"/>
       <c r="V898" s="3"/>
+      <c r="W898" s="3"/>
     </row>
     <row r="899" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="2"/>
@@ -22283,6 +23251,7 @@
       <c r="T899" s="3"/>
       <c r="U899" s="3"/>
       <c r="V899" s="3"/>
+      <c r="W899" s="3"/>
     </row>
     <row r="900" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="2"/>
@@ -22307,6 +23276,7 @@
       <c r="T900" s="3"/>
       <c r="U900" s="3"/>
       <c r="V900" s="3"/>
+      <c r="W900" s="3"/>
     </row>
     <row r="901" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="2"/>
@@ -22331,6 +23301,7 @@
       <c r="T901" s="3"/>
       <c r="U901" s="3"/>
       <c r="V901" s="3"/>
+      <c r="W901" s="3"/>
     </row>
     <row r="902" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="2"/>
@@ -22355,6 +23326,7 @@
       <c r="T902" s="3"/>
       <c r="U902" s="3"/>
       <c r="V902" s="3"/>
+      <c r="W902" s="3"/>
     </row>
     <row r="903" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="2"/>
@@ -22379,6 +23351,7 @@
       <c r="T903" s="3"/>
       <c r="U903" s="3"/>
       <c r="V903" s="3"/>
+      <c r="W903" s="3"/>
     </row>
     <row r="904" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="2"/>
@@ -22403,6 +23376,7 @@
       <c r="T904" s="3"/>
       <c r="U904" s="3"/>
       <c r="V904" s="3"/>
+      <c r="W904" s="3"/>
     </row>
     <row r="905" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="2"/>
@@ -22427,6 +23401,7 @@
       <c r="T905" s="3"/>
       <c r="U905" s="3"/>
       <c r="V905" s="3"/>
+      <c r="W905" s="3"/>
     </row>
     <row r="906" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="2"/>
@@ -22451,6 +23426,7 @@
       <c r="T906" s="3"/>
       <c r="U906" s="3"/>
       <c r="V906" s="3"/>
+      <c r="W906" s="3"/>
     </row>
     <row r="907" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="2"/>
@@ -22475,6 +23451,7 @@
       <c r="T907" s="3"/>
       <c r="U907" s="3"/>
       <c r="V907" s="3"/>
+      <c r="W907" s="3"/>
     </row>
     <row r="908" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="2"/>
@@ -22499,6 +23476,7 @@
       <c r="T908" s="3"/>
       <c r="U908" s="3"/>
       <c r="V908" s="3"/>
+      <c r="W908" s="3"/>
     </row>
     <row r="909" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="2"/>
@@ -22523,6 +23501,7 @@
       <c r="T909" s="3"/>
       <c r="U909" s="3"/>
       <c r="V909" s="3"/>
+      <c r="W909" s="3"/>
     </row>
     <row r="910" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="2"/>
@@ -22547,6 +23526,7 @@
       <c r="T910" s="3"/>
       <c r="U910" s="3"/>
       <c r="V910" s="3"/>
+      <c r="W910" s="3"/>
     </row>
     <row r="911" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="2"/>
@@ -22571,6 +23551,7 @@
       <c r="T911" s="3"/>
       <c r="U911" s="3"/>
       <c r="V911" s="3"/>
+      <c r="W911" s="3"/>
     </row>
     <row r="912" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="2"/>
@@ -22595,6 +23576,7 @@
       <c r="T912" s="3"/>
       <c r="U912" s="3"/>
       <c r="V912" s="3"/>
+      <c r="W912" s="3"/>
     </row>
     <row r="913" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="2"/>
@@ -22619,6 +23601,7 @@
       <c r="T913" s="3"/>
       <c r="U913" s="3"/>
       <c r="V913" s="3"/>
+      <c r="W913" s="3"/>
     </row>
     <row r="914" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="2"/>
@@ -22643,6 +23626,7 @@
       <c r="T914" s="3"/>
       <c r="U914" s="3"/>
       <c r="V914" s="3"/>
+      <c r="W914" s="3"/>
     </row>
     <row r="915" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="2"/>
@@ -22667,6 +23651,7 @@
       <c r="T915" s="3"/>
       <c r="U915" s="3"/>
       <c r="V915" s="3"/>
+      <c r="W915" s="3"/>
     </row>
     <row r="916" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="2"/>
@@ -22691,6 +23676,7 @@
       <c r="T916" s="3"/>
       <c r="U916" s="3"/>
       <c r="V916" s="3"/>
+      <c r="W916" s="3"/>
     </row>
     <row r="917" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="2"/>
@@ -22715,6 +23701,7 @@
       <c r="T917" s="3"/>
       <c r="U917" s="3"/>
       <c r="V917" s="3"/>
+      <c r="W917" s="3"/>
     </row>
     <row r="918" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="2"/>
@@ -22739,6 +23726,7 @@
       <c r="T918" s="3"/>
       <c r="U918" s="3"/>
       <c r="V918" s="3"/>
+      <c r="W918" s="3"/>
     </row>
     <row r="919" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="2"/>
@@ -22763,6 +23751,7 @@
       <c r="T919" s="3"/>
       <c r="U919" s="3"/>
       <c r="V919" s="3"/>
+      <c r="W919" s="3"/>
     </row>
     <row r="920" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="2"/>
@@ -22787,6 +23776,7 @@
       <c r="T920" s="3"/>
       <c r="U920" s="3"/>
       <c r="V920" s="3"/>
+      <c r="W920" s="3"/>
     </row>
     <row r="921" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="2"/>
@@ -22811,6 +23801,7 @@
       <c r="T921" s="3"/>
       <c r="U921" s="3"/>
       <c r="V921" s="3"/>
+      <c r="W921" s="3"/>
     </row>
     <row r="922" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="2"/>
@@ -22835,6 +23826,7 @@
       <c r="T922" s="3"/>
       <c r="U922" s="3"/>
       <c r="V922" s="3"/>
+      <c r="W922" s="3"/>
     </row>
     <row r="923" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="2"/>
@@ -22859,6 +23851,7 @@
       <c r="T923" s="3"/>
       <c r="U923" s="3"/>
       <c r="V923" s="3"/>
+      <c r="W923" s="3"/>
     </row>
     <row r="924" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="2"/>
@@ -22883,6 +23876,7 @@
       <c r="T924" s="3"/>
       <c r="U924" s="3"/>
       <c r="V924" s="3"/>
+      <c r="W924" s="3"/>
     </row>
     <row r="925" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="2"/>
@@ -22907,6 +23901,7 @@
       <c r="T925" s="3"/>
       <c r="U925" s="3"/>
       <c r="V925" s="3"/>
+      <c r="W925" s="3"/>
     </row>
     <row r="926" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="2"/>
@@ -22931,6 +23926,7 @@
       <c r="T926" s="3"/>
       <c r="U926" s="3"/>
       <c r="V926" s="3"/>
+      <c r="W926" s="3"/>
     </row>
     <row r="927" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="2"/>
@@ -22955,6 +23951,7 @@
       <c r="T927" s="3"/>
       <c r="U927" s="3"/>
       <c r="V927" s="3"/>
+      <c r="W927" s="3"/>
     </row>
     <row r="928" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="2"/>
@@ -22979,6 +23976,7 @@
       <c r="T928" s="3"/>
       <c r="U928" s="3"/>
       <c r="V928" s="3"/>
+      <c r="W928" s="3"/>
     </row>
     <row r="929" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="2"/>
@@ -23003,6 +24001,7 @@
       <c r="T929" s="3"/>
       <c r="U929" s="3"/>
       <c r="V929" s="3"/>
+      <c r="W929" s="3"/>
     </row>
     <row r="930" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="2"/>
@@ -23027,6 +24026,7 @@
       <c r="T930" s="3"/>
       <c r="U930" s="3"/>
       <c r="V930" s="3"/>
+      <c r="W930" s="3"/>
     </row>
     <row r="931" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="2"/>
@@ -23051,6 +24051,7 @@
       <c r="T931" s="3"/>
       <c r="U931" s="3"/>
       <c r="V931" s="3"/>
+      <c r="W931" s="3"/>
     </row>
     <row r="932" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="2"/>
@@ -23075,6 +24076,7 @@
       <c r="T932" s="3"/>
       <c r="U932" s="3"/>
       <c r="V932" s="3"/>
+      <c r="W932" s="3"/>
     </row>
     <row r="933" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="2"/>
@@ -23099,6 +24101,7 @@
       <c r="T933" s="3"/>
       <c r="U933" s="3"/>
       <c r="V933" s="3"/>
+      <c r="W933" s="3"/>
     </row>
     <row r="934" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="2"/>
@@ -23123,6 +24126,7 @@
       <c r="T934" s="3"/>
       <c r="U934" s="3"/>
       <c r="V934" s="3"/>
+      <c r="W934" s="3"/>
     </row>
     <row r="935" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="2"/>
@@ -23147,6 +24151,7 @@
       <c r="T935" s="3"/>
       <c r="U935" s="3"/>
       <c r="V935" s="3"/>
+      <c r="W935" s="3"/>
     </row>
     <row r="936" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="2"/>
@@ -23171,6 +24176,7 @@
       <c r="T936" s="3"/>
       <c r="U936" s="3"/>
       <c r="V936" s="3"/>
+      <c r="W936" s="3"/>
     </row>
     <row r="937" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="2"/>
@@ -23195,6 +24201,7 @@
       <c r="T937" s="3"/>
       <c r="U937" s="3"/>
       <c r="V937" s="3"/>
+      <c r="W937" s="3"/>
     </row>
     <row r="938" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="2"/>
@@ -23219,6 +24226,7 @@
       <c r="T938" s="3"/>
       <c r="U938" s="3"/>
       <c r="V938" s="3"/>
+      <c r="W938" s="3"/>
     </row>
     <row r="939" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="2"/>
@@ -23243,6 +24251,7 @@
       <c r="T939" s="3"/>
       <c r="U939" s="3"/>
       <c r="V939" s="3"/>
+      <c r="W939" s="3"/>
     </row>
     <row r="940" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="2"/>
@@ -23267,6 +24276,7 @@
       <c r="T940" s="3"/>
       <c r="U940" s="3"/>
       <c r="V940" s="3"/>
+      <c r="W940" s="3"/>
     </row>
     <row r="941" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="2"/>
@@ -23291,6 +24301,7 @@
       <c r="T941" s="3"/>
       <c r="U941" s="3"/>
       <c r="V941" s="3"/>
+      <c r="W941" s="3"/>
     </row>
     <row r="942" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="2"/>
@@ -23315,6 +24326,7 @@
       <c r="T942" s="3"/>
       <c r="U942" s="3"/>
       <c r="V942" s="3"/>
+      <c r="W942" s="3"/>
     </row>
     <row r="943" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="2"/>
@@ -23339,6 +24351,7 @@
       <c r="T943" s="3"/>
       <c r="U943" s="3"/>
       <c r="V943" s="3"/>
+      <c r="W943" s="3"/>
     </row>
     <row r="944" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="2"/>
@@ -23363,6 +24376,7 @@
       <c r="T944" s="3"/>
       <c r="U944" s="3"/>
       <c r="V944" s="3"/>
+      <c r="W944" s="3"/>
     </row>
     <row r="945" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="2"/>
@@ -23387,6 +24401,7 @@
       <c r="T945" s="3"/>
       <c r="U945" s="3"/>
       <c r="V945" s="3"/>
+      <c r="W945" s="3"/>
     </row>
     <row r="946" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="2"/>
@@ -23411,6 +24426,7 @@
       <c r="T946" s="3"/>
       <c r="U946" s="3"/>
       <c r="V946" s="3"/>
+      <c r="W946" s="3"/>
     </row>
     <row r="947" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="2"/>
@@ -23435,6 +24451,7 @@
       <c r="T947" s="3"/>
       <c r="U947" s="3"/>
       <c r="V947" s="3"/>
+      <c r="W947" s="3"/>
     </row>
     <row r="948" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="2"/>
@@ -23459,6 +24476,7 @@
       <c r="T948" s="3"/>
       <c r="U948" s="3"/>
       <c r="V948" s="3"/>
+      <c r="W948" s="3"/>
     </row>
     <row r="949" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="2"/>
@@ -23483,6 +24501,7 @@
       <c r="T949" s="3"/>
       <c r="U949" s="3"/>
       <c r="V949" s="3"/>
+      <c r="W949" s="3"/>
     </row>
     <row r="950" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="2"/>
@@ -23507,6 +24526,7 @@
       <c r="T950" s="3"/>
       <c r="U950" s="3"/>
       <c r="V950" s="3"/>
+      <c r="W950" s="3"/>
     </row>
     <row r="951" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="2"/>
@@ -23531,6 +24551,7 @@
       <c r="T951" s="3"/>
       <c r="U951" s="3"/>
       <c r="V951" s="3"/>
+      <c r="W951" s="3"/>
     </row>
     <row r="952" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="2"/>
@@ -23555,6 +24576,7 @@
       <c r="T952" s="3"/>
       <c r="U952" s="3"/>
       <c r="V952" s="3"/>
+      <c r="W952" s="3"/>
     </row>
     <row r="953" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="2"/>
@@ -23579,6 +24601,7 @@
       <c r="T953" s="3"/>
       <c r="U953" s="3"/>
       <c r="V953" s="3"/>
+      <c r="W953" s="3"/>
     </row>
     <row r="954" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="2"/>
@@ -23603,6 +24626,7 @@
       <c r="T954" s="3"/>
       <c r="U954" s="3"/>
       <c r="V954" s="3"/>
+      <c r="W954" s="3"/>
     </row>
     <row r="955" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="2"/>
@@ -23627,6 +24651,7 @@
       <c r="T955" s="3"/>
       <c r="U955" s="3"/>
       <c r="V955" s="3"/>
+      <c r="W955" s="3"/>
     </row>
     <row r="956" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="2"/>
@@ -23651,6 +24676,7 @@
       <c r="T956" s="3"/>
       <c r="U956" s="3"/>
       <c r="V956" s="3"/>
+      <c r="W956" s="3"/>
     </row>
     <row r="957" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="2"/>
@@ -23675,6 +24701,7 @@
       <c r="T957" s="3"/>
       <c r="U957" s="3"/>
       <c r="V957" s="3"/>
+      <c r="W957" s="3"/>
     </row>
     <row r="958" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="2"/>
@@ -23699,6 +24726,7 @@
       <c r="T958" s="3"/>
       <c r="U958" s="3"/>
       <c r="V958" s="3"/>
+      <c r="W958" s="3"/>
     </row>
     <row r="959" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="2"/>
@@ -23723,6 +24751,7 @@
       <c r="T959" s="3"/>
       <c r="U959" s="3"/>
       <c r="V959" s="3"/>
+      <c r="W959" s="3"/>
     </row>
     <row r="960" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="2"/>
@@ -23747,6 +24776,7 @@
       <c r="T960" s="3"/>
       <c r="U960" s="3"/>
       <c r="V960" s="3"/>
+      <c r="W960" s="3"/>
     </row>
     <row r="961" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="2"/>
@@ -23771,6 +24801,7 @@
       <c r="T961" s="3"/>
       <c r="U961" s="3"/>
       <c r="V961" s="3"/>
+      <c r="W961" s="3"/>
     </row>
     <row r="962" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="2"/>
@@ -23795,6 +24826,7 @@
       <c r="T962" s="3"/>
       <c r="U962" s="3"/>
       <c r="V962" s="3"/>
+      <c r="W962" s="3"/>
     </row>
     <row r="963" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="2"/>
@@ -23819,6 +24851,7 @@
       <c r="T963" s="3"/>
       <c r="U963" s="3"/>
       <c r="V963" s="3"/>
+      <c r="W963" s="3"/>
     </row>
     <row r="964" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="2"/>
@@ -23843,6 +24876,7 @@
       <c r="T964" s="3"/>
       <c r="U964" s="3"/>
       <c r="V964" s="3"/>
+      <c r="W964" s="3"/>
     </row>
     <row r="965" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="2"/>
@@ -23867,6 +24901,7 @@
       <c r="T965" s="3"/>
       <c r="U965" s="3"/>
       <c r="V965" s="3"/>
+      <c r="W965" s="3"/>
     </row>
     <row r="966" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="2"/>
@@ -23891,6 +24926,7 @@
       <c r="T966" s="3"/>
       <c r="U966" s="3"/>
       <c r="V966" s="3"/>
+      <c r="W966" s="3"/>
     </row>
     <row r="967" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="2"/>
@@ -23915,6 +24951,7 @@
       <c r="T967" s="3"/>
       <c r="U967" s="3"/>
       <c r="V967" s="3"/>
+      <c r="W967" s="3"/>
     </row>
     <row r="968" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="2"/>
@@ -23939,6 +24976,7 @@
       <c r="T968" s="3"/>
       <c r="U968" s="3"/>
       <c r="V968" s="3"/>
+      <c r="W968" s="3"/>
     </row>
     <row r="969" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="2"/>
@@ -23963,6 +25001,7 @@
       <c r="T969" s="3"/>
       <c r="U969" s="3"/>
       <c r="V969" s="3"/>
+      <c r="W969" s="3"/>
     </row>
     <row r="970" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="2"/>
@@ -23987,6 +25026,7 @@
       <c r="T970" s="3"/>
       <c r="U970" s="3"/>
       <c r="V970" s="3"/>
+      <c r="W970" s="3"/>
     </row>
     <row r="971" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="2"/>
@@ -24011,6 +25051,7 @@
       <c r="T971" s="3"/>
       <c r="U971" s="3"/>
       <c r="V971" s="3"/>
+      <c r="W971" s="3"/>
     </row>
     <row r="972" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="2"/>
@@ -24035,6 +25076,7 @@
       <c r="T972" s="3"/>
       <c r="U972" s="3"/>
       <c r="V972" s="3"/>
+      <c r="W972" s="3"/>
     </row>
     <row r="973" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="2"/>
@@ -24059,6 +25101,7 @@
       <c r="T973" s="3"/>
       <c r="U973" s="3"/>
       <c r="V973" s="3"/>
+      <c r="W973" s="3"/>
     </row>
     <row r="974" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="2"/>
@@ -24083,6 +25126,7 @@
       <c r="T974" s="3"/>
       <c r="U974" s="3"/>
       <c r="V974" s="3"/>
+      <c r="W974" s="3"/>
     </row>
     <row r="975" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="2"/>
@@ -24107,6 +25151,7 @@
       <c r="T975" s="3"/>
       <c r="U975" s="3"/>
       <c r="V975" s="3"/>
+      <c r="W975" s="3"/>
     </row>
     <row r="976" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="2"/>
@@ -24131,6 +25176,7 @@
       <c r="T976" s="3"/>
       <c r="U976" s="3"/>
       <c r="V976" s="3"/>
+      <c r="W976" s="3"/>
     </row>
     <row r="977" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="2"/>
@@ -24155,6 +25201,7 @@
       <c r="T977" s="3"/>
       <c r="U977" s="3"/>
       <c r="V977" s="3"/>
+      <c r="W977" s="3"/>
     </row>
     <row r="978" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="2"/>
@@ -24179,6 +25226,7 @@
       <c r="T978" s="3"/>
       <c r="U978" s="3"/>
       <c r="V978" s="3"/>
+      <c r="W978" s="3"/>
     </row>
     <row r="979" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="2"/>
@@ -24203,6 +25251,7 @@
       <c r="T979" s="3"/>
       <c r="U979" s="3"/>
       <c r="V979" s="3"/>
+      <c r="W979" s="3"/>
     </row>
     <row r="980" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="2"/>
@@ -24227,6 +25276,7 @@
       <c r="T980" s="3"/>
       <c r="U980" s="3"/>
       <c r="V980" s="3"/>
+      <c r="W980" s="3"/>
     </row>
     <row r="981" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="2"/>
@@ -24251,6 +25301,7 @@
       <c r="T981" s="3"/>
       <c r="U981" s="3"/>
       <c r="V981" s="3"/>
+      <c r="W981" s="3"/>
     </row>
     <row r="982" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="2"/>
@@ -24275,6 +25326,7 @@
       <c r="T982" s="3"/>
       <c r="U982" s="3"/>
       <c r="V982" s="3"/>
+      <c r="W982" s="3"/>
     </row>
     <row r="983" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="2"/>
@@ -24299,6 +25351,7 @@
       <c r="T983" s="3"/>
       <c r="U983" s="3"/>
       <c r="V983" s="3"/>
+      <c r="W983" s="3"/>
     </row>
     <row r="984" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="2"/>
@@ -24323,6 +25376,7 @@
       <c r="T984" s="3"/>
       <c r="U984" s="3"/>
       <c r="V984" s="3"/>
+      <c r="W984" s="3"/>
     </row>
     <row r="985" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="2"/>
@@ -24347,6 +25401,7 @@
       <c r="T985" s="3"/>
       <c r="U985" s="3"/>
       <c r="V985" s="3"/>
+      <c r="W985" s="3"/>
     </row>
     <row r="986" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="2"/>
@@ -24371,6 +25426,7 @@
       <c r="T986" s="3"/>
       <c r="U986" s="3"/>
       <c r="V986" s="3"/>
+      <c r="W986" s="3"/>
     </row>
     <row r="987" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="2"/>
@@ -24395,6 +25451,7 @@
       <c r="T987" s="3"/>
       <c r="U987" s="3"/>
       <c r="V987" s="3"/>
+      <c r="W987" s="3"/>
     </row>
     <row r="988" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="2"/>
@@ -24419,6 +25476,7 @@
       <c r="T988" s="3"/>
       <c r="U988" s="3"/>
       <c r="V988" s="3"/>
+      <c r="W988" s="3"/>
     </row>
     <row r="989" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="2"/>
@@ -24443,6 +25501,7 @@
       <c r="T989" s="3"/>
       <c r="U989" s="3"/>
       <c r="V989" s="3"/>
+      <c r="W989" s="3"/>
     </row>
     <row r="990" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="2"/>
@@ -24467,6 +25526,7 @@
       <c r="T990" s="3"/>
       <c r="U990" s="3"/>
       <c r="V990" s="3"/>
+      <c r="W990" s="3"/>
     </row>
     <row r="991" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="2"/>
@@ -24491,6 +25551,7 @@
       <c r="T991" s="3"/>
       <c r="U991" s="3"/>
       <c r="V991" s="3"/>
+      <c r="W991" s="3"/>
     </row>
     <row r="992" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="2"/>
@@ -24515,6 +25576,7 @@
       <c r="T992" s="3"/>
       <c r="U992" s="3"/>
       <c r="V992" s="3"/>
+      <c r="W992" s="3"/>
     </row>
     <row r="993" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="2"/>
@@ -24539,6 +25601,7 @@
       <c r="T993" s="3"/>
       <c r="U993" s="3"/>
       <c r="V993" s="3"/>
+      <c r="W993" s="3"/>
     </row>
     <row r="994" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="2"/>
@@ -24563,6 +25626,7 @@
       <c r="T994" s="3"/>
       <c r="U994" s="3"/>
       <c r="V994" s="3"/>
+      <c r="W994" s="3"/>
     </row>
     <row r="995" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="2"/>
@@ -24587,6 +25651,7 @@
       <c r="T995" s="3"/>
       <c r="U995" s="3"/>
       <c r="V995" s="3"/>
+      <c r="W995" s="3"/>
     </row>
     <row r="996" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="2"/>
@@ -24611,6 +25676,7 @@
       <c r="T996" s="3"/>
       <c r="U996" s="3"/>
       <c r="V996" s="3"/>
+      <c r="W996" s="3"/>
     </row>
     <row r="997" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="2"/>
@@ -24635,6 +25701,7 @@
       <c r="T997" s="3"/>
       <c r="U997" s="3"/>
       <c r="V997" s="3"/>
+      <c r="W997" s="3"/>
     </row>
     <row r="998" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="2"/>
@@ -24659,6 +25726,7 @@
       <c r="T998" s="3"/>
       <c r="U998" s="3"/>
       <c r="V998" s="3"/>
+      <c r="W998" s="3"/>
     </row>
     <row r="999" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="2"/>
@@ -24683,6 +25751,7 @@
       <c r="T999" s="3"/>
       <c r="U999" s="3"/>
       <c r="V999" s="3"/>
+      <c r="W999" s="3"/>
     </row>
     <row r="1000" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="2"/>
@@ -24707,6 +25776,7 @@
       <c r="T1000" s="3"/>
       <c r="U1000" s="3"/>
       <c r="V1000" s="3"/>
+      <c r="W1000" s="3"/>
     </row>
     <row r="1001" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1001" s="2"/>
@@ -24731,6 +25801,7 @@
       <c r="T1001" s="3"/>
       <c r="U1001" s="3"/>
       <c r="V1001" s="3"/>
+      <c r="W1001" s="3"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -294,7 +294,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,12 +339,6 @@
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="0"/>
     </font>
     <font>
       <u val="single"/>
@@ -437,7 +431,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -482,7 +476,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -490,11 +484,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1076,7 +1066,7 @@
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="2"/>
@@ -1108,7 +1098,7 @@
       <c r="D10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="11" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="2"/>
@@ -1145,7 +1135,7 @@
       <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="12" t="s">
         <v>34</v>
       </c>
       <c r="F11" s="2"/>
@@ -1223,7 +1213,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -1493,7 +1483,7 @@
       <c r="D21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="11" t="s">
         <v>58</v>
       </c>
       <c r="F21" s="2"/>
@@ -1591,7 +1581,7 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="2"/>
@@ -1627,7 +1617,7 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="12" t="s">
         <v>67</v>
       </c>
       <c r="F25" s="2"/>
@@ -1914,12 +1904,12 @@
       <c r="W33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="95">
   <si>
     <t xml:space="preserve">Рубрика</t>
   </si>
@@ -73,6 +73,9 @@
     <t xml:space="preserve">https://www.reld.com.ar/</t>
   </si>
   <si>
+    <t xml:space="preserve">Reld%2024foT</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bellini</t>
   </si>
   <si>
@@ -121,6 +124,12 @@
     <t xml:space="preserve">https://www.fijamom.com.ar/</t>
   </si>
   <si>
+    <t xml:space="preserve">dashamalkina.sf@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbtinternational</t>
+  </si>
+  <si>
     <t xml:space="preserve">Belgrano</t>
   </si>
   <si>
@@ -136,6 +145,12 @@
     <t xml:space="preserve">https://www.agrupacionduna.com/</t>
   </si>
   <si>
+    <t xml:space="preserve">sbt.international.srl@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asdfghjkl2024</t>
+  </si>
+  <si>
     <t xml:space="preserve">Компресора</t>
   </si>
   <si>
@@ -145,10 +160,16 @@
     <t xml:space="preserve">http://www.electrofrig.com.ar/es/</t>
   </si>
   <si>
+    <t xml:space="preserve">Asdfghj-2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">Electrocity</t>
   </si>
   <si>
     <t xml:space="preserve">https://electrocity.com.ar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sbtint2026</t>
   </si>
   <si>
     <t xml:space="preserve">Масла</t>
@@ -846,8 +867,12 @@
       <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="F3" s="2" t="n">
+        <v>254902</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>30718398254</v>
+      </c>
       <c r="H3" s="2" t="s">
         <v>14</v>
       </c>
@@ -887,8 +912,12 @@
       <c r="E4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="F4" s="2" t="n">
+        <v>30718398254</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
@@ -913,7 +942,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>12</v>
@@ -922,7 +951,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -947,22 +976,22 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -982,17 +1011,17 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1017,17 +1046,17 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1052,22 +1081,22 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -1087,10 +1116,10 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>12</v>
@@ -1099,10 +1128,14 @@
         <v>12</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1124,10 +1157,10 @@
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>12</v>
@@ -1136,7 +1169,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1161,10 +1194,10 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>12</v>
@@ -1173,10 +1206,14 @@
         <v>12</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
       </c>
@@ -1198,22 +1235,26 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="H13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -1234,15 +1275,19 @@
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="7"/>
       <c r="E14" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1264,17 +1309,17 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -1299,10 +1344,10 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="7" t="s">
@@ -1332,17 +1377,17 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -1367,10 +1412,10 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="7" t="s">
@@ -1400,10 +1445,10 @@
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>12</v>
@@ -1412,10 +1457,14 @@
         <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>12345678</v>
+      </c>
       <c r="H19" s="2" t="s">
         <v>14</v>
       </c>
@@ -1437,17 +1486,17 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1472,10 +1521,10 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>12</v>
@@ -1484,7 +1533,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1509,10 +1558,10 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>12</v>
@@ -1521,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1546,17 +1595,17 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1582,12 +1631,12 @@
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
       <c r="B24" s="13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="7"/>
       <c r="E24" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1613,12 +1662,12 @@
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="7"/>
       <c r="E25" s="12" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1643,15 +1692,15 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="7"/>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1676,18 +1725,22 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="H27" s="2" t="s">
         <v>14</v>
       </c>
@@ -1709,15 +1762,15 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="7"/>
       <c r="E28" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1742,10 +1795,10 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1774,12 +1827,12 @@
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1804,15 +1857,15 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -1837,17 +1890,17 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1872,15 +1925,15 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1905,7 +1958,7 @@
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="14" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -25804,25 +25857,31 @@
     <hyperlink ref="E8" r:id="rId6" display="https://www.torrington.com.ar/"/>
     <hyperlink ref="E9" r:id="rId7" display="https://listado.mercadolibre.com.ar/fluor-gas-refrigerantes"/>
     <hyperlink ref="E10" r:id="rId8" display="https://www.fijamom.com.ar/"/>
-    <hyperlink ref="E11" r:id="rId9" display="https://catalogo.duxsoftware.com.ar/3820"/>
-    <hyperlink ref="E12" r:id="rId10" display="https://www.agrupacionduna.com/"/>
-    <hyperlink ref="E13" r:id="rId11" display="http://www.electrofrig.com.ar/es/"/>
-    <hyperlink ref="E14" r:id="rId12" display="https://electrocity.com.ar"/>
-    <hyperlink ref="E15" r:id="rId13" display="https://refrioil.com/"/>
-    <hyperlink ref="E17" r:id="rId14" display="https://www.instagram.com/imi.metalurgica.integral/"/>
-    <hyperlink ref="E19" r:id="rId15" display="https://tienda.romarep.com.ar/"/>
-    <hyperlink ref="E20" r:id="rId16" display="https://oesteservice.com.ar/"/>
-    <hyperlink ref="E21" r:id="rId17" display="https://distribuidorajc.com/"/>
-    <hyperlink ref="E23" r:id="rId18" display="https://www.dpmg.com.ar/brand/anton/"/>
-    <hyperlink ref="E24" r:id="rId19" display="https://tidar.com.ar/"/>
-    <hyperlink ref="E25" r:id="rId20" display="https://casajarse.com/"/>
-    <hyperlink ref="E26" r:id="rId21" display="https://lujumar.com.ar/"/>
-    <hyperlink ref="E27" r:id="rId22" display="https://norfrig.com.ar/"/>
-    <hyperlink ref="E28" r:id="rId23" display="https://pilisardistribuidor.com.ar/"/>
-    <hyperlink ref="E30" r:id="rId24" display="https://industriasmct.com"/>
-    <hyperlink ref="E31" r:id="rId25" display="https://pini.com.ar/"/>
-    <hyperlink ref="E32" r:id="rId26" display="https://damfer.com/"/>
-    <hyperlink ref="E33" r:id="rId27" display="https://www.persano.com.ar/index.php"/>
+    <hyperlink ref="F10" r:id="rId9" display="dashamalkina.sf@gmail.com"/>
+    <hyperlink ref="E11" r:id="rId10" display="https://catalogo.duxsoftware.com.ar/3820"/>
+    <hyperlink ref="E12" r:id="rId11" display="https://www.agrupacionduna.com/"/>
+    <hyperlink ref="F12" r:id="rId12" display="sbt.international.srl@gmail.com"/>
+    <hyperlink ref="E13" r:id="rId13" display="http://www.electrofrig.com.ar/es/"/>
+    <hyperlink ref="F13" r:id="rId14" display="sbt.international.srl@gmail.com"/>
+    <hyperlink ref="E14" r:id="rId15" display="https://electrocity.com.ar"/>
+    <hyperlink ref="F14" r:id="rId16" display="sbt.international.srl@gmail.com"/>
+    <hyperlink ref="E15" r:id="rId17" display="https://refrioil.com/"/>
+    <hyperlink ref="E17" r:id="rId18" display="https://www.instagram.com/imi.metalurgica.integral/"/>
+    <hyperlink ref="E19" r:id="rId19" display="https://tienda.romarep.com.ar/"/>
+    <hyperlink ref="F19" r:id="rId20" display="sbt.international.srl@gmail.com"/>
+    <hyperlink ref="E20" r:id="rId21" display="https://oesteservice.com.ar/"/>
+    <hyperlink ref="E21" r:id="rId22" display="https://distribuidorajc.com/"/>
+    <hyperlink ref="E23" r:id="rId23" display="https://www.dpmg.com.ar/brand/anton/"/>
+    <hyperlink ref="E24" r:id="rId24" display="https://tidar.com.ar/"/>
+    <hyperlink ref="E25" r:id="rId25" display="https://casajarse.com/"/>
+    <hyperlink ref="E26" r:id="rId26" display="https://lujumar.com.ar/"/>
+    <hyperlink ref="E27" r:id="rId27" display="https://norfrig.com.ar/"/>
+    <hyperlink ref="F27" r:id="rId28" display="sbt.international.srl@gmail.com"/>
+    <hyperlink ref="E28" r:id="rId29" display="https://pilisardistribuidor.com.ar/"/>
+    <hyperlink ref="E30" r:id="rId30" display="https://industriasmct.com"/>
+    <hyperlink ref="E31" r:id="rId31" display="https://pini.com.ar/"/>
+    <hyperlink ref="E32" r:id="rId32" display="https://damfer.com/"/>
+    <hyperlink ref="E33" r:id="rId33" display="https://www.persano.com.ar/index.php"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
   <si>
     <t xml:space="preserve">Рубрика</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t xml:space="preserve">https://www.persano.com.ar/index.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refrigeracion Norte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://refrigeracionnorte.com.ar/</t>
   </si>
   <si>
     <t xml:space="preserve">Итог по холоду и климату</t>
@@ -766,7 +772,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W1048576"/>
+  <dimension ref="A1:W1002"/>
   <sheetFormatPr defaultColWidth="14.4296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="17.43"/>
@@ -1957,16 +1963,20 @@
       <c r="W33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
+      <c r="H34" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -1983,11 +1993,13 @@
       <c r="V34" s="2"/>
       <c r="W34" s="2"/>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -2008,12 +2020,36 @@
       <c r="V35" s="2"/>
       <c r="W35" s="2"/>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+    </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -2021,31 +2057,7 @@
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-    </row>
+    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
@@ -25846,7 +25858,31 @@
       <c r="V1001" s="3"/>
       <c r="W1001" s="3"/>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1002" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1002" s="2"/>
+      <c r="B1002" s="2"/>
+      <c r="C1002" s="3"/>
+      <c r="D1002" s="3"/>
+      <c r="E1002" s="3"/>
+      <c r="F1002" s="3"/>
+      <c r="G1002" s="3"/>
+      <c r="H1002" s="3"/>
+      <c r="I1002" s="3"/>
+      <c r="J1002" s="3"/>
+      <c r="K1002" s="3"/>
+      <c r="L1002" s="3"/>
+      <c r="M1002" s="3"/>
+      <c r="N1002" s="3"/>
+      <c r="O1002" s="3"/>
+      <c r="P1002" s="3"/>
+      <c r="Q1002" s="3"/>
+      <c r="R1002" s="3"/>
+      <c r="S1002" s="3"/>
+      <c r="T1002" s="3"/>
+      <c r="U1002" s="3"/>
+      <c r="V1002" s="3"/>
+      <c r="W1002" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" display="https://www.ansal.com.ar/"/>
@@ -25882,6 +25918,7 @@
     <hyperlink ref="E31" r:id="rId31" display="https://pini.com.ar/"/>
     <hyperlink ref="E32" r:id="rId32" display="https://damfer.com/"/>
     <hyperlink ref="E33" r:id="rId33" display="https://www.persano.com.ar/index.php"/>
+    <hyperlink ref="E34" r:id="rId34" display="https://refrigeracionnorte.com.ar/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/init_uploads/download_files/Копия Список поставщиков.xlsx
+++ b/init_uploads/download_files/Копия Список поставщиков.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="101">
   <si>
     <t xml:space="preserve">Рубрика</t>
   </si>
@@ -52,6 +52,9 @@
     <t xml:space="preserve">IVA</t>
   </si>
   <si>
+    <t xml:space="preserve">Данные</t>
+  </si>
+  <si>
     <t xml:space="preserve">Холод-Климат</t>
   </si>
   <si>
@@ -67,6 +70,9 @@
     <t xml:space="preserve">ARS</t>
   </si>
   <si>
+    <t xml:space="preserve">web</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reld</t>
   </si>
   <si>
@@ -76,10 +82,16 @@
     <t xml:space="preserve">Reld%2024foT</t>
   </si>
   <si>
+    <t xml:space="preserve">doc, web</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bellini</t>
   </si>
   <si>
     <t xml:space="preserve">www.bellinihnos.com.ar/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">doc</t>
   </si>
   <si>
     <t xml:space="preserve">Холод-Климат Сма</t>
@@ -458,7 +470,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -481,6 +493,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -777,8 +793,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="1" min="1" style="1" width="17.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.43"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="14.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="34.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.27"/>
@@ -843,7 +859,9 @@
       <c r="J2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="2"/>
+      <c r="K2" s="6" t="s">
+        <v>10</v>
+      </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -859,19 +877,19 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>12</v>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>13</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>254902</v>
@@ -880,15 +898,17 @@
         <v>30718398254</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <v>0.21</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K3" s="2"/>
+      <c r="K3" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -904,32 +924,34 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
+      <c r="B4" s="7" t="s">
+        <v>17</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
+      <c r="C4" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>12</v>
+      <c r="D4" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>16</v>
+      <c r="E4" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>30718398254</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="K4" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -945,28 +967,30 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
+      <c r="B5" s="7" t="s">
+        <v>21</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
+      <c r="C5" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>12</v>
+      <c r="D5" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>19</v>
+      <c r="E5" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="K5" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -982,26 +1006,28 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="7" t="s">
-        <v>12</v>
+      <c r="C6" s="11"/>
+      <c r="D6" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="K6" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -1017,26 +1043,28 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="7" t="s">
-        <v>12</v>
+      <c r="C7" s="11"/>
+      <c r="D7" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="K7" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -1052,26 +1080,26 @@
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>27</v>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="7" t="s">
-        <v>12</v>
+      <c r="D8" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="6"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1087,26 +1115,28 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>29</v>
+      <c r="B9" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="7" t="s">
-        <v>12</v>
+      <c r="D9" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="K9" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -1122,32 +1152,34 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>12</v>
+      <c r="C10" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>12</v>
+      <c r="D10" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>33</v>
+      <c r="E10" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="K10" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1163,28 +1195,30 @@
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>36</v>
+      <c r="B11" s="7" t="s">
+        <v>40</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>12</v>
+      <c r="C11" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>12</v>
+      <c r="D11" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E11" s="12" t="s">
-        <v>37</v>
+      <c r="E11" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="K11" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -1200,32 +1234,34 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>12</v>
+      <c r="C12" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>12</v>
+      <c r="D12" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>40</v>
+      <c r="E12" s="9" t="s">
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="K12" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -1241,30 +1277,32 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>44</v>
+      <c r="B13" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="7" t="s">
-        <v>12</v>
+      <c r="D13" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="G13" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -1281,25 +1319,27 @@
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="K14" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -1315,26 +1355,26 @@
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="7" t="s">
-        <v>12</v>
+      <c r="D15" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="K15" s="6"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -1350,24 +1390,24 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="7" t="s">
-        <v>12</v>
+      <c r="D16" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="K16" s="6"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -1383,26 +1423,28 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="7" t="s">
-        <v>12</v>
+      <c r="D17" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="K17" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1418,24 +1460,26 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>59</v>
+      <c r="B18" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="7" t="s">
-        <v>12</v>
+      <c r="D18" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="K18" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -1451,32 +1495,34 @@
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>60</v>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>12</v>
+      <c r="C19" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>12</v>
+      <c r="D19" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>12345678</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="K19" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -1492,26 +1538,26 @@
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="7" t="s">
-        <v>12</v>
+      <c r="D20" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="K20" s="6"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -1527,28 +1573,30 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>12</v>
+      <c r="C21" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>12</v>
+      <c r="D21" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="E21" s="11" t="s">
-        <v>65</v>
+      <c r="E21" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="K21" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -1564,28 +1612,30 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>12</v>
+      <c r="C22" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>12</v>
+      <c r="D22" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
+      <c r="K22" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -1601,26 +1651,26 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="7" t="s">
-        <v>12</v>
+      <c r="C23" s="11"/>
+      <c r="D23" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="K23" s="6"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1636,22 +1686,24 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="13" t="s">
-        <v>71</v>
+      <c r="B24" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="8"/>
       <c r="E24" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -1668,21 +1720,23 @@
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="12" t="s">
-        <v>74</v>
+      <c r="D25" s="8"/>
+      <c r="E25" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -1698,24 +1752,24 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
+      <c r="K26" s="6"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -1731,28 +1785,30 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
+      <c r="K27" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -1768,24 +1824,24 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="8"/>
       <c r="E28" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
+      <c r="K28" s="6"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -1801,10 +1857,10 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1812,11 +1868,11 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
+      <c r="K29" s="6"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -1833,21 +1889,21 @@
     <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
+      <c r="K30" s="6"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
@@ -1863,24 +1919,24 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+      <c r="K31" s="6"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -1896,26 +1952,26 @@
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C32" s="2"/>
-      <c r="D32" s="7" t="s">
-        <v>12</v>
+      <c r="D32" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
+      <c r="K32" s="6"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
@@ -1931,24 +1987,24 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="K33" s="6"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -1965,21 +2021,23 @@
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2"/>
       <c r="B34" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="K34" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -1994,19 +2052,19 @@
       <c r="W34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="14" t="s">
-        <v>96</v>
+      <c r="A35" s="15" t="s">
+        <v>100</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
+      <c r="K35" s="6"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
